--- a/data/c_dropColor(掉落品质).xlsx
+++ b/data/c_dropColor(掉落品质).xlsx
@@ -356,7 +356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,6 +367,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -688,7 +694,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -712,16 +718,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
@@ -730,89 +736,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -829,6 +835,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9371,133 +9380,133 @@
       <c r="H374" s="1"/>
     </row>
     <row r="375" ht="14.25" spans="1:8">
-      <c r="A375" s="1">
+      <c r="A375" s="6">
         <v>373</v>
       </c>
-      <c r="B375" s="1" t="s">
+      <c r="B375" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C375" s="1" t="s">
+      <c r="C375" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D375" s="1" t="s">
+      <c r="D375" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E375" s="1">
-        <v>50025</v>
-      </c>
-      <c r="F375" s="1">
+      <c r="E375" s="6">
+        <v>60016</v>
+      </c>
+      <c r="F375" s="6">
         <v>0</v>
       </c>
       <c r="G375" s="1"/>
       <c r="H375" s="1"/>
     </row>
     <row r="376" ht="14.25" spans="1:8">
-      <c r="A376" s="1">
+      <c r="A376" s="6">
         <v>374</v>
       </c>
-      <c r="B376" s="1" t="s">
+      <c r="B376" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C376" s="1" t="s">
+      <c r="C376" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D376" s="1" t="s">
+      <c r="D376" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E376" s="1">
-        <v>50025</v>
-      </c>
-      <c r="F376" s="1">
-        <v>1400</v>
+      <c r="E376" s="6">
+        <v>60016</v>
+      </c>
+      <c r="F376" s="6">
+        <v>0</v>
       </c>
       <c r="G376" s="1"/>
       <c r="H376" s="1"/>
     </row>
     <row r="377" ht="14.25" spans="1:8">
-      <c r="A377" s="1">
+      <c r="A377" s="6">
         <v>375</v>
       </c>
-      <c r="B377" s="1" t="s">
+      <c r="B377" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C377" s="1" t="s">
+      <c r="C377" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D377" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E377" s="1">
-        <v>50025</v>
-      </c>
-      <c r="F377" s="1">
-        <v>5000</v>
+      <c r="D377" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E377" s="6">
+        <v>60016</v>
+      </c>
+      <c r="F377" s="6">
+        <v>4350</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
     </row>
     <row r="378" ht="14.25" spans="1:8">
-      <c r="A378" s="1">
+      <c r="A378" s="6">
         <v>376</v>
       </c>
-      <c r="B378" s="1" t="s">
+      <c r="B378" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C378" s="1" t="s">
+      <c r="C378" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D378" s="1" t="s">
+      <c r="D378" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E378" s="1">
-        <v>50025</v>
-      </c>
-      <c r="F378" s="1">
-        <v>3000</v>
+      <c r="E378" s="6">
+        <v>60016</v>
+      </c>
+      <c r="F378" s="6">
+        <v>4350</v>
       </c>
       <c r="G378" s="1"/>
       <c r="H378" s="1"/>
     </row>
     <row r="379" ht="14.25" spans="1:8">
-      <c r="A379" s="1">
+      <c r="A379" s="6">
         <v>377</v>
       </c>
-      <c r="B379" s="1" t="s">
+      <c r="B379" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C379" s="1" t="s">
+      <c r="C379" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D379" s="1" t="s">
+      <c r="D379" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E379" s="1">
-        <v>50025</v>
-      </c>
-      <c r="F379" s="1">
-        <v>500</v>
+      <c r="E379" s="6">
+        <v>60016</v>
+      </c>
+      <c r="F379" s="6">
+        <v>1000</v>
       </c>
       <c r="G379" s="1"/>
       <c r="H379" s="1"/>
     </row>
     <row r="380" ht="14.25" spans="1:8">
-      <c r="A380" s="1">
+      <c r="A380" s="6">
         <v>378</v>
       </c>
-      <c r="B380" s="1" t="s">
+      <c r="B380" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C380" s="1" t="s">
+      <c r="C380" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D380" s="1" t="s">
+      <c r="D380" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E380" s="1">
-        <v>50025</v>
-      </c>
-      <c r="F380" s="1">
-        <v>100</v>
+      <c r="E380" s="6">
+        <v>60016</v>
+      </c>
+      <c r="F380" s="6">
+        <v>300</v>
       </c>
       <c r="G380" s="1"/>
       <c r="H380" s="1"/>

--- a/data/c_dropColor(掉落品质).xlsx
+++ b/data/c_dropColor(掉落品质).xlsx
@@ -185,11 +185,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -206,10 +207,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -818,7 +820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -831,13 +833,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -892,6 +897,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.799798577837458"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1211,7 +1225,7 @@
       <c r="E3" s="1">
         <v>10011</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="4">
         <v>6000</v>
       </c>
       <c r="G3" s="1"/>
@@ -1233,7 +1247,7 @@
       <c r="E4" s="1">
         <v>10011</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="4">
         <v>3000</v>
       </c>
       <c r="G4" s="1"/>
@@ -1255,7 +1269,7 @@
       <c r="E5" s="1">
         <v>10011</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="4">
         <v>700</v>
       </c>
       <c r="G5" s="1"/>
@@ -1277,7 +1291,7 @@
       <c r="E6" s="1">
         <v>10011</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="4">
         <v>289</v>
       </c>
       <c r="G6" s="1"/>
@@ -1299,7 +1313,7 @@
       <c r="E7" s="1">
         <v>10011</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="4">
         <v>10</v>
       </c>
       <c r="G7" s="1"/>
@@ -1321,7 +1335,7 @@
       <c r="E8" s="1">
         <v>10011</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>1</v>
       </c>
       <c r="G8" s="1"/>
@@ -1343,7 +1357,7 @@
       <c r="E9" s="1">
         <v>10021</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4">
         <v>6000</v>
       </c>
       <c r="G9" s="1"/>
@@ -1365,7 +1379,7 @@
       <c r="E10" s="1">
         <v>10021</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="4">
         <v>3000</v>
       </c>
       <c r="G10" s="1"/>
@@ -1387,7 +1401,7 @@
       <c r="E11" s="1">
         <v>10021</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="4">
         <v>700</v>
       </c>
       <c r="G11" s="1"/>
@@ -1409,7 +1423,7 @@
       <c r="E12" s="1">
         <v>10021</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="4">
         <v>289</v>
       </c>
       <c r="G12" s="1"/>
@@ -1431,7 +1445,7 @@
       <c r="E13" s="1">
         <v>10021</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="4">
         <v>10</v>
       </c>
       <c r="G13" s="1"/>
@@ -1453,7 +1467,7 @@
       <c r="E14" s="1">
         <v>10021</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="4">
         <v>1</v>
       </c>
       <c r="G14" s="1"/>
@@ -1475,7 +1489,7 @@
       <c r="E15" s="1">
         <v>10031</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="4">
         <v>6000</v>
       </c>
       <c r="G15" s="1"/>
@@ -1497,7 +1511,7 @@
       <c r="E16" s="1">
         <v>10031</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="4">
         <v>3000</v>
       </c>
       <c r="G16" s="1"/>
@@ -1519,7 +1533,7 @@
       <c r="E17" s="1">
         <v>10031</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="4">
         <v>700</v>
       </c>
       <c r="G17" s="1"/>
@@ -1541,7 +1555,7 @@
       <c r="E18" s="1">
         <v>10031</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="4">
         <v>289</v>
       </c>
       <c r="G18" s="1"/>
@@ -1563,7 +1577,7 @@
       <c r="E19" s="1">
         <v>10031</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="4">
         <v>10</v>
       </c>
       <c r="G19" s="1"/>
@@ -1585,7 +1599,7 @@
       <c r="E20" s="1">
         <v>10031</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="4">
         <v>1</v>
       </c>
       <c r="G20" s="1"/>
@@ -1607,7 +1621,7 @@
       <c r="E21" s="1">
         <v>10041</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="4">
         <v>6000</v>
       </c>
       <c r="G21" s="1"/>
@@ -1629,7 +1643,7 @@
       <c r="E22" s="1">
         <v>10041</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="4">
         <v>3000</v>
       </c>
       <c r="G22" s="1"/>
@@ -1651,7 +1665,7 @@
       <c r="E23" s="1">
         <v>10041</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="4">
         <v>700</v>
       </c>
       <c r="G23" s="1"/>
@@ -1673,7 +1687,7 @@
       <c r="E24" s="1">
         <v>10041</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="4">
         <v>289</v>
       </c>
       <c r="G24" s="1"/>
@@ -1695,7 +1709,7 @@
       <c r="E25" s="1">
         <v>10041</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="4">
         <v>10</v>
       </c>
       <c r="G25" s="1"/>
@@ -1717,7 +1731,7 @@
       <c r="E26" s="1">
         <v>10041</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="4">
         <v>1</v>
       </c>
       <c r="G26" s="1"/>
@@ -1739,7 +1753,7 @@
       <c r="E27" s="1">
         <v>10051</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="4">
         <v>6000</v>
       </c>
       <c r="G27" s="1"/>
@@ -1761,7 +1775,7 @@
       <c r="E28" s="1">
         <v>10051</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="4">
         <v>3000</v>
       </c>
       <c r="G28" s="1"/>
@@ -1783,7 +1797,7 @@
       <c r="E29" s="1">
         <v>10051</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="4">
         <v>700</v>
       </c>
       <c r="G29" s="1"/>
@@ -1805,7 +1819,7 @@
       <c r="E30" s="1">
         <v>10051</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="4">
         <v>289</v>
       </c>
       <c r="G30" s="1"/>
@@ -1827,7 +1841,7 @@
       <c r="E31" s="1">
         <v>10051</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="4">
         <v>10</v>
       </c>
       <c r="G31" s="1"/>
@@ -1849,7 +1863,7 @@
       <c r="E32" s="1">
         <v>10051</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="4">
         <v>1</v>
       </c>
       <c r="G32" s="1"/>
@@ -1871,7 +1885,7 @@
       <c r="E33" s="1">
         <v>10061</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="4">
         <v>6000</v>
       </c>
       <c r="G33" s="1"/>
@@ -1893,7 +1907,7 @@
       <c r="E34" s="1">
         <v>10061</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="4">
         <v>3000</v>
       </c>
       <c r="G34" s="1"/>
@@ -1915,7 +1929,7 @@
       <c r="E35" s="1">
         <v>10061</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="4">
         <v>700</v>
       </c>
       <c r="G35" s="1"/>
@@ -1937,7 +1951,7 @@
       <c r="E36" s="1">
         <v>10061</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="4">
         <v>289</v>
       </c>
       <c r="G36" s="1"/>
@@ -1959,7 +1973,7 @@
       <c r="E37" s="1">
         <v>10061</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="4">
         <v>10</v>
       </c>
       <c r="G37" s="1"/>
@@ -1981,7 +1995,7 @@
       <c r="E38" s="1">
         <v>10061</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="4">
         <v>1</v>
       </c>
       <c r="G38" s="1"/>
@@ -2003,7 +2017,7 @@
       <c r="E39" s="1">
         <v>10071</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="4">
         <v>6000</v>
       </c>
       <c r="G39" s="1"/>
@@ -2025,7 +2039,7 @@
       <c r="E40" s="1">
         <v>10071</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="4">
         <v>3000</v>
       </c>
       <c r="G40" s="1"/>
@@ -2047,7 +2061,7 @@
       <c r="E41" s="1">
         <v>10071</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="4">
         <v>700</v>
       </c>
       <c r="G41" s="1"/>
@@ -2069,7 +2083,7 @@
       <c r="E42" s="1">
         <v>10071</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="4">
         <v>289</v>
       </c>
       <c r="G42" s="1"/>
@@ -2091,7 +2105,7 @@
       <c r="E43" s="1">
         <v>10071</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="4">
         <v>10</v>
       </c>
       <c r="G43" s="1"/>
@@ -2113,7 +2127,7 @@
       <c r="E44" s="1">
         <v>10071</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="4">
         <v>1</v>
       </c>
       <c r="G44" s="1"/>
@@ -2135,7 +2149,7 @@
       <c r="E45" s="1">
         <v>10081</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="4">
         <v>6000</v>
       </c>
       <c r="G45" s="1"/>
@@ -2157,7 +2171,7 @@
       <c r="E46" s="1">
         <v>10081</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="4">
         <v>3000</v>
       </c>
       <c r="G46" s="1"/>
@@ -2179,7 +2193,7 @@
       <c r="E47" s="1">
         <v>10081</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="4">
         <v>700</v>
       </c>
       <c r="G47" s="1"/>
@@ -2201,7 +2215,7 @@
       <c r="E48" s="1">
         <v>10081</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="4">
         <v>289</v>
       </c>
       <c r="G48" s="1"/>
@@ -2223,7 +2237,7 @@
       <c r="E49" s="1">
         <v>10081</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="4">
         <v>10</v>
       </c>
       <c r="G49" s="1"/>
@@ -2245,7 +2259,7 @@
       <c r="E50" s="1">
         <v>10081</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="4">
         <v>1</v>
       </c>
       <c r="G50" s="1"/>
@@ -2267,7 +2281,7 @@
       <c r="E51" s="1">
         <v>10091</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="4">
         <v>6000</v>
       </c>
       <c r="G51" s="1"/>
@@ -2289,7 +2303,7 @@
       <c r="E52" s="1">
         <v>10091</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="4">
         <v>3000</v>
       </c>
       <c r="G52" s="1"/>
@@ -2311,7 +2325,7 @@
       <c r="E53" s="1">
         <v>10091</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="4">
         <v>700</v>
       </c>
       <c r="G53" s="1"/>
@@ -2333,7 +2347,7 @@
       <c r="E54" s="1">
         <v>10091</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="4">
         <v>289</v>
       </c>
       <c r="G54" s="1"/>
@@ -2355,7 +2369,7 @@
       <c r="E55" s="1">
         <v>10091</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="4">
         <v>10</v>
       </c>
       <c r="G55" s="1"/>
@@ -2377,7 +2391,7 @@
       <c r="E56" s="1">
         <v>10091</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="4">
         <v>1</v>
       </c>
       <c r="G56" s="1"/>
@@ -2399,7 +2413,7 @@
       <c r="E57" s="1">
         <v>10101</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="4">
         <v>6000</v>
       </c>
       <c r="G57" s="1"/>
@@ -2421,7 +2435,7 @@
       <c r="E58" s="1">
         <v>10101</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="4">
         <v>3000</v>
       </c>
       <c r="G58" s="1"/>
@@ -2443,7 +2457,7 @@
       <c r="E59" s="1">
         <v>10101</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="4">
         <v>700</v>
       </c>
       <c r="G59" s="1"/>
@@ -2465,7 +2479,7 @@
       <c r="E60" s="1">
         <v>10101</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="4">
         <v>289</v>
       </c>
       <c r="G60" s="1"/>
@@ -2487,7 +2501,7 @@
       <c r="E61" s="1">
         <v>10101</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="4">
         <v>10</v>
       </c>
       <c r="G61" s="1"/>
@@ -2509,7 +2523,7 @@
       <c r="E62" s="1">
         <v>10101</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="4">
         <v>1</v>
       </c>
       <c r="G62" s="1"/>
@@ -2531,7 +2545,7 @@
       <c r="E63" s="1">
         <v>20012</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="4">
         <v>4000</v>
       </c>
       <c r="G63" s="1"/>
@@ -2553,7 +2567,7 @@
       <c r="E64" s="1">
         <v>20012</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="4">
         <v>4000</v>
       </c>
       <c r="G64" s="1"/>
@@ -2575,7 +2589,7 @@
       <c r="E65" s="1">
         <v>20012</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="4">
         <v>1500</v>
       </c>
       <c r="G65" s="1"/>
@@ -2597,7 +2611,7 @@
       <c r="E66" s="1">
         <v>20012</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="4">
         <v>467</v>
       </c>
       <c r="G66" s="1"/>
@@ -2619,7 +2633,7 @@
       <c r="E67" s="1">
         <v>20012</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="4">
         <v>30</v>
       </c>
       <c r="G67" s="1"/>
@@ -2641,7 +2655,7 @@
       <c r="E68" s="1">
         <v>20012</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="4">
         <v>3</v>
       </c>
       <c r="G68" s="1"/>
@@ -2663,7 +2677,7 @@
       <c r="E69" s="1">
         <v>20012</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="4">
         <v>6000</v>
       </c>
       <c r="G69" s="1"/>
@@ -2685,7 +2699,7 @@
       <c r="E70" s="1">
         <v>20012</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="4">
         <v>3000</v>
       </c>
       <c r="G70" s="1"/>
@@ -2707,7 +2721,7 @@
       <c r="E71" s="1">
         <v>20012</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="4">
         <v>700</v>
       </c>
       <c r="G71" s="1"/>
@@ -2729,7 +2743,7 @@
       <c r="E72" s="1">
         <v>20012</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="4">
         <v>289</v>
       </c>
       <c r="G72" s="1"/>
@@ -2751,7 +2765,7 @@
       <c r="E73" s="1">
         <v>20012</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="4">
         <v>10</v>
       </c>
       <c r="G73" s="1"/>
@@ -2773,7 +2787,7 @@
       <c r="E74" s="1">
         <v>20012</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="4">
         <v>1</v>
       </c>
       <c r="G74" s="1"/>
@@ -2795,7 +2809,7 @@
       <c r="E75" s="1">
         <v>20022</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="4">
         <v>4000</v>
       </c>
       <c r="G75" s="1"/>
@@ -2817,7 +2831,7 @@
       <c r="E76" s="1">
         <v>20022</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="4">
         <v>4000</v>
       </c>
       <c r="G76" s="1"/>
@@ -2839,7 +2853,7 @@
       <c r="E77" s="1">
         <v>20022</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="4">
         <v>1500</v>
       </c>
       <c r="G77" s="1"/>
@@ -2861,7 +2875,7 @@
       <c r="E78" s="1">
         <v>20022</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="4">
         <v>467</v>
       </c>
       <c r="G78" s="1"/>
@@ -2883,7 +2897,7 @@
       <c r="E79" s="1">
         <v>20022</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="4">
         <v>30</v>
       </c>
       <c r="G79" s="1"/>
@@ -2905,7 +2919,7 @@
       <c r="E80" s="1">
         <v>20022</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="4">
         <v>3</v>
       </c>
       <c r="G80" s="1"/>
@@ -2927,7 +2941,7 @@
       <c r="E81" s="1">
         <v>20022</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="4">
         <v>6000</v>
       </c>
       <c r="G81" s="1"/>
@@ -2949,7 +2963,7 @@
       <c r="E82" s="1">
         <v>20022</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="4">
         <v>3000</v>
       </c>
       <c r="G82" s="1"/>
@@ -2971,7 +2985,7 @@
       <c r="E83" s="1">
         <v>20022</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="4">
         <v>700</v>
       </c>
       <c r="G83" s="1"/>
@@ -2993,7 +3007,7 @@
       <c r="E84" s="1">
         <v>20022</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="4">
         <v>289</v>
       </c>
       <c r="G84" s="1"/>
@@ -3015,7 +3029,7 @@
       <c r="E85" s="1">
         <v>20022</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="4">
         <v>10</v>
       </c>
       <c r="G85" s="1"/>
@@ -3037,7 +3051,7 @@
       <c r="E86" s="1">
         <v>20022</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="4">
         <v>1</v>
       </c>
       <c r="G86" s="1"/>
@@ -3059,7 +3073,7 @@
       <c r="E87" s="1">
         <v>20032</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="4">
         <v>4000</v>
       </c>
       <c r="G87" s="1"/>
@@ -3081,7 +3095,7 @@
       <c r="E88" s="1">
         <v>20032</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="4">
         <v>4000</v>
       </c>
       <c r="G88" s="1"/>
@@ -3103,7 +3117,7 @@
       <c r="E89" s="1">
         <v>20032</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="4">
         <v>1500</v>
       </c>
       <c r="G89" s="1"/>
@@ -3125,7 +3139,7 @@
       <c r="E90" s="1">
         <v>20032</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="4">
         <v>467</v>
       </c>
       <c r="G90" s="1"/>
@@ -3147,7 +3161,7 @@
       <c r="E91" s="1">
         <v>20032</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="4">
         <v>30</v>
       </c>
       <c r="G91" s="1"/>
@@ -3169,7 +3183,7 @@
       <c r="E92" s="1">
         <v>20032</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="4">
         <v>3</v>
       </c>
       <c r="G92" s="1"/>
@@ -3191,7 +3205,7 @@
       <c r="E93" s="1">
         <v>20032</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="4">
         <v>6000</v>
       </c>
       <c r="G93" s="1"/>
@@ -3213,7 +3227,7 @@
       <c r="E94" s="1">
         <v>20032</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="4">
         <v>3000</v>
       </c>
       <c r="G94" s="1"/>
@@ -3235,7 +3249,7 @@
       <c r="E95" s="1">
         <v>20032</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="4">
         <v>700</v>
       </c>
       <c r="G95" s="1"/>
@@ -3257,7 +3271,7 @@
       <c r="E96" s="1">
         <v>20032</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="4">
         <v>289</v>
       </c>
       <c r="G96" s="1"/>
@@ -3279,7 +3293,7 @@
       <c r="E97" s="1">
         <v>20032</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="4">
         <v>10</v>
       </c>
       <c r="G97" s="1"/>
@@ -3301,7 +3315,7 @@
       <c r="E98" s="1">
         <v>20032</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="4">
         <v>1</v>
       </c>
       <c r="G98" s="1"/>
@@ -3323,7 +3337,7 @@
       <c r="E99" s="1">
         <v>20042</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="4">
         <v>4000</v>
       </c>
       <c r="G99" s="1"/>
@@ -3345,7 +3359,7 @@
       <c r="E100" s="1">
         <v>20042</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="4">
         <v>4000</v>
       </c>
       <c r="G100" s="1"/>
@@ -3367,7 +3381,7 @@
       <c r="E101" s="1">
         <v>20042</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="4">
         <v>1500</v>
       </c>
       <c r="G101" s="1"/>
@@ -3389,7 +3403,7 @@
       <c r="E102" s="1">
         <v>20042</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="4">
         <v>467</v>
       </c>
       <c r="G102" s="1"/>
@@ -3411,7 +3425,7 @@
       <c r="E103" s="1">
         <v>20042</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="4">
         <v>30</v>
       </c>
       <c r="G103" s="1"/>
@@ -3433,7 +3447,7 @@
       <c r="E104" s="1">
         <v>20042</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="4">
         <v>3</v>
       </c>
       <c r="G104" s="1"/>
@@ -3455,7 +3469,7 @@
       <c r="E105" s="1">
         <v>20042</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="4">
         <v>6000</v>
       </c>
       <c r="G105" s="1"/>
@@ -3477,7 +3491,7 @@
       <c r="E106" s="1">
         <v>20042</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="4">
         <v>3000</v>
       </c>
       <c r="G106" s="1"/>
@@ -3499,7 +3513,7 @@
       <c r="E107" s="1">
         <v>20042</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="4">
         <v>700</v>
       </c>
       <c r="G107" s="1"/>
@@ -3521,7 +3535,7 @@
       <c r="E108" s="1">
         <v>20042</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="4">
         <v>289</v>
       </c>
       <c r="G108" s="1"/>
@@ -3543,7 +3557,7 @@
       <c r="E109" s="1">
         <v>20042</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="4">
         <v>10</v>
       </c>
       <c r="G109" s="1"/>
@@ -3565,7 +3579,7 @@
       <c r="E110" s="1">
         <v>20042</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="4">
         <v>1</v>
       </c>
       <c r="G110" s="1"/>
@@ -3587,7 +3601,7 @@
       <c r="E111" s="1">
         <v>20052</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="4">
         <v>4000</v>
       </c>
       <c r="G111" s="1"/>
@@ -3609,7 +3623,7 @@
       <c r="E112" s="1">
         <v>20052</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="4">
         <v>4000</v>
       </c>
       <c r="G112" s="1"/>
@@ -3631,7 +3645,7 @@
       <c r="E113" s="1">
         <v>20052</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="4">
         <v>1500</v>
       </c>
       <c r="G113" s="1"/>
@@ -3653,7 +3667,7 @@
       <c r="E114" s="1">
         <v>20052</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="4">
         <v>467</v>
       </c>
       <c r="G114" s="1"/>
@@ -3675,7 +3689,7 @@
       <c r="E115" s="1">
         <v>20052</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="4">
         <v>30</v>
       </c>
       <c r="G115" s="1"/>
@@ -3697,7 +3711,7 @@
       <c r="E116" s="1">
         <v>20052</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="4">
         <v>3</v>
       </c>
       <c r="G116" s="1"/>
@@ -3719,7 +3733,7 @@
       <c r="E117" s="1">
         <v>20052</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="4">
         <v>6000</v>
       </c>
       <c r="G117" s="1"/>
@@ -3741,7 +3755,7 @@
       <c r="E118" s="1">
         <v>20052</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="4">
         <v>3000</v>
       </c>
       <c r="G118" s="1"/>
@@ -3763,7 +3777,7 @@
       <c r="E119" s="1">
         <v>20052</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="4">
         <v>700</v>
       </c>
       <c r="G119" s="1"/>
@@ -3785,7 +3799,7 @@
       <c r="E120" s="1">
         <v>20052</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="4">
         <v>289</v>
       </c>
       <c r="G120" s="1"/>
@@ -3807,7 +3821,7 @@
       <c r="E121" s="1">
         <v>20052</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="4">
         <v>10</v>
       </c>
       <c r="G121" s="1"/>
@@ -3829,7 +3843,7 @@
       <c r="E122" s="1">
         <v>20052</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="4">
         <v>1</v>
       </c>
       <c r="G122" s="1"/>
@@ -3851,7 +3865,7 @@
       <c r="E123" s="1">
         <v>20062</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="4">
         <v>4000</v>
       </c>
       <c r="G123" s="1"/>
@@ -3873,7 +3887,7 @@
       <c r="E124" s="1">
         <v>20062</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="4">
         <v>4000</v>
       </c>
       <c r="G124" s="1"/>
@@ -3895,7 +3909,7 @@
       <c r="E125" s="1">
         <v>20062</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="4">
         <v>1500</v>
       </c>
       <c r="G125" s="1"/>
@@ -3917,7 +3931,7 @@
       <c r="E126" s="1">
         <v>20062</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="4">
         <v>467</v>
       </c>
       <c r="G126" s="1"/>
@@ -3939,7 +3953,7 @@
       <c r="E127" s="1">
         <v>20062</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="4">
         <v>30</v>
       </c>
       <c r="G127" s="1"/>
@@ -3961,7 +3975,7 @@
       <c r="E128" s="1">
         <v>20062</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="4">
         <v>3</v>
       </c>
       <c r="G128" s="1"/>
@@ -3983,7 +3997,7 @@
       <c r="E129" s="1">
         <v>20062</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="4">
         <v>6000</v>
       </c>
       <c r="G129" s="1"/>
@@ -4005,7 +4019,7 @@
       <c r="E130" s="1">
         <v>20062</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="4">
         <v>3000</v>
       </c>
       <c r="G130" s="1"/>
@@ -4027,7 +4041,7 @@
       <c r="E131" s="1">
         <v>20062</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="4">
         <v>700</v>
       </c>
       <c r="G131" s="1"/>
@@ -4049,7 +4063,7 @@
       <c r="E132" s="1">
         <v>20062</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="4">
         <v>289</v>
       </c>
       <c r="G132" s="1"/>
@@ -4071,7 +4085,7 @@
       <c r="E133" s="1">
         <v>20062</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="4">
         <v>10</v>
       </c>
       <c r="G133" s="1"/>
@@ -4093,7 +4107,7 @@
       <c r="E134" s="1">
         <v>20062</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="4">
         <v>1</v>
       </c>
       <c r="G134" s="1"/>
@@ -4115,7 +4129,7 @@
       <c r="E135" s="1">
         <v>20072</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="4">
         <v>4000</v>
       </c>
       <c r="G135" s="1"/>
@@ -4137,7 +4151,7 @@
       <c r="E136" s="1">
         <v>20072</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="4">
         <v>4000</v>
       </c>
       <c r="G136" s="1"/>
@@ -4159,7 +4173,7 @@
       <c r="E137" s="1">
         <v>20072</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="4">
         <v>1500</v>
       </c>
       <c r="G137" s="1"/>
@@ -4181,7 +4195,7 @@
       <c r="E138" s="1">
         <v>20072</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="4">
         <v>467</v>
       </c>
       <c r="G138" s="1"/>
@@ -4203,7 +4217,7 @@
       <c r="E139" s="1">
         <v>20072</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="4">
         <v>30</v>
       </c>
       <c r="G139" s="1"/>
@@ -4225,7 +4239,7 @@
       <c r="E140" s="1">
         <v>20072</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="4">
         <v>3</v>
       </c>
       <c r="G140" s="1"/>
@@ -4247,7 +4261,7 @@
       <c r="E141" s="1">
         <v>20072</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="4">
         <v>6000</v>
       </c>
       <c r="G141" s="1"/>
@@ -4269,7 +4283,7 @@
       <c r="E142" s="1">
         <v>20072</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="4">
         <v>3000</v>
       </c>
       <c r="G142" s="1"/>
@@ -4291,7 +4305,7 @@
       <c r="E143" s="1">
         <v>20072</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="4">
         <v>700</v>
       </c>
       <c r="G143" s="1"/>
@@ -4313,7 +4327,7 @@
       <c r="E144" s="1">
         <v>20072</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="4">
         <v>289</v>
       </c>
       <c r="G144" s="1"/>
@@ -4335,7 +4349,7 @@
       <c r="E145" s="1">
         <v>20072</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="4">
         <v>10</v>
       </c>
       <c r="G145" s="1"/>
@@ -4357,7 +4371,7 @@
       <c r="E146" s="1">
         <v>20072</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="4">
         <v>1</v>
       </c>
       <c r="G146" s="1"/>
@@ -4379,7 +4393,7 @@
       <c r="E147" s="1">
         <v>20082</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="4">
         <v>4000</v>
       </c>
       <c r="G147" s="1"/>
@@ -4401,7 +4415,7 @@
       <c r="E148" s="1">
         <v>20082</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="4">
         <v>4000</v>
       </c>
       <c r="G148" s="1"/>
@@ -4423,7 +4437,7 @@
       <c r="E149" s="1">
         <v>20082</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="4">
         <v>1500</v>
       </c>
       <c r="G149" s="1"/>
@@ -4445,7 +4459,7 @@
       <c r="E150" s="1">
         <v>20082</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="4">
         <v>467</v>
       </c>
       <c r="G150" s="1"/>
@@ -4467,7 +4481,7 @@
       <c r="E151" s="1">
         <v>20082</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="4">
         <v>30</v>
       </c>
       <c r="G151" s="1"/>
@@ -4489,7 +4503,7 @@
       <c r="E152" s="1">
         <v>20082</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="4">
         <v>3</v>
       </c>
       <c r="G152" s="1"/>
@@ -4511,7 +4525,7 @@
       <c r="E153" s="1">
         <v>20082</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="4">
         <v>6000</v>
       </c>
       <c r="G153" s="1"/>
@@ -4533,7 +4547,7 @@
       <c r="E154" s="1">
         <v>20082</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="4">
         <v>3000</v>
       </c>
       <c r="G154" s="1"/>
@@ -4555,7 +4569,7 @@
       <c r="E155" s="1">
         <v>20082</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="4">
         <v>700</v>
       </c>
       <c r="G155" s="1"/>
@@ -4577,7 +4591,7 @@
       <c r="E156" s="1">
         <v>20082</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="4">
         <v>289</v>
       </c>
       <c r="G156" s="1"/>
@@ -4599,7 +4613,7 @@
       <c r="E157" s="1">
         <v>20082</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="4">
         <v>10</v>
       </c>
       <c r="G157" s="1"/>
@@ -4621,7 +4635,7 @@
       <c r="E158" s="1">
         <v>20082</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="4">
         <v>1</v>
       </c>
       <c r="G158" s="1"/>
@@ -4643,8 +4657,8 @@
       <c r="E159" s="1">
         <v>30013</v>
       </c>
-      <c r="F159" s="1">
-        <v>1550</v>
+      <c r="F159" s="4">
+        <v>1600</v>
       </c>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
@@ -4665,8 +4679,8 @@
       <c r="E160" s="1">
         <v>30013</v>
       </c>
-      <c r="F160" s="1">
-        <v>5000</v>
+      <c r="F160" s="4">
+        <v>4400</v>
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
@@ -4687,8 +4701,8 @@
       <c r="E161" s="1">
         <v>30013</v>
       </c>
-      <c r="F161" s="1">
-        <v>2500</v>
+      <c r="F161" s="4">
+        <v>3000</v>
       </c>
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
@@ -4709,8 +4723,8 @@
       <c r="E162" s="1">
         <v>30013</v>
       </c>
-      <c r="F162" s="1">
-        <v>850</v>
+      <c r="F162" s="4">
+        <v>900</v>
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
@@ -4731,7 +4745,7 @@
       <c r="E163" s="1">
         <v>30013</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="4">
         <v>90</v>
       </c>
       <c r="G163" s="1"/>
@@ -4753,7 +4767,7 @@
       <c r="E164" s="1">
         <v>30013</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="4">
         <v>10</v>
       </c>
       <c r="G164" s="1"/>
@@ -4775,7 +4789,7 @@
       <c r="E165" s="1">
         <v>30013</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="4">
         <v>4000</v>
       </c>
       <c r="G165" s="1"/>
@@ -4797,7 +4811,7 @@
       <c r="E166" s="1">
         <v>30013</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="4">
         <v>4000</v>
       </c>
       <c r="G166" s="1"/>
@@ -4819,7 +4833,7 @@
       <c r="E167" s="1">
         <v>30013</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="4">
         <v>1500</v>
       </c>
       <c r="G167" s="1"/>
@@ -4841,7 +4855,7 @@
       <c r="E168" s="1">
         <v>30013</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="4">
         <v>467</v>
       </c>
       <c r="G168" s="1"/>
@@ -4863,7 +4877,7 @@
       <c r="E169" s="1">
         <v>30013</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="4">
         <v>30</v>
       </c>
       <c r="G169" s="1"/>
@@ -4885,7 +4899,7 @@
       <c r="E170" s="1">
         <v>30013</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="4">
         <v>3</v>
       </c>
       <c r="G170" s="1"/>
@@ -4907,7 +4921,7 @@
       <c r="E171" s="1">
         <v>30013</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="4">
         <v>6000</v>
       </c>
       <c r="G171" s="1"/>
@@ -4929,7 +4943,7 @@
       <c r="E172" s="1">
         <v>30013</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="4">
         <v>3000</v>
       </c>
       <c r="G172" s="1"/>
@@ -4951,7 +4965,7 @@
       <c r="E173" s="1">
         <v>30013</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="4">
         <v>700</v>
       </c>
       <c r="G173" s="1"/>
@@ -4973,7 +4987,7 @@
       <c r="E174" s="1">
         <v>30013</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="4">
         <v>289</v>
       </c>
       <c r="G174" s="1"/>
@@ -4995,7 +5009,7 @@
       <c r="E175" s="1">
         <v>30013</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="4">
         <v>10</v>
       </c>
       <c r="G175" s="1"/>
@@ -5017,7 +5031,7 @@
       <c r="E176" s="1">
         <v>30013</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="4">
         <v>1</v>
       </c>
       <c r="G176" s="1"/>
@@ -5039,8 +5053,8 @@
       <c r="E177" s="1">
         <v>30023</v>
       </c>
-      <c r="F177" s="1">
-        <v>1550</v>
+      <c r="F177" s="4">
+        <v>1600</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
@@ -5061,8 +5075,8 @@
       <c r="E178" s="1">
         <v>30023</v>
       </c>
-      <c r="F178" s="1">
-        <v>5000</v>
+      <c r="F178" s="4">
+        <v>4400</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
@@ -5083,8 +5097,8 @@
       <c r="E179" s="1">
         <v>30023</v>
       </c>
-      <c r="F179" s="1">
-        <v>2500</v>
+      <c r="F179" s="4">
+        <v>3000</v>
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
@@ -5105,8 +5119,8 @@
       <c r="E180" s="1">
         <v>30023</v>
       </c>
-      <c r="F180" s="1">
-        <v>850</v>
+      <c r="F180" s="4">
+        <v>900</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -5127,7 +5141,7 @@
       <c r="E181" s="1">
         <v>30023</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="4">
         <v>90</v>
       </c>
       <c r="G181" s="1"/>
@@ -5149,7 +5163,7 @@
       <c r="E182" s="1">
         <v>30023</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="4">
         <v>10</v>
       </c>
       <c r="G182" s="1"/>
@@ -5171,7 +5185,7 @@
       <c r="E183" s="1">
         <v>30023</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="4">
         <v>4000</v>
       </c>
       <c r="G183" s="1"/>
@@ -5193,7 +5207,7 @@
       <c r="E184" s="1">
         <v>30023</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="4">
         <v>4000</v>
       </c>
       <c r="G184" s="1"/>
@@ -5215,7 +5229,7 @@
       <c r="E185" s="1">
         <v>30023</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="4">
         <v>1500</v>
       </c>
       <c r="G185" s="1"/>
@@ -5237,7 +5251,7 @@
       <c r="E186" s="1">
         <v>30023</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="4">
         <v>467</v>
       </c>
       <c r="G186" s="1"/>
@@ -5259,7 +5273,7 @@
       <c r="E187" s="1">
         <v>30023</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="4">
         <v>30</v>
       </c>
       <c r="G187" s="1"/>
@@ -5281,7 +5295,7 @@
       <c r="E188" s="1">
         <v>30023</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="4">
         <v>3</v>
       </c>
       <c r="G188" s="1"/>
@@ -5303,7 +5317,7 @@
       <c r="E189" s="1">
         <v>30023</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="4">
         <v>6000</v>
       </c>
       <c r="G189" s="1"/>
@@ -5325,7 +5339,7 @@
       <c r="E190" s="1">
         <v>30023</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="4">
         <v>3000</v>
       </c>
       <c r="G190" s="1"/>
@@ -5347,7 +5361,7 @@
       <c r="E191" s="1">
         <v>30023</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="4">
         <v>700</v>
       </c>
       <c r="G191" s="1"/>
@@ -5369,7 +5383,7 @@
       <c r="E192" s="1">
         <v>30023</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="4">
         <v>289</v>
       </c>
       <c r="G192" s="1"/>
@@ -5391,7 +5405,7 @@
       <c r="E193" s="1">
         <v>30023</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="4">
         <v>10</v>
       </c>
       <c r="G193" s="1"/>
@@ -5413,7 +5427,7 @@
       <c r="E194" s="1">
         <v>30023</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="4">
         <v>1</v>
       </c>
       <c r="G194" s="1"/>
@@ -5423,7 +5437,7 @@
       <c r="A195" s="1">
         <v>193</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C195" s="1" t="s">
@@ -5435,7 +5449,7 @@
       <c r="E195" s="1">
         <v>30033</v>
       </c>
-      <c r="F195" s="5">
+      <c r="F195" s="4">
         <v>0</v>
       </c>
       <c r="G195" s="1"/>
@@ -5445,7 +5459,7 @@
       <c r="A196" s="1">
         <v>194</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C196" s="1" t="s">
@@ -5457,8 +5471,8 @@
       <c r="E196" s="1">
         <v>30033</v>
       </c>
-      <c r="F196" s="1">
-        <v>5917</v>
+      <c r="F196" s="4">
+        <v>5238</v>
       </c>
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
@@ -5467,7 +5481,7 @@
       <c r="A197" s="1">
         <v>195</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C197" s="1" t="s">
@@ -5479,8 +5493,8 @@
       <c r="E197" s="1">
         <v>30033</v>
       </c>
-      <c r="F197" s="1">
-        <v>2934</v>
+      <c r="F197" s="4">
+        <v>3571</v>
       </c>
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
@@ -5489,7 +5503,7 @@
       <c r="A198" s="1">
         <v>196</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C198" s="1" t="s">
@@ -5501,8 +5515,8 @@
       <c r="E198" s="1">
         <v>30033</v>
       </c>
-      <c r="F198" s="1">
-        <v>1006</v>
+      <c r="F198" s="4">
+        <v>1071</v>
       </c>
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
@@ -5511,7 +5525,7 @@
       <c r="A199" s="1">
         <v>197</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C199" s="1" t="s">
@@ -5523,7 +5537,7 @@
       <c r="E199" s="1">
         <v>30033</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="4">
         <v>107</v>
       </c>
       <c r="G199" s="1"/>
@@ -5533,7 +5547,7 @@
       <c r="A200" s="1">
         <v>198</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C200" s="1" t="s">
@@ -5545,8 +5559,8 @@
       <c r="E200" s="1">
         <v>30033</v>
       </c>
-      <c r="F200" s="1">
-        <v>36</v>
+      <c r="F200" s="4">
+        <v>12</v>
       </c>
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
@@ -5555,7 +5569,7 @@
       <c r="A201" s="1">
         <v>199</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C201" s="1" t="s">
@@ -5567,7 +5581,7 @@
       <c r="E201" s="1">
         <v>30033</v>
       </c>
-      <c r="F201" s="5">
+      <c r="F201" s="4">
         <v>0</v>
       </c>
       <c r="G201" s="1"/>
@@ -5577,7 +5591,7 @@
       <c r="A202" s="1">
         <v>200</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C202" s="1" t="s">
@@ -5589,7 +5603,7 @@
       <c r="E202" s="1">
         <v>30033</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="4">
         <v>6667</v>
       </c>
       <c r="G202" s="1"/>
@@ -5599,7 +5613,7 @@
       <c r="A203" s="1">
         <v>201</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C203" s="1" t="s">
@@ -5611,8 +5625,8 @@
       <c r="E203" s="1">
         <v>30033</v>
       </c>
-      <c r="F203" s="1">
-        <v>2489</v>
+      <c r="F203" s="4">
+        <v>2500</v>
       </c>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
@@ -5621,7 +5635,7 @@
       <c r="A204" s="1">
         <v>202</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C204" s="1" t="s">
@@ -5633,7 +5647,7 @@
       <c r="E204" s="1">
         <v>30033</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="4">
         <v>778</v>
       </c>
       <c r="G204" s="1"/>
@@ -5643,7 +5657,7 @@
       <c r="A205" s="1">
         <v>203</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C205" s="1" t="s">
@@ -5655,7 +5669,7 @@
       <c r="E205" s="1">
         <v>30033</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="4">
         <v>50</v>
       </c>
       <c r="G205" s="1"/>
@@ -5665,7 +5679,7 @@
       <c r="A206" s="1">
         <v>204</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C206" s="1" t="s">
@@ -5677,8 +5691,8 @@
       <c r="E206" s="1">
         <v>30033</v>
       </c>
-      <c r="F206" s="1">
-        <v>16</v>
+      <c r="F206" s="4">
+        <v>5</v>
       </c>
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
@@ -5687,7 +5701,7 @@
       <c r="A207" s="1">
         <v>205</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C207" s="1" t="s">
@@ -5699,7 +5713,7 @@
       <c r="E207" s="1">
         <v>30033</v>
       </c>
-      <c r="F207" s="5">
+      <c r="F207" s="4">
         <v>0</v>
       </c>
       <c r="G207" s="1"/>
@@ -5709,7 +5723,7 @@
       <c r="A208" s="1">
         <v>206</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C208" s="1" t="s">
@@ -5721,7 +5735,7 @@
       <c r="E208" s="1">
         <v>30033</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="4">
         <v>7500</v>
       </c>
       <c r="G208" s="1"/>
@@ -5731,7 +5745,7 @@
       <c r="A209" s="1">
         <v>207</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C209" s="1" t="s">
@@ -5743,8 +5757,8 @@
       <c r="E209" s="1">
         <v>30033</v>
       </c>
-      <c r="F209" s="1">
-        <v>1740</v>
+      <c r="F209" s="4">
+        <v>1750</v>
       </c>
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
@@ -5753,7 +5767,7 @@
       <c r="A210" s="1">
         <v>208</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C210" s="1" t="s">
@@ -5765,7 +5779,7 @@
       <c r="E210" s="1">
         <v>30033</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="4">
         <v>723</v>
       </c>
       <c r="G210" s="1"/>
@@ -5775,7 +5789,7 @@
       <c r="A211" s="1">
         <v>209</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C211" s="1" t="s">
@@ -5787,7 +5801,7 @@
       <c r="E211" s="1">
         <v>30033</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="4">
         <v>25</v>
       </c>
       <c r="G211" s="1"/>
@@ -5797,7 +5811,7 @@
       <c r="A212" s="1">
         <v>210</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C212" s="1" t="s">
@@ -5809,8 +5823,8 @@
       <c r="E212" s="1">
         <v>30033</v>
       </c>
-      <c r="F212" s="1">
-        <v>12</v>
+      <c r="F212" s="4">
+        <v>3</v>
       </c>
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
@@ -5831,8 +5845,8 @@
       <c r="E213" s="1">
         <v>30043</v>
       </c>
-      <c r="F213" s="1">
-        <v>1550</v>
+      <c r="F213" s="4">
+        <v>1600</v>
       </c>
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
@@ -5853,8 +5867,8 @@
       <c r="E214" s="1">
         <v>30043</v>
       </c>
-      <c r="F214" s="1">
-        <v>5000</v>
+      <c r="F214" s="4">
+        <v>4400</v>
       </c>
       <c r="G214" s="1"/>
       <c r="H214" s="1"/>
@@ -5875,8 +5889,8 @@
       <c r="E215" s="1">
         <v>30043</v>
       </c>
-      <c r="F215" s="1">
-        <v>2500</v>
+      <c r="F215" s="4">
+        <v>3000</v>
       </c>
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
@@ -5897,8 +5911,8 @@
       <c r="E216" s="1">
         <v>30043</v>
       </c>
-      <c r="F216" s="1">
-        <v>850</v>
+      <c r="F216" s="4">
+        <v>900</v>
       </c>
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
@@ -5919,7 +5933,7 @@
       <c r="E217" s="1">
         <v>30043</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="4">
         <v>90</v>
       </c>
       <c r="G217" s="1"/>
@@ -5941,7 +5955,7 @@
       <c r="E218" s="1">
         <v>30043</v>
       </c>
-      <c r="F218" s="1">
+      <c r="F218" s="4">
         <v>10</v>
       </c>
       <c r="G218" s="1"/>
@@ -5963,7 +5977,7 @@
       <c r="E219" s="1">
         <v>30043</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="4">
         <v>4000</v>
       </c>
       <c r="G219" s="1"/>
@@ -5985,7 +5999,7 @@
       <c r="E220" s="1">
         <v>30043</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="4">
         <v>4000</v>
       </c>
       <c r="G220" s="1"/>
@@ -6007,7 +6021,7 @@
       <c r="E221" s="1">
         <v>30043</v>
       </c>
-      <c r="F221" s="1">
+      <c r="F221" s="4">
         <v>1500</v>
       </c>
       <c r="G221" s="1"/>
@@ -6029,7 +6043,7 @@
       <c r="E222" s="1">
         <v>30043</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F222" s="4">
         <v>467</v>
       </c>
       <c r="G222" s="1"/>
@@ -6051,7 +6065,7 @@
       <c r="E223" s="1">
         <v>30043</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="4">
         <v>30</v>
       </c>
       <c r="G223" s="1"/>
@@ -6073,7 +6087,7 @@
       <c r="E224" s="1">
         <v>30043</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="4">
         <v>3</v>
       </c>
       <c r="G224" s="1"/>
@@ -6095,7 +6109,7 @@
       <c r="E225" s="1">
         <v>30043</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F225" s="4">
         <v>6000</v>
       </c>
       <c r="G225" s="1"/>
@@ -6117,7 +6131,7 @@
       <c r="E226" s="1">
         <v>30043</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="4">
         <v>3000</v>
       </c>
       <c r="G226" s="1"/>
@@ -6139,7 +6153,7 @@
       <c r="E227" s="1">
         <v>30043</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F227" s="4">
         <v>700</v>
       </c>
       <c r="G227" s="1"/>
@@ -6161,7 +6175,7 @@
       <c r="E228" s="1">
         <v>30043</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="4">
         <v>289</v>
       </c>
       <c r="G228" s="1"/>
@@ -6183,7 +6197,7 @@
       <c r="E229" s="1">
         <v>30043</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F229" s="4">
         <v>10</v>
       </c>
       <c r="G229" s="1"/>
@@ -6205,7 +6219,7 @@
       <c r="E230" s="1">
         <v>30043</v>
       </c>
-      <c r="F230" s="1">
+      <c r="F230" s="4">
         <v>1</v>
       </c>
       <c r="G230" s="1"/>
@@ -6227,8 +6241,8 @@
       <c r="E231" s="1">
         <v>30053</v>
       </c>
-      <c r="F231" s="1">
-        <v>1550</v>
+      <c r="F231" s="4">
+        <v>1600</v>
       </c>
       <c r="G231" s="1"/>
       <c r="H231" s="1"/>
@@ -6249,8 +6263,8 @@
       <c r="E232" s="1">
         <v>30053</v>
       </c>
-      <c r="F232" s="1">
-        <v>5000</v>
+      <c r="F232" s="4">
+        <v>4400</v>
       </c>
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
@@ -6271,8 +6285,8 @@
       <c r="E233" s="1">
         <v>30053</v>
       </c>
-      <c r="F233" s="1">
-        <v>2500</v>
+      <c r="F233" s="4">
+        <v>3000</v>
       </c>
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
@@ -6293,8 +6307,8 @@
       <c r="E234" s="1">
         <v>30053</v>
       </c>
-      <c r="F234" s="1">
-        <v>850</v>
+      <c r="F234" s="4">
+        <v>900</v>
       </c>
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
@@ -6315,7 +6329,7 @@
       <c r="E235" s="1">
         <v>30053</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F235" s="4">
         <v>90</v>
       </c>
       <c r="G235" s="1"/>
@@ -6337,7 +6351,7 @@
       <c r="E236" s="1">
         <v>30053</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F236" s="4">
         <v>10</v>
       </c>
       <c r="G236" s="1"/>
@@ -6359,7 +6373,7 @@
       <c r="E237" s="1">
         <v>30053</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F237" s="4">
         <v>4000</v>
       </c>
       <c r="G237" s="1"/>
@@ -6381,7 +6395,7 @@
       <c r="E238" s="1">
         <v>30053</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F238" s="4">
         <v>4000</v>
       </c>
       <c r="G238" s="1"/>
@@ -6403,7 +6417,7 @@
       <c r="E239" s="1">
         <v>30053</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F239" s="4">
         <v>1500</v>
       </c>
       <c r="G239" s="1"/>
@@ -6425,7 +6439,7 @@
       <c r="E240" s="1">
         <v>30053</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F240" s="4">
         <v>467</v>
       </c>
       <c r="G240" s="1"/>
@@ -6447,7 +6461,7 @@
       <c r="E241" s="1">
         <v>30053</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F241" s="4">
         <v>30</v>
       </c>
       <c r="G241" s="1"/>
@@ -6469,7 +6483,7 @@
       <c r="E242" s="1">
         <v>30053</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F242" s="4">
         <v>3</v>
       </c>
       <c r="G242" s="1"/>
@@ -6491,7 +6505,7 @@
       <c r="E243" s="1">
         <v>30053</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F243" s="4">
         <v>6000</v>
       </c>
       <c r="G243" s="1"/>
@@ -6513,7 +6527,7 @@
       <c r="E244" s="1">
         <v>30053</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F244" s="4">
         <v>3000</v>
       </c>
       <c r="G244" s="1"/>
@@ -6535,7 +6549,7 @@
       <c r="E245" s="1">
         <v>30053</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F245" s="4">
         <v>700</v>
       </c>
       <c r="G245" s="1"/>
@@ -6557,7 +6571,7 @@
       <c r="E246" s="1">
         <v>30053</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F246" s="4">
         <v>289</v>
       </c>
       <c r="G246" s="1"/>
@@ -6579,7 +6593,7 @@
       <c r="E247" s="1">
         <v>30053</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F247" s="4">
         <v>10</v>
       </c>
       <c r="G247" s="1"/>
@@ -6601,7 +6615,7 @@
       <c r="E248" s="1">
         <v>30053</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F248" s="4">
         <v>1</v>
       </c>
       <c r="G248" s="1"/>
@@ -6623,8 +6637,8 @@
       <c r="E249" s="1">
         <v>30063</v>
       </c>
-      <c r="F249" s="1">
-        <v>1550</v>
+      <c r="F249" s="4">
+        <v>1600</v>
       </c>
       <c r="G249" s="1"/>
       <c r="H249" s="1"/>
@@ -6645,8 +6659,8 @@
       <c r="E250" s="1">
         <v>30063</v>
       </c>
-      <c r="F250" s="1">
-        <v>5000</v>
+      <c r="F250" s="4">
+        <v>4400</v>
       </c>
       <c r="G250" s="1"/>
       <c r="H250" s="1"/>
@@ -6667,8 +6681,8 @@
       <c r="E251" s="1">
         <v>30063</v>
       </c>
-      <c r="F251" s="1">
-        <v>2500</v>
+      <c r="F251" s="4">
+        <v>3000</v>
       </c>
       <c r="G251" s="1"/>
       <c r="H251" s="1"/>
@@ -6689,8 +6703,8 @@
       <c r="E252" s="1">
         <v>30063</v>
       </c>
-      <c r="F252" s="1">
-        <v>850</v>
+      <c r="F252" s="4">
+        <v>900</v>
       </c>
       <c r="G252" s="1"/>
       <c r="H252" s="1"/>
@@ -6711,7 +6725,7 @@
       <c r="E253" s="1">
         <v>30063</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="4">
         <v>90</v>
       </c>
       <c r="G253" s="1"/>
@@ -6733,7 +6747,7 @@
       <c r="E254" s="1">
         <v>30063</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F254" s="4">
         <v>10</v>
       </c>
       <c r="G254" s="1"/>
@@ -6755,7 +6769,7 @@
       <c r="E255" s="1">
         <v>30063</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F255" s="4">
         <v>4000</v>
       </c>
       <c r="G255" s="1"/>
@@ -6777,7 +6791,7 @@
       <c r="E256" s="1">
         <v>30063</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F256" s="4">
         <v>4000</v>
       </c>
       <c r="G256" s="1"/>
@@ -6799,7 +6813,7 @@
       <c r="E257" s="1">
         <v>30063</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F257" s="4">
         <v>1500</v>
       </c>
       <c r="G257" s="1"/>
@@ -6821,7 +6835,7 @@
       <c r="E258" s="1">
         <v>30063</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F258" s="4">
         <v>467</v>
       </c>
       <c r="G258" s="1"/>
@@ -6843,7 +6857,7 @@
       <c r="E259" s="1">
         <v>30063</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F259" s="4">
         <v>30</v>
       </c>
       <c r="G259" s="1"/>
@@ -6865,7 +6879,7 @@
       <c r="E260" s="1">
         <v>30063</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F260" s="4">
         <v>3</v>
       </c>
       <c r="G260" s="1"/>
@@ -6887,7 +6901,7 @@
       <c r="E261" s="1">
         <v>30063</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F261" s="4">
         <v>6000</v>
       </c>
       <c r="G261" s="1"/>
@@ -6909,7 +6923,7 @@
       <c r="E262" s="1">
         <v>30063</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F262" s="4">
         <v>3000</v>
       </c>
       <c r="G262" s="1"/>
@@ -6931,7 +6945,7 @@
       <c r="E263" s="1">
         <v>30063</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F263" s="4">
         <v>700</v>
       </c>
       <c r="G263" s="1"/>
@@ -6953,7 +6967,7 @@
       <c r="E264" s="1">
         <v>30063</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F264" s="4">
         <v>289</v>
       </c>
       <c r="G264" s="1"/>
@@ -6975,7 +6989,7 @@
       <c r="E265" s="1">
         <v>30063</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F265" s="4">
         <v>10</v>
       </c>
       <c r="G265" s="1"/>
@@ -6997,7 +7011,7 @@
       <c r="E266" s="1">
         <v>30063</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F266" s="4">
         <v>1</v>
       </c>
       <c r="G266" s="1"/>
@@ -7019,8 +7033,8 @@
       <c r="E267" s="1">
         <v>40014</v>
       </c>
-      <c r="F267" s="1">
-        <v>900</v>
+      <c r="F267" s="4">
+        <v>0</v>
       </c>
       <c r="G267" s="1"/>
       <c r="H267" s="1"/>
@@ -7041,8 +7055,8 @@
       <c r="E268" s="1">
         <v>40014</v>
       </c>
-      <c r="F268" s="1">
-        <v>3500</v>
+      <c r="F268" s="4">
+        <v>4000</v>
       </c>
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
@@ -7063,8 +7077,8 @@
       <c r="E269" s="1">
         <v>40014</v>
       </c>
-      <c r="F269" s="1">
-        <v>3500</v>
+      <c r="F269" s="4">
+        <v>4000</v>
       </c>
       <c r="G269" s="1"/>
       <c r="H269" s="1"/>
@@ -7085,8 +7099,8 @@
       <c r="E270" s="1">
         <v>40014</v>
       </c>
-      <c r="F270" s="1">
-        <v>1870</v>
+      <c r="F270" s="4">
+        <v>1470</v>
       </c>
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
@@ -7107,8 +7121,8 @@
       <c r="E271" s="1">
         <v>40014</v>
       </c>
-      <c r="F271" s="1">
-        <v>200</v>
+      <c r="F271" s="4">
+        <v>500</v>
       </c>
       <c r="G271" s="1"/>
       <c r="H271" s="1"/>
@@ -7129,7 +7143,7 @@
       <c r="E272" s="1">
         <v>40014</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F272" s="4">
         <v>30</v>
       </c>
       <c r="G272" s="1"/>
@@ -7151,8 +7165,8 @@
       <c r="E273" s="1">
         <v>40014</v>
       </c>
-      <c r="F273" s="1">
-        <v>1550</v>
+      <c r="F273" s="4">
+        <v>1600</v>
       </c>
       <c r="G273" s="1"/>
       <c r="H273" s="1"/>
@@ -7173,8 +7187,8 @@
       <c r="E274" s="1">
         <v>40014</v>
       </c>
-      <c r="F274" s="1">
-        <v>5000</v>
+      <c r="F274" s="4">
+        <v>4400</v>
       </c>
       <c r="G274" s="1"/>
       <c r="H274" s="1"/>
@@ -7195,8 +7209,8 @@
       <c r="E275" s="1">
         <v>40014</v>
       </c>
-      <c r="F275" s="1">
-        <v>2500</v>
+      <c r="F275" s="4">
+        <v>3000</v>
       </c>
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
@@ -7217,8 +7231,8 @@
       <c r="E276" s="1">
         <v>40014</v>
       </c>
-      <c r="F276" s="1">
-        <v>850</v>
+      <c r="F276" s="4">
+        <v>900</v>
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="1"/>
@@ -7239,7 +7253,7 @@
       <c r="E277" s="1">
         <v>40014</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F277" s="4">
         <v>90</v>
       </c>
       <c r="G277" s="1"/>
@@ -7261,7 +7275,7 @@
       <c r="E278" s="1">
         <v>40014</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F278" s="4">
         <v>10</v>
       </c>
       <c r="G278" s="1"/>
@@ -7283,7 +7297,7 @@
       <c r="E279" s="1">
         <v>40014</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F279" s="4">
         <v>4000</v>
       </c>
       <c r="G279" s="1"/>
@@ -7305,7 +7319,7 @@
       <c r="E280" s="1">
         <v>40014</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F280" s="4">
         <v>4000</v>
       </c>
       <c r="G280" s="1"/>
@@ -7327,7 +7341,7 @@
       <c r="E281" s="1">
         <v>40014</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F281" s="4">
         <v>1500</v>
       </c>
       <c r="G281" s="1"/>
@@ -7349,7 +7363,7 @@
       <c r="E282" s="1">
         <v>40014</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F282" s="4">
         <v>467</v>
       </c>
       <c r="G282" s="1"/>
@@ -7371,7 +7385,7 @@
       <c r="E283" s="1">
         <v>40014</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F283" s="4">
         <v>30</v>
       </c>
       <c r="G283" s="1"/>
@@ -7393,7 +7407,7 @@
       <c r="E284" s="1">
         <v>40014</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F284" s="4">
         <v>3</v>
       </c>
       <c r="G284" s="1"/>
@@ -7415,8 +7429,8 @@
       <c r="E285" s="1">
         <v>40024</v>
       </c>
-      <c r="F285" s="1">
-        <v>900</v>
+      <c r="F285" s="4">
+        <v>0</v>
       </c>
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
@@ -7437,8 +7451,8 @@
       <c r="E286" s="1">
         <v>40024</v>
       </c>
-      <c r="F286" s="1">
-        <v>3500</v>
+      <c r="F286" s="4">
+        <v>4000</v>
       </c>
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
@@ -7459,8 +7473,8 @@
       <c r="E287" s="1">
         <v>40024</v>
       </c>
-      <c r="F287" s="1">
-        <v>3500</v>
+      <c r="F287" s="4">
+        <v>4000</v>
       </c>
       <c r="G287" s="1"/>
       <c r="H287" s="1"/>
@@ -7481,8 +7495,8 @@
       <c r="E288" s="1">
         <v>40024</v>
       </c>
-      <c r="F288" s="1">
-        <v>1870</v>
+      <c r="F288" s="4">
+        <v>1470</v>
       </c>
       <c r="G288" s="1"/>
       <c r="H288" s="1"/>
@@ -7503,8 +7517,8 @@
       <c r="E289" s="1">
         <v>40024</v>
       </c>
-      <c r="F289" s="1">
-        <v>200</v>
+      <c r="F289" s="4">
+        <v>500</v>
       </c>
       <c r="G289" s="1"/>
       <c r="H289" s="1"/>
@@ -7525,7 +7539,7 @@
       <c r="E290" s="1">
         <v>40024</v>
       </c>
-      <c r="F290" s="1">
+      <c r="F290" s="4">
         <v>30</v>
       </c>
       <c r="G290" s="1"/>
@@ -7547,8 +7561,8 @@
       <c r="E291" s="1">
         <v>40024</v>
       </c>
-      <c r="F291" s="1">
-        <v>1550</v>
+      <c r="F291" s="4">
+        <v>1600</v>
       </c>
       <c r="G291" s="1"/>
       <c r="H291" s="1"/>
@@ -7569,8 +7583,8 @@
       <c r="E292" s="1">
         <v>40024</v>
       </c>
-      <c r="F292" s="1">
-        <v>5000</v>
+      <c r="F292" s="4">
+        <v>4400</v>
       </c>
       <c r="G292" s="1"/>
       <c r="H292" s="1"/>
@@ -7591,8 +7605,8 @@
       <c r="E293" s="1">
         <v>40024</v>
       </c>
-      <c r="F293" s="1">
-        <v>2500</v>
+      <c r="F293" s="4">
+        <v>3000</v>
       </c>
       <c r="G293" s="1"/>
       <c r="H293" s="1"/>
@@ -7613,8 +7627,8 @@
       <c r="E294" s="1">
         <v>40024</v>
       </c>
-      <c r="F294" s="1">
-        <v>850</v>
+      <c r="F294" s="4">
+        <v>900</v>
       </c>
       <c r="G294" s="1"/>
       <c r="H294" s="1"/>
@@ -7635,7 +7649,7 @@
       <c r="E295" s="1">
         <v>40024</v>
       </c>
-      <c r="F295" s="1">
+      <c r="F295" s="4">
         <v>90</v>
       </c>
       <c r="G295" s="1"/>
@@ -7657,7 +7671,7 @@
       <c r="E296" s="1">
         <v>40024</v>
       </c>
-      <c r="F296" s="1">
+      <c r="F296" s="4">
         <v>10</v>
       </c>
       <c r="G296" s="1"/>
@@ -7679,7 +7693,7 @@
       <c r="E297" s="1">
         <v>40024</v>
       </c>
-      <c r="F297" s="1">
+      <c r="F297" s="4">
         <v>4000</v>
       </c>
       <c r="G297" s="1"/>
@@ -7701,7 +7715,7 @@
       <c r="E298" s="1">
         <v>40024</v>
       </c>
-      <c r="F298" s="1">
+      <c r="F298" s="4">
         <v>4000</v>
       </c>
       <c r="G298" s="1"/>
@@ -7723,7 +7737,7 @@
       <c r="E299" s="1">
         <v>40024</v>
       </c>
-      <c r="F299" s="1">
+      <c r="F299" s="4">
         <v>1500</v>
       </c>
       <c r="G299" s="1"/>
@@ -7745,7 +7759,7 @@
       <c r="E300" s="1">
         <v>40024</v>
       </c>
-      <c r="F300" s="1">
+      <c r="F300" s="4">
         <v>467</v>
       </c>
       <c r="G300" s="1"/>
@@ -7767,7 +7781,7 @@
       <c r="E301" s="1">
         <v>40024</v>
       </c>
-      <c r="F301" s="1">
+      <c r="F301" s="4">
         <v>30</v>
       </c>
       <c r="G301" s="1"/>
@@ -7789,7 +7803,7 @@
       <c r="E302" s="1">
         <v>40024</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F302" s="4">
         <v>3</v>
       </c>
       <c r="G302" s="1"/>
@@ -7811,8 +7825,8 @@
       <c r="E303" s="1">
         <v>40034</v>
       </c>
-      <c r="F303" s="1">
-        <v>900</v>
+      <c r="F303" s="4">
+        <v>0</v>
       </c>
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
@@ -7833,8 +7847,8 @@
       <c r="E304" s="1">
         <v>40034</v>
       </c>
-      <c r="F304" s="1">
-        <v>3500</v>
+      <c r="F304" s="4">
+        <v>4000</v>
       </c>
       <c r="G304" s="1"/>
       <c r="H304" s="1"/>
@@ -7855,8 +7869,8 @@
       <c r="E305" s="1">
         <v>40034</v>
       </c>
-      <c r="F305" s="1">
-        <v>3500</v>
+      <c r="F305" s="4">
+        <v>4000</v>
       </c>
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
@@ -7877,8 +7891,8 @@
       <c r="E306" s="1">
         <v>40034</v>
       </c>
-      <c r="F306" s="1">
-        <v>1870</v>
+      <c r="F306" s="4">
+        <v>1470</v>
       </c>
       <c r="G306" s="1"/>
       <c r="H306" s="1"/>
@@ -7899,8 +7913,8 @@
       <c r="E307" s="1">
         <v>40034</v>
       </c>
-      <c r="F307" s="1">
-        <v>200</v>
+      <c r="F307" s="4">
+        <v>500</v>
       </c>
       <c r="G307" s="1"/>
       <c r="H307" s="1"/>
@@ -7921,7 +7935,7 @@
       <c r="E308" s="1">
         <v>40034</v>
       </c>
-      <c r="F308" s="1">
+      <c r="F308" s="4">
         <v>30</v>
       </c>
       <c r="G308" s="1"/>
@@ -7943,8 +7957,8 @@
       <c r="E309" s="1">
         <v>40034</v>
       </c>
-      <c r="F309" s="1">
-        <v>1550</v>
+      <c r="F309" s="4">
+        <v>1600</v>
       </c>
       <c r="G309" s="1"/>
       <c r="H309" s="1"/>
@@ -7965,8 +7979,8 @@
       <c r="E310" s="1">
         <v>40034</v>
       </c>
-      <c r="F310" s="1">
-        <v>5000</v>
+      <c r="F310" s="4">
+        <v>4400</v>
       </c>
       <c r="G310" s="1"/>
       <c r="H310" s="1"/>
@@ -7987,8 +8001,8 @@
       <c r="E311" s="1">
         <v>40034</v>
       </c>
-      <c r="F311" s="1">
-        <v>2500</v>
+      <c r="F311" s="4">
+        <v>3000</v>
       </c>
       <c r="G311" s="1"/>
       <c r="H311" s="1"/>
@@ -8009,8 +8023,8 @@
       <c r="E312" s="1">
         <v>40034</v>
       </c>
-      <c r="F312" s="1">
-        <v>850</v>
+      <c r="F312" s="4">
+        <v>900</v>
       </c>
       <c r="G312" s="1"/>
       <c r="H312" s="1"/>
@@ -8031,7 +8045,7 @@
       <c r="E313" s="1">
         <v>40034</v>
       </c>
-      <c r="F313" s="1">
+      <c r="F313" s="4">
         <v>90</v>
       </c>
       <c r="G313" s="1"/>
@@ -8053,7 +8067,7 @@
       <c r="E314" s="1">
         <v>40034</v>
       </c>
-      <c r="F314" s="1">
+      <c r="F314" s="4">
         <v>10</v>
       </c>
       <c r="G314" s="1"/>
@@ -8075,7 +8089,7 @@
       <c r="E315" s="1">
         <v>40034</v>
       </c>
-      <c r="F315" s="1">
+      <c r="F315" s="4">
         <v>4000</v>
       </c>
       <c r="G315" s="1"/>
@@ -8097,7 +8111,7 @@
       <c r="E316" s="1">
         <v>40034</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="4">
         <v>4000</v>
       </c>
       <c r="G316" s="1"/>
@@ -8119,7 +8133,7 @@
       <c r="E317" s="1">
         <v>40034</v>
       </c>
-      <c r="F317" s="1">
+      <c r="F317" s="4">
         <v>1500</v>
       </c>
       <c r="G317" s="1"/>
@@ -8141,7 +8155,7 @@
       <c r="E318" s="1">
         <v>40034</v>
       </c>
-      <c r="F318" s="1">
+      <c r="F318" s="4">
         <v>467</v>
       </c>
       <c r="G318" s="1"/>
@@ -8163,7 +8177,7 @@
       <c r="E319" s="1">
         <v>40034</v>
       </c>
-      <c r="F319" s="1">
+      <c r="F319" s="4">
         <v>30</v>
       </c>
       <c r="G319" s="1"/>
@@ -8185,7 +8199,7 @@
       <c r="E320" s="1">
         <v>40034</v>
       </c>
-      <c r="F320" s="1">
+      <c r="F320" s="4">
         <v>3</v>
       </c>
       <c r="G320" s="1"/>
@@ -8207,8 +8221,8 @@
       <c r="E321" s="1">
         <v>40044</v>
       </c>
-      <c r="F321" s="1">
-        <v>900</v>
+      <c r="F321" s="4">
+        <v>0</v>
       </c>
       <c r="G321" s="1"/>
       <c r="H321" s="1"/>
@@ -8229,8 +8243,8 @@
       <c r="E322" s="1">
         <v>40044</v>
       </c>
-      <c r="F322" s="1">
-        <v>3500</v>
+      <c r="F322" s="4">
+        <v>4000</v>
       </c>
       <c r="G322" s="1"/>
       <c r="H322" s="1"/>
@@ -8251,8 +8265,8 @@
       <c r="E323" s="1">
         <v>40044</v>
       </c>
-      <c r="F323" s="1">
-        <v>3500</v>
+      <c r="F323" s="4">
+        <v>4000</v>
       </c>
       <c r="G323" s="1"/>
       <c r="H323" s="1"/>
@@ -8273,8 +8287,8 @@
       <c r="E324" s="1">
         <v>40044</v>
       </c>
-      <c r="F324" s="1">
-        <v>1870</v>
+      <c r="F324" s="4">
+        <v>1470</v>
       </c>
       <c r="G324" s="1"/>
       <c r="H324" s="1"/>
@@ -8295,8 +8309,8 @@
       <c r="E325" s="1">
         <v>40044</v>
       </c>
-      <c r="F325" s="1">
-        <v>200</v>
+      <c r="F325" s="4">
+        <v>500</v>
       </c>
       <c r="G325" s="1"/>
       <c r="H325" s="1"/>
@@ -8317,7 +8331,7 @@
       <c r="E326" s="1">
         <v>40044</v>
       </c>
-      <c r="F326" s="1">
+      <c r="F326" s="4">
         <v>30</v>
       </c>
       <c r="G326" s="1"/>
@@ -8339,8 +8353,8 @@
       <c r="E327" s="1">
         <v>40044</v>
       </c>
-      <c r="F327" s="1">
-        <v>1550</v>
+      <c r="F327" s="4">
+        <v>1600</v>
       </c>
       <c r="G327" s="1"/>
       <c r="H327" s="1"/>
@@ -8361,8 +8375,8 @@
       <c r="E328" s="1">
         <v>40044</v>
       </c>
-      <c r="F328" s="1">
-        <v>5000</v>
+      <c r="F328" s="4">
+        <v>4400</v>
       </c>
       <c r="G328" s="1"/>
       <c r="H328" s="1"/>
@@ -8383,8 +8397,8 @@
       <c r="E329" s="1">
         <v>40044</v>
       </c>
-      <c r="F329" s="1">
-        <v>2500</v>
+      <c r="F329" s="4">
+        <v>3000</v>
       </c>
       <c r="G329" s="1"/>
       <c r="H329" s="1"/>
@@ -8405,8 +8419,8 @@
       <c r="E330" s="1">
         <v>40044</v>
       </c>
-      <c r="F330" s="1">
-        <v>850</v>
+      <c r="F330" s="4">
+        <v>900</v>
       </c>
       <c r="G330" s="1"/>
       <c r="H330" s="1"/>
@@ -8427,7 +8441,7 @@
       <c r="E331" s="1">
         <v>40044</v>
       </c>
-      <c r="F331" s="1">
+      <c r="F331" s="4">
         <v>90</v>
       </c>
       <c r="G331" s="1"/>
@@ -8449,7 +8463,7 @@
       <c r="E332" s="1">
         <v>40044</v>
       </c>
-      <c r="F332" s="1">
+      <c r="F332" s="4">
         <v>10</v>
       </c>
       <c r="G332" s="1"/>
@@ -8471,7 +8485,7 @@
       <c r="E333" s="1">
         <v>40044</v>
       </c>
-      <c r="F333" s="1">
+      <c r="F333" s="4">
         <v>4000</v>
       </c>
       <c r="G333" s="1"/>
@@ -8493,7 +8507,7 @@
       <c r="E334" s="1">
         <v>40044</v>
       </c>
-      <c r="F334" s="1">
+      <c r="F334" s="4">
         <v>4000</v>
       </c>
       <c r="G334" s="1"/>
@@ -8515,7 +8529,7 @@
       <c r="E335" s="1">
         <v>40044</v>
       </c>
-      <c r="F335" s="1">
+      <c r="F335" s="4">
         <v>1500</v>
       </c>
       <c r="G335" s="1"/>
@@ -8537,7 +8551,7 @@
       <c r="E336" s="1">
         <v>40044</v>
       </c>
-      <c r="F336" s="1">
+      <c r="F336" s="4">
         <v>467</v>
       </c>
       <c r="G336" s="1"/>
@@ -8559,7 +8573,7 @@
       <c r="E337" s="1">
         <v>40044</v>
       </c>
-      <c r="F337" s="1">
+      <c r="F337" s="4">
         <v>30</v>
       </c>
       <c r="G337" s="1"/>
@@ -8581,7 +8595,7 @@
       <c r="E338" s="1">
         <v>40044</v>
       </c>
-      <c r="F338" s="1">
+      <c r="F338" s="4">
         <v>3</v>
       </c>
       <c r="G338" s="1"/>
@@ -8603,8 +8617,8 @@
       <c r="E339" s="1">
         <v>40054</v>
       </c>
-      <c r="F339" s="1">
-        <v>900</v>
+      <c r="F339" s="4">
+        <v>0</v>
       </c>
       <c r="G339" s="1"/>
       <c r="H339" s="1"/>
@@ -8625,8 +8639,8 @@
       <c r="E340" s="1">
         <v>40054</v>
       </c>
-      <c r="F340" s="1">
-        <v>3500</v>
+      <c r="F340" s="4">
+        <v>4000</v>
       </c>
       <c r="G340" s="1"/>
       <c r="H340" s="1"/>
@@ -8647,8 +8661,8 @@
       <c r="E341" s="1">
         <v>40054</v>
       </c>
-      <c r="F341" s="1">
-        <v>3500</v>
+      <c r="F341" s="4">
+        <v>4000</v>
       </c>
       <c r="G341" s="1"/>
       <c r="H341" s="1"/>
@@ -8669,8 +8683,8 @@
       <c r="E342" s="1">
         <v>40054</v>
       </c>
-      <c r="F342" s="1">
-        <v>1870</v>
+      <c r="F342" s="4">
+        <v>1470</v>
       </c>
       <c r="G342" s="1"/>
       <c r="H342" s="1"/>
@@ -8691,8 +8705,8 @@
       <c r="E343" s="1">
         <v>40054</v>
       </c>
-      <c r="F343" s="1">
-        <v>200</v>
+      <c r="F343" s="4">
+        <v>500</v>
       </c>
       <c r="G343" s="1"/>
       <c r="H343" s="1"/>
@@ -8713,7 +8727,7 @@
       <c r="E344" s="1">
         <v>40054</v>
       </c>
-      <c r="F344" s="1">
+      <c r="F344" s="4">
         <v>30</v>
       </c>
       <c r="G344" s="1"/>
@@ -8735,8 +8749,8 @@
       <c r="E345" s="1">
         <v>40054</v>
       </c>
-      <c r="F345" s="1">
-        <v>1550</v>
+      <c r="F345" s="4">
+        <v>1600</v>
       </c>
       <c r="G345" s="1"/>
       <c r="H345" s="1"/>
@@ -8757,8 +8771,8 @@
       <c r="E346" s="1">
         <v>40054</v>
       </c>
-      <c r="F346" s="1">
-        <v>5000</v>
+      <c r="F346" s="4">
+        <v>4400</v>
       </c>
       <c r="G346" s="1"/>
       <c r="H346" s="1"/>
@@ -8779,8 +8793,8 @@
       <c r="E347" s="1">
         <v>40054</v>
       </c>
-      <c r="F347" s="1">
-        <v>2500</v>
+      <c r="F347" s="4">
+        <v>3000</v>
       </c>
       <c r="G347" s="1"/>
       <c r="H347" s="1"/>
@@ -8801,8 +8815,8 @@
       <c r="E348" s="1">
         <v>40054</v>
       </c>
-      <c r="F348" s="1">
-        <v>850</v>
+      <c r="F348" s="4">
+        <v>900</v>
       </c>
       <c r="G348" s="1"/>
       <c r="H348" s="1"/>
@@ -8823,7 +8837,7 @@
       <c r="E349" s="1">
         <v>40054</v>
       </c>
-      <c r="F349" s="1">
+      <c r="F349" s="4">
         <v>90</v>
       </c>
       <c r="G349" s="1"/>
@@ -8845,7 +8859,7 @@
       <c r="E350" s="1">
         <v>40054</v>
       </c>
-      <c r="F350" s="1">
+      <c r="F350" s="4">
         <v>10</v>
       </c>
       <c r="G350" s="1"/>
@@ -8867,7 +8881,7 @@
       <c r="E351" s="1">
         <v>40054</v>
       </c>
-      <c r="F351" s="1">
+      <c r="F351" s="4">
         <v>4000</v>
       </c>
       <c r="G351" s="1"/>
@@ -8889,7 +8903,7 @@
       <c r="E352" s="1">
         <v>40054</v>
       </c>
-      <c r="F352" s="1">
+      <c r="F352" s="4">
         <v>4000</v>
       </c>
       <c r="G352" s="1"/>
@@ -8911,7 +8925,7 @@
       <c r="E353" s="1">
         <v>40054</v>
       </c>
-      <c r="F353" s="1">
+      <c r="F353" s="4">
         <v>1500</v>
       </c>
       <c r="G353" s="1"/>
@@ -8933,7 +8947,7 @@
       <c r="E354" s="1">
         <v>40054</v>
       </c>
-      <c r="F354" s="1">
+      <c r="F354" s="4">
         <v>467</v>
       </c>
       <c r="G354" s="1"/>
@@ -8955,7 +8969,7 @@
       <c r="E355" s="1">
         <v>40054</v>
       </c>
-      <c r="F355" s="1">
+      <c r="F355" s="4">
         <v>30</v>
       </c>
       <c r="G355" s="1"/>
@@ -8977,7 +8991,7 @@
       <c r="E356" s="1">
         <v>40054</v>
       </c>
-      <c r="F356" s="1">
+      <c r="F356" s="4">
         <v>3</v>
       </c>
       <c r="G356" s="1"/>
@@ -8999,7 +9013,7 @@
       <c r="E357" s="1">
         <v>50015</v>
       </c>
-      <c r="F357" s="1">
+      <c r="F357" s="4">
         <v>0</v>
       </c>
       <c r="G357" s="1"/>
@@ -9021,8 +9035,8 @@
       <c r="E358" s="1">
         <v>50015</v>
       </c>
-      <c r="F358" s="1">
-        <v>1400</v>
+      <c r="F358" s="4">
+        <v>0</v>
       </c>
       <c r="G358" s="1"/>
       <c r="H358" s="1"/>
@@ -9043,8 +9057,8 @@
       <c r="E359" s="1">
         <v>50015</v>
       </c>
-      <c r="F359" s="1">
-        <v>5000</v>
+      <c r="F359" s="4">
+        <v>4400</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
@@ -9065,8 +9079,8 @@
       <c r="E360" s="1">
         <v>50015</v>
       </c>
-      <c r="F360" s="1">
-        <v>3000</v>
+      <c r="F360" s="4">
+        <v>4400</v>
       </c>
       <c r="G360" s="1"/>
       <c r="H360" s="1"/>
@@ -9087,8 +9101,8 @@
       <c r="E361" s="1">
         <v>50015</v>
       </c>
-      <c r="F361" s="1">
-        <v>500</v>
+      <c r="F361" s="4">
+        <v>1100</v>
       </c>
       <c r="G361" s="1"/>
       <c r="H361" s="1"/>
@@ -9109,7 +9123,7 @@
       <c r="E362" s="1">
         <v>50015</v>
       </c>
-      <c r="F362" s="1">
+      <c r="F362" s="4">
         <v>100</v>
       </c>
       <c r="G362" s="1"/>
@@ -9131,8 +9145,8 @@
       <c r="E363" s="1">
         <v>50015</v>
       </c>
-      <c r="F363" s="1">
-        <v>900</v>
+      <c r="F363" s="4">
+        <v>0</v>
       </c>
       <c r="G363" s="1"/>
       <c r="H363" s="1"/>
@@ -9153,8 +9167,8 @@
       <c r="E364" s="1">
         <v>50015</v>
       </c>
-      <c r="F364" s="1">
-        <v>3500</v>
+      <c r="F364" s="4">
+        <v>4000</v>
       </c>
       <c r="G364" s="1"/>
       <c r="H364" s="1"/>
@@ -9175,8 +9189,8 @@
       <c r="E365" s="1">
         <v>50015</v>
       </c>
-      <c r="F365" s="1">
-        <v>3500</v>
+      <c r="F365" s="4">
+        <v>4000</v>
       </c>
       <c r="G365" s="1"/>
       <c r="H365" s="1"/>
@@ -9197,8 +9211,8 @@
       <c r="E366" s="1">
         <v>50015</v>
       </c>
-      <c r="F366" s="1">
-        <v>1870</v>
+      <c r="F366" s="4">
+        <v>1470</v>
       </c>
       <c r="G366" s="1"/>
       <c r="H366" s="1"/>
@@ -9219,8 +9233,8 @@
       <c r="E367" s="1">
         <v>50015</v>
       </c>
-      <c r="F367" s="1">
-        <v>200</v>
+      <c r="F367" s="4">
+        <v>500</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="1"/>
@@ -9241,7 +9255,7 @@
       <c r="E368" s="1">
         <v>50015</v>
       </c>
-      <c r="F368" s="1">
+      <c r="F368" s="4">
         <v>30</v>
       </c>
       <c r="G368" s="1"/>
@@ -9263,8 +9277,8 @@
       <c r="E369" s="1">
         <v>50015</v>
       </c>
-      <c r="F369" s="1">
-        <v>1550</v>
+      <c r="F369" s="4">
+        <v>1600</v>
       </c>
       <c r="G369" s="1"/>
       <c r="H369" s="1"/>
@@ -9285,8 +9299,8 @@
       <c r="E370" s="1">
         <v>50015</v>
       </c>
-      <c r="F370" s="1">
-        <v>5000</v>
+      <c r="F370" s="4">
+        <v>4400</v>
       </c>
       <c r="G370" s="1"/>
       <c r="H370" s="1"/>
@@ -9307,8 +9321,8 @@
       <c r="E371" s="1">
         <v>50015</v>
       </c>
-      <c r="F371" s="1">
-        <v>2500</v>
+      <c r="F371" s="4">
+        <v>3000</v>
       </c>
       <c r="G371" s="1"/>
       <c r="H371" s="1"/>
@@ -9329,8 +9343,8 @@
       <c r="E372" s="1">
         <v>50015</v>
       </c>
-      <c r="F372" s="1">
-        <v>850</v>
+      <c r="F372" s="4">
+        <v>900</v>
       </c>
       <c r="G372" s="1"/>
       <c r="H372" s="1"/>
@@ -9351,7 +9365,7 @@
       <c r="E373" s="1">
         <v>50015</v>
       </c>
-      <c r="F373" s="1">
+      <c r="F373" s="4">
         <v>90</v>
       </c>
       <c r="G373" s="1"/>
@@ -9373,7 +9387,7 @@
       <c r="E374" s="1">
         <v>50015</v>
       </c>
-      <c r="F374" s="1">
+      <c r="F374" s="4">
         <v>10</v>
       </c>
       <c r="G374" s="1"/>
@@ -9395,7 +9409,7 @@
       <c r="E375" s="6">
         <v>60016</v>
       </c>
-      <c r="F375" s="6">
+      <c r="F375" s="7">
         <v>0</v>
       </c>
       <c r="G375" s="1"/>
@@ -9417,7 +9431,7 @@
       <c r="E376" s="6">
         <v>60016</v>
       </c>
-      <c r="F376" s="6">
+      <c r="F376" s="7">
         <v>0</v>
       </c>
       <c r="G376" s="1"/>
@@ -9439,8 +9453,8 @@
       <c r="E377" s="6">
         <v>60016</v>
       </c>
-      <c r="F377" s="6">
-        <v>4350</v>
+      <c r="F377" s="7">
+        <v>0</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -9461,8 +9475,8 @@
       <c r="E378" s="6">
         <v>60016</v>
       </c>
-      <c r="F378" s="6">
-        <v>4350</v>
+      <c r="F378" s="7">
+        <v>7000</v>
       </c>
       <c r="G378" s="1"/>
       <c r="H378" s="1"/>
@@ -9483,8 +9497,8 @@
       <c r="E379" s="6">
         <v>60016</v>
       </c>
-      <c r="F379" s="6">
-        <v>1000</v>
+      <c r="F379" s="7">
+        <v>2700</v>
       </c>
       <c r="G379" s="1"/>
       <c r="H379" s="1"/>
@@ -9505,7 +9519,7 @@
       <c r="E380" s="6">
         <v>60016</v>
       </c>
-      <c r="F380" s="6">
+      <c r="F380" s="7">
         <v>300</v>
       </c>
       <c r="G380" s="1"/>
@@ -9527,8 +9541,8 @@
       <c r="E381" s="1">
         <v>50025</v>
       </c>
-      <c r="F381" s="1">
-        <v>900</v>
+      <c r="F381" s="4">
+        <v>0</v>
       </c>
       <c r="G381" s="1"/>
       <c r="H381" s="1"/>
@@ -9549,8 +9563,8 @@
       <c r="E382" s="1">
         <v>50025</v>
       </c>
-      <c r="F382" s="1">
-        <v>3500</v>
+      <c r="F382" s="4">
+        <v>4000</v>
       </c>
       <c r="G382" s="1"/>
       <c r="H382" s="1"/>
@@ -9571,8 +9585,8 @@
       <c r="E383" s="1">
         <v>50025</v>
       </c>
-      <c r="F383" s="1">
-        <v>3500</v>
+      <c r="F383" s="4">
+        <v>4000</v>
       </c>
       <c r="G383" s="1"/>
       <c r="H383" s="1"/>
@@ -9593,8 +9607,8 @@
       <c r="E384" s="1">
         <v>50025</v>
       </c>
-      <c r="F384" s="1">
-        <v>1870</v>
+      <c r="F384" s="4">
+        <v>1470</v>
       </c>
       <c r="G384" s="1"/>
       <c r="H384" s="1"/>
@@ -9615,8 +9629,8 @@
       <c r="E385" s="1">
         <v>50025</v>
       </c>
-      <c r="F385" s="1">
-        <v>200</v>
+      <c r="F385" s="4">
+        <v>500</v>
       </c>
       <c r="G385" s="1"/>
       <c r="H385" s="1"/>
@@ -9637,7 +9651,7 @@
       <c r="E386" s="1">
         <v>50025</v>
       </c>
-      <c r="F386" s="1">
+      <c r="F386" s="4">
         <v>30</v>
       </c>
       <c r="G386" s="1"/>
@@ -9659,8 +9673,8 @@
       <c r="E387" s="1">
         <v>50025</v>
       </c>
-      <c r="F387" s="1">
-        <v>1550</v>
+      <c r="F387" s="4">
+        <v>1600</v>
       </c>
       <c r="G387" s="1"/>
       <c r="H387" s="1"/>
@@ -9681,8 +9695,8 @@
       <c r="E388" s="1">
         <v>50025</v>
       </c>
-      <c r="F388" s="1">
-        <v>5000</v>
+      <c r="F388" s="4">
+        <v>4400</v>
       </c>
       <c r="G388" s="1"/>
       <c r="H388" s="1"/>
@@ -9703,8 +9717,8 @@
       <c r="E389" s="1">
         <v>50025</v>
       </c>
-      <c r="F389" s="1">
-        <v>2500</v>
+      <c r="F389" s="4">
+        <v>3000</v>
       </c>
       <c r="G389" s="1"/>
       <c r="H389" s="1"/>
@@ -9725,8 +9739,8 @@
       <c r="E390" s="1">
         <v>50025</v>
       </c>
-      <c r="F390" s="1">
-        <v>850</v>
+      <c r="F390" s="4">
+        <v>900</v>
       </c>
       <c r="G390" s="1"/>
       <c r="H390" s="1"/>
@@ -9747,7 +9761,7 @@
       <c r="E391" s="1">
         <v>50025</v>
       </c>
-      <c r="F391" s="1">
+      <c r="F391" s="4">
         <v>90</v>
       </c>
       <c r="G391" s="1"/>
@@ -9769,7 +9783,7 @@
       <c r="E392" s="1">
         <v>50025</v>
       </c>
-      <c r="F392" s="1">
+      <c r="F392" s="4">
         <v>10</v>
       </c>
       <c r="G392" s="1"/>
@@ -9791,7 +9805,7 @@
       <c r="E393" s="1">
         <v>60016</v>
       </c>
-      <c r="F393" s="1">
+      <c r="F393" s="4">
         <v>0</v>
       </c>
       <c r="G393" s="1"/>
@@ -9813,7 +9827,7 @@
       <c r="E394" s="1">
         <v>60016</v>
       </c>
-      <c r="F394" s="1">
+      <c r="F394" s="4">
         <v>0</v>
       </c>
       <c r="G394" s="1"/>
@@ -9835,8 +9849,8 @@
       <c r="E395" s="1">
         <v>60016</v>
       </c>
-      <c r="F395" s="1">
-        <v>4350</v>
+      <c r="F395" s="4">
+        <v>0</v>
       </c>
       <c r="G395" s="1"/>
       <c r="H395" s="1"/>
@@ -9857,8 +9871,8 @@
       <c r="E396" s="1">
         <v>60016</v>
       </c>
-      <c r="F396" s="1">
-        <v>4350</v>
+      <c r="F396" s="4">
+        <v>7000</v>
       </c>
       <c r="G396" s="1"/>
       <c r="H396" s="1"/>
@@ -9879,8 +9893,8 @@
       <c r="E397" s="1">
         <v>60016</v>
       </c>
-      <c r="F397" s="1">
-        <v>1000</v>
+      <c r="F397" s="4">
+        <v>2700</v>
       </c>
       <c r="G397" s="1"/>
       <c r="H397" s="1"/>
@@ -9901,7 +9915,7 @@
       <c r="E398" s="1">
         <v>60016</v>
       </c>
-      <c r="F398" s="1">
+      <c r="F398" s="4">
         <v>300</v>
       </c>
       <c r="G398" s="1"/>
@@ -9923,7 +9937,7 @@
       <c r="E399" s="1">
         <v>60016</v>
       </c>
-      <c r="F399" s="1">
+      <c r="F399" s="4">
         <v>0</v>
       </c>
       <c r="G399" s="1"/>
@@ -9945,8 +9959,8 @@
       <c r="E400" s="1">
         <v>60016</v>
       </c>
-      <c r="F400" s="1">
-        <v>1400</v>
+      <c r="F400" s="4">
+        <v>0</v>
       </c>
       <c r="G400" s="1"/>
       <c r="H400" s="1"/>
@@ -9967,8 +9981,8 @@
       <c r="E401" s="1">
         <v>60016</v>
       </c>
-      <c r="F401" s="1">
-        <v>5000</v>
+      <c r="F401" s="4">
+        <v>4400</v>
       </c>
       <c r="G401" s="1"/>
       <c r="H401" s="1"/>
@@ -9989,8 +10003,8 @@
       <c r="E402" s="1">
         <v>60016</v>
       </c>
-      <c r="F402" s="1">
-        <v>3000</v>
+      <c r="F402" s="4">
+        <v>4400</v>
       </c>
       <c r="G402" s="1"/>
       <c r="H402" s="1"/>
@@ -10011,8 +10025,8 @@
       <c r="E403" s="1">
         <v>60016</v>
       </c>
-      <c r="F403" s="1">
-        <v>500</v>
+      <c r="F403" s="4">
+        <v>1100</v>
       </c>
       <c r="G403" s="1"/>
       <c r="H403" s="1"/>
@@ -10033,7 +10047,7 @@
       <c r="E404" s="1">
         <v>60016</v>
       </c>
-      <c r="F404" s="1">
+      <c r="F404" s="4">
         <v>100</v>
       </c>
       <c r="G404" s="1"/>
@@ -10055,8 +10069,8 @@
       <c r="E405" s="1">
         <v>60016</v>
       </c>
-      <c r="F405" s="1">
-        <v>900</v>
+      <c r="F405" s="4">
+        <v>0</v>
       </c>
       <c r="G405" s="1"/>
       <c r="H405" s="1"/>
@@ -10077,8 +10091,8 @@
       <c r="E406" s="1">
         <v>60016</v>
       </c>
-      <c r="F406" s="1">
-        <v>3500</v>
+      <c r="F406" s="4">
+        <v>4000</v>
       </c>
       <c r="G406" s="1"/>
       <c r="H406" s="1"/>
@@ -10099,8 +10113,8 @@
       <c r="E407" s="1">
         <v>60016</v>
       </c>
-      <c r="F407" s="1">
-        <v>3500</v>
+      <c r="F407" s="4">
+        <v>4000</v>
       </c>
       <c r="G407" s="1"/>
       <c r="H407" s="1"/>
@@ -10121,8 +10135,8 @@
       <c r="E408" s="1">
         <v>60016</v>
       </c>
-      <c r="F408" s="1">
-        <v>1870</v>
+      <c r="F408" s="4">
+        <v>1470</v>
       </c>
       <c r="G408" s="1"/>
       <c r="H408" s="1"/>
@@ -10143,8 +10157,8 @@
       <c r="E409" s="1">
         <v>60016</v>
       </c>
-      <c r="F409" s="1">
-        <v>200</v>
+      <c r="F409" s="4">
+        <v>500</v>
       </c>
       <c r="G409" s="1"/>
       <c r="H409" s="1"/>
@@ -10165,7 +10179,7 @@
       <c r="E410" s="1">
         <v>60016</v>
       </c>
-      <c r="F410" s="1">
+      <c r="F410" s="4">
         <v>30</v>
       </c>
       <c r="G410" s="1"/>
@@ -10190,6 +10204,11 @@
       <c r="F416" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F3:F410">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($D3,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/data/c_dropColor(掉落品质).xlsx
+++ b/data/c_dropColor(掉落品质).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1165,8 +1165,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H416"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I416"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
@@ -1175,7 +1175,7 @@
     <col min="6" max="6" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:8">
+    <row r="1" ht="14.25" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,7 +1197,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" ht="14.25" spans="1:8">
+    <row r="2" ht="14.25" spans="1:9">
       <c r="A2" s="3">
         <v>-1</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" ht="14.25" spans="1:8">
+    <row r="3" ht="14.25" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1225,13 +1225,15 @@
       <c r="E3" s="1">
         <v>10011</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>6000</v>
       </c>
-      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-    </row>
-    <row r="4" ht="14.25" spans="1:8">
+      <c r="I3" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1247,13 +1249,15 @@
       <c r="E4" s="1">
         <v>10011</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>3000</v>
       </c>
-      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" ht="14.25" spans="1:8">
+      <c r="I4" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1269,13 +1273,15 @@
       <c r="E5" s="1">
         <v>10011</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>700</v>
       </c>
-      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" ht="14.25" spans="1:8">
+      <c r="I5" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1291,13 +1297,15 @@
       <c r="E6" s="1">
         <v>10011</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
+        <v>275</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="4">
         <v>289</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" ht="14.25" spans="1:8">
+    </row>
+    <row r="7" ht="14.25" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1313,13 +1321,15 @@
       <c r="E7" s="1">
         <v>10011</v>
       </c>
-      <c r="F7" s="4">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
+      <c r="F7" s="3">
+        <v>20</v>
+      </c>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" ht="14.25" spans="1:8">
+      <c r="I7" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1335,13 +1345,15 @@
       <c r="E8" s="1">
         <v>10011</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="4">
         <v>1</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" ht="14.25" spans="1:8">
+    </row>
+    <row r="9" ht="14.25" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1357,13 +1369,15 @@
       <c r="E9" s="1">
         <v>10021</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>6000</v>
       </c>
-      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" ht="14.25" spans="1:8">
+      <c r="I9" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1379,13 +1393,15 @@
       <c r="E10" s="1">
         <v>10021</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>3000</v>
       </c>
-      <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" ht="14.25" spans="1:8">
+      <c r="I10" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1401,13 +1417,15 @@
       <c r="E11" s="1">
         <v>10021</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>700</v>
       </c>
-      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" ht="14.25" spans="1:8">
+      <c r="I11" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1423,13 +1441,15 @@
       <c r="E12" s="1">
         <v>10021</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
+        <v>275</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4">
         <v>289</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" ht="14.25" spans="1:8">
+    </row>
+    <row r="13" ht="14.25" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1445,13 +1465,15 @@
       <c r="E13" s="1">
         <v>10021</v>
       </c>
-      <c r="F13" s="4">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1"/>
+      <c r="F13" s="3">
+        <v>20</v>
+      </c>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:8">
+      <c r="I13" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1467,13 +1489,15 @@
       <c r="E14" s="1">
         <v>10021</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" ht="14.25" spans="1:8">
+    </row>
+    <row r="15" ht="14.25" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1489,13 +1513,15 @@
       <c r="E15" s="1">
         <v>10031</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <v>6000</v>
       </c>
-      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" ht="14.25" spans="1:8">
+      <c r="I15" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1511,13 +1537,15 @@
       <c r="E16" s="1">
         <v>10031</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>3000</v>
       </c>
-      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-    </row>
-    <row r="17" ht="14.25" spans="1:8">
+      <c r="I16" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1533,13 +1561,15 @@
       <c r="E17" s="1">
         <v>10031</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-    </row>
-    <row r="18" ht="14.25" spans="1:8">
+      <c r="I17" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1555,13 +1585,15 @@
       <c r="E18" s="1">
         <v>10031</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
+        <v>275</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="4">
         <v>289</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" ht="14.25" spans="1:8">
+    </row>
+    <row r="19" ht="14.25" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1577,13 +1609,15 @@
       <c r="E19" s="1">
         <v>10031</v>
       </c>
-      <c r="F19" s="4">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1"/>
+      <c r="F19" s="3">
+        <v>20</v>
+      </c>
       <c r="H19" s="1"/>
-    </row>
-    <row r="20" ht="14.25" spans="1:8">
+      <c r="I19" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1599,13 +1633,15 @@
       <c r="E20" s="1">
         <v>10031</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="4">
         <v>1</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" ht="14.25" spans="1:8">
+    </row>
+    <row r="21" ht="14.25" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1621,13 +1657,15 @@
       <c r="E21" s="1">
         <v>10041</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>6000</v>
       </c>
-      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-    </row>
-    <row r="22" ht="14.25" spans="1:8">
+      <c r="I21" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1643,13 +1681,15 @@
       <c r="E22" s="1">
         <v>10041</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>3000</v>
       </c>
-      <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-    </row>
-    <row r="23" ht="14.25" spans="1:8">
+      <c r="I22" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1665,13 +1705,15 @@
       <c r="E23" s="1">
         <v>10041</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:8">
+      <c r="I23" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1687,13 +1729,15 @@
       <c r="E24" s="1">
         <v>10041</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
+        <v>275</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="4">
         <v>289</v>
       </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:8">
+    </row>
+    <row r="25" ht="14.25" spans="1:9">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1709,13 +1753,15 @@
       <c r="E25" s="1">
         <v>10041</v>
       </c>
-      <c r="F25" s="4">
-        <v>10</v>
-      </c>
-      <c r="G25" s="1"/>
+      <c r="F25" s="3">
+        <v>20</v>
+      </c>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:8">
+      <c r="I25" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" spans="1:9">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1731,13 +1777,15 @@
       <c r="E26" s="1">
         <v>10041</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="3">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="4">
         <v>1</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" ht="14.25" spans="1:8">
+    </row>
+    <row r="27" ht="14.25" spans="1:9">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1753,13 +1801,15 @@
       <c r="E27" s="1">
         <v>10051</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:8">
+      <c r="I27" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:9">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1775,13 +1825,15 @@
       <c r="E28" s="1">
         <v>10051</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="3">
         <v>3000</v>
       </c>
-      <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:8">
+      <c r="I28" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="1:9">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1797,13 +1849,15 @@
       <c r="E29" s="1">
         <v>10051</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="3">
         <v>700</v>
       </c>
-      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-    </row>
-    <row r="30" ht="14.25" spans="1:8">
+      <c r="I29" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" spans="1:9">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1819,13 +1873,15 @@
       <c r="E30" s="1">
         <v>10051</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="3">
+        <v>275</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="4">
         <v>289</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:8">
+    </row>
+    <row r="31" ht="14.25" spans="1:9">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1841,13 +1897,15 @@
       <c r="E31" s="1">
         <v>10051</v>
       </c>
-      <c r="F31" s="4">
-        <v>10</v>
-      </c>
-      <c r="G31" s="1"/>
+      <c r="F31" s="3">
+        <v>20</v>
+      </c>
       <c r="H31" s="1"/>
-    </row>
-    <row r="32" ht="14.25" spans="1:8">
+      <c r="I31" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" spans="1:9">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1863,13 +1921,15 @@
       <c r="E32" s="1">
         <v>10051</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="3">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="4">
         <v>1</v>
       </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" ht="14.25" spans="1:8">
+    </row>
+    <row r="33" ht="14.25" spans="1:9">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1885,13 +1945,15 @@
       <c r="E33" s="1">
         <v>10061</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-    </row>
-    <row r="34" ht="14.25" spans="1:8">
+      <c r="I33" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" spans="1:9">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1907,13 +1969,15 @@
       <c r="E34" s="1">
         <v>10061</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="3">
         <v>3000</v>
       </c>
-      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:8">
+      <c r="I34" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" spans="1:9">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -1929,13 +1993,15 @@
       <c r="E35" s="1">
         <v>10061</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-    </row>
-    <row r="36" ht="14.25" spans="1:8">
+      <c r="I35" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:9">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -1951,13 +2017,15 @@
       <c r="E36" s="1">
         <v>10061</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="3">
+        <v>275</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="4">
         <v>289</v>
       </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" ht="14.25" spans="1:8">
+    </row>
+    <row r="37" ht="14.25" spans="1:9">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -1973,13 +2041,15 @@
       <c r="E37" s="1">
         <v>10061</v>
       </c>
-      <c r="F37" s="4">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1"/>
+      <c r="F37" s="3">
+        <v>20</v>
+      </c>
       <c r="H37" s="1"/>
-    </row>
-    <row r="38" ht="14.25" spans="1:8">
+      <c r="I37" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" spans="1:9">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -1995,13 +2065,15 @@
       <c r="E38" s="1">
         <v>10061</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="3">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38" s="4">
         <v>1</v>
       </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" ht="14.25" spans="1:8">
+    </row>
+    <row r="39" ht="14.25" spans="1:9">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2017,13 +2089,15 @@
       <c r="E39" s="1">
         <v>10071</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="3">
         <v>6000</v>
       </c>
-      <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-    </row>
-    <row r="40" ht="14.25" spans="1:8">
+      <c r="I39" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" spans="1:9">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2039,13 +2113,15 @@
       <c r="E40" s="1">
         <v>10071</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="3">
         <v>3000</v>
       </c>
-      <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-    </row>
-    <row r="41" ht="14.25" spans="1:8">
+      <c r="I40" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" spans="1:9">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2061,13 +2137,15 @@
       <c r="E41" s="1">
         <v>10071</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-    </row>
-    <row r="42" ht="14.25" spans="1:8">
+      <c r="I41" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" spans="1:9">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2083,13 +2161,15 @@
       <c r="E42" s="1">
         <v>10071</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="3">
+        <v>275</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="4">
         <v>289</v>
       </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" ht="14.25" spans="1:8">
+    </row>
+    <row r="43" ht="14.25" spans="1:9">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2105,13 +2185,15 @@
       <c r="E43" s="1">
         <v>10071</v>
       </c>
-      <c r="F43" s="4">
-        <v>10</v>
-      </c>
-      <c r="G43" s="1"/>
+      <c r="F43" s="3">
+        <v>20</v>
+      </c>
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" ht="14.25" spans="1:8">
+      <c r="I43" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" spans="1:9">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2127,13 +2209,15 @@
       <c r="E44" s="1">
         <v>10071</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="3">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" s="4">
         <v>1</v>
       </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" ht="14.25" spans="1:8">
+    </row>
+    <row r="45" ht="14.25" spans="1:9">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2149,13 +2233,15 @@
       <c r="E45" s="1">
         <v>10081</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="3">
         <v>6000</v>
       </c>
-      <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-    </row>
-    <row r="46" ht="14.25" spans="1:8">
+      <c r="I45" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" spans="1:9">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -2171,13 +2257,15 @@
       <c r="E46" s="1">
         <v>10081</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="3">
         <v>3000</v>
       </c>
-      <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-    </row>
-    <row r="47" ht="14.25" spans="1:8">
+      <c r="I46" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -2193,13 +2281,15 @@
       <c r="E47" s="1">
         <v>10081</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="3">
         <v>700</v>
       </c>
-      <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-    </row>
-    <row r="48" ht="14.25" spans="1:8">
+      <c r="I47" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" spans="1:9">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -2215,13 +2305,15 @@
       <c r="E48" s="1">
         <v>10081</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="3">
+        <v>275</v>
+      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="4">
         <v>289</v>
       </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" ht="14.25" spans="1:8">
+    </row>
+    <row r="49" ht="14.25" spans="1:9">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -2237,13 +2329,15 @@
       <c r="E49" s="1">
         <v>10081</v>
       </c>
-      <c r="F49" s="4">
-        <v>10</v>
-      </c>
-      <c r="G49" s="1"/>
+      <c r="F49" s="3">
+        <v>20</v>
+      </c>
       <c r="H49" s="1"/>
-    </row>
-    <row r="50" ht="14.25" spans="1:8">
+      <c r="I49" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25" spans="1:9">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -2259,13 +2353,15 @@
       <c r="E50" s="1">
         <v>10081</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="3">
+        <v>5</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="4">
         <v>1</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" ht="14.25" spans="1:8">
+    </row>
+    <row r="51" ht="14.25" spans="1:9">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -2281,13 +2377,15 @@
       <c r="E51" s="1">
         <v>10091</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="3">
         <v>6000</v>
       </c>
-      <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-    </row>
-    <row r="52" ht="14.25" spans="1:8">
+      <c r="I51" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" spans="1:9">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -2303,13 +2401,15 @@
       <c r="E52" s="1">
         <v>10091</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-    </row>
-    <row r="53" ht="14.25" spans="1:8">
+      <c r="I52" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25" spans="1:9">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -2325,13 +2425,15 @@
       <c r="E53" s="1">
         <v>10091</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="3">
         <v>700</v>
       </c>
-      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-    </row>
-    <row r="54" ht="14.25" spans="1:8">
+      <c r="I53" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" spans="1:9">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -2347,13 +2449,15 @@
       <c r="E54" s="1">
         <v>10091</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="3">
+        <v>275</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="4">
         <v>289</v>
       </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" ht="14.25" spans="1:8">
+    </row>
+    <row r="55" ht="14.25" spans="1:9">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -2369,13 +2473,15 @@
       <c r="E55" s="1">
         <v>10091</v>
       </c>
-      <c r="F55" s="4">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1"/>
+      <c r="F55" s="3">
+        <v>20</v>
+      </c>
       <c r="H55" s="1"/>
-    </row>
-    <row r="56" ht="14.25" spans="1:8">
+      <c r="I55" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" spans="1:9">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -2391,13 +2497,15 @@
       <c r="E56" s="1">
         <v>10091</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="3">
+        <v>5</v>
+      </c>
+      <c r="H56" s="1"/>
+      <c r="I56" s="4">
         <v>1</v>
       </c>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" ht="14.25" spans="1:8">
+    </row>
+    <row r="57" ht="14.25" spans="1:9">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -2413,13 +2521,15 @@
       <c r="E57" s="1">
         <v>10101</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="3">
         <v>6000</v>
       </c>
-      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-    </row>
-    <row r="58" ht="14.25" spans="1:8">
+      <c r="I57" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25" spans="1:9">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -2435,13 +2545,15 @@
       <c r="E58" s="1">
         <v>10101</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-    </row>
-    <row r="59" ht="14.25" spans="1:8">
+      <c r="I58" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25" spans="1:9">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -2457,13 +2569,15 @@
       <c r="E59" s="1">
         <v>10101</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-    </row>
-    <row r="60" ht="14.25" spans="1:8">
+      <c r="I59" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25" spans="1:9">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -2479,13 +2593,15 @@
       <c r="E60" s="1">
         <v>10101</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="3">
+        <v>275</v>
+      </c>
+      <c r="H60" s="1"/>
+      <c r="I60" s="4">
         <v>289</v>
       </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" ht="14.25" spans="1:8">
+    </row>
+    <row r="61" ht="14.25" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -2501,13 +2617,15 @@
       <c r="E61" s="1">
         <v>10101</v>
       </c>
-      <c r="F61" s="4">
-        <v>10</v>
-      </c>
-      <c r="G61" s="1"/>
+      <c r="F61" s="3">
+        <v>20</v>
+      </c>
       <c r="H61" s="1"/>
-    </row>
-    <row r="62" ht="14.25" spans="1:8">
+      <c r="I61" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" spans="1:9">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -2523,13 +2641,15 @@
       <c r="E62" s="1">
         <v>10101</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="3">
+        <v>5</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="4">
         <v>1</v>
       </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-    </row>
-    <row r="63" ht="14.25" spans="1:8">
+    </row>
+    <row r="63" ht="14.25" spans="1:9">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -2545,13 +2665,15 @@
       <c r="E63" s="1">
         <v>20012</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="3">
         <v>4000</v>
       </c>
-      <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-    </row>
-    <row r="64" ht="14.25" spans="1:8">
+      <c r="I63" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="64" ht="14.25" spans="1:9">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -2567,13 +2689,15 @@
       <c r="E64" s="1">
         <v>20012</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="3">
         <v>4000</v>
       </c>
-      <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-    </row>
-    <row r="65" ht="14.25" spans="1:8">
+      <c r="I64" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25" spans="1:9">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -2589,13 +2713,15 @@
       <c r="E65" s="1">
         <v>20012</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="3">
         <v>1500</v>
       </c>
-      <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-    </row>
-    <row r="66" ht="14.25" spans="1:8">
+      <c r="I65" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25" spans="1:9">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -2611,13 +2737,15 @@
       <c r="E66" s="1">
         <v>20012</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="3">
+        <v>450</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="4">
         <v>467</v>
       </c>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-    </row>
-    <row r="67" ht="14.25" spans="1:8">
+    </row>
+    <row r="67" ht="14.25" spans="1:9">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -2633,13 +2761,15 @@
       <c r="E67" s="1">
         <v>20012</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="3">
+        <v>40</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="4">
         <v>30</v>
       </c>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-    </row>
-    <row r="68" ht="14.25" spans="1:8">
+    </row>
+    <row r="68" ht="14.25" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -2655,13 +2785,15 @@
       <c r="E68" s="1">
         <v>20012</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="3">
+        <v>10</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="4">
         <v>3</v>
       </c>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-    </row>
-    <row r="69" ht="14.25" spans="1:8">
+    </row>
+    <row r="69" ht="14.25" spans="1:9">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -2677,13 +2809,15 @@
       <c r="E69" s="1">
         <v>20012</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="3">
         <v>6000</v>
       </c>
-      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-    </row>
-    <row r="70" ht="14.25" spans="1:8">
+      <c r="I69" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25" spans="1:9">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -2699,13 +2833,15 @@
       <c r="E70" s="1">
         <v>20012</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="3">
         <v>3000</v>
       </c>
-      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-    </row>
-    <row r="71" ht="14.25" spans="1:8">
+      <c r="I70" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25" spans="1:9">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -2721,13 +2857,15 @@
       <c r="E71" s="1">
         <v>20012</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="3">
         <v>700</v>
       </c>
-      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
-    </row>
-    <row r="72" ht="14.25" spans="1:8">
+      <c r="I71" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25" spans="1:9">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -2743,13 +2881,15 @@
       <c r="E72" s="1">
         <v>20012</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="3">
+        <v>275</v>
+      </c>
+      <c r="H72" s="1"/>
+      <c r="I72" s="4">
         <v>289</v>
       </c>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-    </row>
-    <row r="73" ht="14.25" spans="1:8">
+    </row>
+    <row r="73" ht="14.25" spans="1:9">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -2765,13 +2905,15 @@
       <c r="E73" s="1">
         <v>20012</v>
       </c>
-      <c r="F73" s="4">
-        <v>10</v>
-      </c>
-      <c r="G73" s="1"/>
+      <c r="F73" s="3">
+        <v>20</v>
+      </c>
       <c r="H73" s="1"/>
-    </row>
-    <row r="74" ht="14.25" spans="1:8">
+      <c r="I73" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" ht="14.25" spans="1:9">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -2787,13 +2929,15 @@
       <c r="E74" s="1">
         <v>20012</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="3">
+        <v>5</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="4">
         <v>1</v>
       </c>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-    </row>
-    <row r="75" ht="14.25" spans="1:8">
+    </row>
+    <row r="75" ht="14.25" spans="1:9">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -2809,13 +2953,15 @@
       <c r="E75" s="1">
         <v>20022</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="3">
         <v>4000</v>
       </c>
-      <c r="G75" s="1"/>
       <c r="H75" s="1"/>
-    </row>
-    <row r="76" ht="14.25" spans="1:8">
+      <c r="I75" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="76" ht="14.25" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -2831,13 +2977,15 @@
       <c r="E76" s="1">
         <v>20022</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="3">
         <v>4000</v>
       </c>
-      <c r="G76" s="1"/>
       <c r="H76" s="1"/>
-    </row>
-    <row r="77" ht="14.25" spans="1:8">
+      <c r="I76" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="77" ht="14.25" spans="1:9">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -2853,13 +3001,15 @@
       <c r="E77" s="1">
         <v>20022</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="3">
         <v>1500</v>
       </c>
-      <c r="G77" s="1"/>
       <c r="H77" s="1"/>
-    </row>
-    <row r="78" ht="14.25" spans="1:8">
+      <c r="I77" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="78" ht="14.25" spans="1:9">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -2875,13 +3025,15 @@
       <c r="E78" s="1">
         <v>20022</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="3">
+        <v>450</v>
+      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="4">
         <v>467</v>
       </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-    </row>
-    <row r="79" ht="14.25" spans="1:8">
+    </row>
+    <row r="79" ht="14.25" spans="1:9">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -2897,13 +3049,15 @@
       <c r="E79" s="1">
         <v>20022</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="3">
+        <v>40</v>
+      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="4">
         <v>30</v>
       </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="80" ht="14.25" spans="1:8">
+    </row>
+    <row r="80" ht="14.25" spans="1:9">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -2919,13 +3073,15 @@
       <c r="E80" s="1">
         <v>20022</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="3">
+        <v>10</v>
+      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="4">
         <v>3</v>
       </c>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" ht="14.25" spans="1:8">
+    </row>
+    <row r="81" ht="14.25" spans="1:9">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -2941,13 +3097,15 @@
       <c r="E81" s="1">
         <v>20022</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="1"/>
       <c r="H81" s="1"/>
-    </row>
-    <row r="82" ht="14.25" spans="1:8">
+      <c r="I81" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="82" ht="14.25" spans="1:9">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -2963,13 +3121,15 @@
       <c r="E82" s="1">
         <v>20022</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="3">
         <v>3000</v>
       </c>
-      <c r="G82" s="1"/>
       <c r="H82" s="1"/>
-    </row>
-    <row r="83" ht="14.25" spans="1:8">
+      <c r="I82" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83" ht="14.25" spans="1:9">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -2985,13 +3145,15 @@
       <c r="E83" s="1">
         <v>20022</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="1"/>
       <c r="H83" s="1"/>
-    </row>
-    <row r="84" ht="14.25" spans="1:8">
+      <c r="I83" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" ht="14.25" spans="1:9">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -3007,13 +3169,15 @@
       <c r="E84" s="1">
         <v>20022</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="3">
+        <v>275</v>
+      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="4">
         <v>289</v>
       </c>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-    </row>
-    <row r="85" ht="14.25" spans="1:8">
+    </row>
+    <row r="85" ht="14.25" spans="1:9">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -3029,13 +3193,15 @@
       <c r="E85" s="1">
         <v>20022</v>
       </c>
-      <c r="F85" s="4">
-        <v>10</v>
-      </c>
-      <c r="G85" s="1"/>
+      <c r="F85" s="3">
+        <v>20</v>
+      </c>
       <c r="H85" s="1"/>
-    </row>
-    <row r="86" ht="14.25" spans="1:8">
+      <c r="I85" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" ht="14.25" spans="1:9">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -3051,13 +3217,15 @@
       <c r="E86" s="1">
         <v>20022</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="3">
+        <v>5</v>
+      </c>
+      <c r="H86" s="1"/>
+      <c r="I86" s="4">
         <v>1</v>
       </c>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-    </row>
-    <row r="87" ht="14.25" spans="1:8">
+    </row>
+    <row r="87" ht="14.25" spans="1:9">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -3073,13 +3241,15 @@
       <c r="E87" s="1">
         <v>20032</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="3">
         <v>4000</v>
       </c>
-      <c r="G87" s="1"/>
       <c r="H87" s="1"/>
-    </row>
-    <row r="88" ht="14.25" spans="1:8">
+      <c r="I87" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25" spans="1:9">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -3095,13 +3265,15 @@
       <c r="E88" s="1">
         <v>20032</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="3">
         <v>4000</v>
       </c>
-      <c r="G88" s="1"/>
       <c r="H88" s="1"/>
-    </row>
-    <row r="89" ht="14.25" spans="1:8">
+      <c r="I88" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="89" ht="14.25" spans="1:9">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -3117,13 +3289,15 @@
       <c r="E89" s="1">
         <v>20032</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="3">
         <v>1500</v>
       </c>
-      <c r="G89" s="1"/>
       <c r="H89" s="1"/>
-    </row>
-    <row r="90" ht="14.25" spans="1:8">
+      <c r="I89" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25" spans="1:9">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -3139,13 +3313,15 @@
       <c r="E90" s="1">
         <v>20032</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="3">
+        <v>450</v>
+      </c>
+      <c r="H90" s="1"/>
+      <c r="I90" s="4">
         <v>467</v>
       </c>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-    </row>
-    <row r="91" ht="14.25" spans="1:8">
+    </row>
+    <row r="91" ht="14.25" spans="1:9">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -3161,13 +3337,15 @@
       <c r="E91" s="1">
         <v>20032</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="3">
+        <v>40</v>
+      </c>
+      <c r="H91" s="1"/>
+      <c r="I91" s="4">
         <v>30</v>
       </c>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-    </row>
-    <row r="92" ht="14.25" spans="1:8">
+    </row>
+    <row r="92" ht="14.25" spans="1:9">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -3183,13 +3361,15 @@
       <c r="E92" s="1">
         <v>20032</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="3">
+        <v>10</v>
+      </c>
+      <c r="H92" s="1"/>
+      <c r="I92" s="4">
         <v>3</v>
       </c>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-    </row>
-    <row r="93" ht="14.25" spans="1:8">
+    </row>
+    <row r="93" ht="14.25" spans="1:9">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -3205,13 +3385,15 @@
       <c r="E93" s="1">
         <v>20032</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="3">
         <v>6000</v>
       </c>
-      <c r="G93" s="1"/>
       <c r="H93" s="1"/>
-    </row>
-    <row r="94" ht="14.25" spans="1:8">
+      <c r="I93" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" spans="1:9">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -3227,13 +3409,15 @@
       <c r="E94" s="1">
         <v>20032</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="3">
         <v>3000</v>
       </c>
-      <c r="G94" s="1"/>
       <c r="H94" s="1"/>
-    </row>
-    <row r="95" ht="14.25" spans="1:8">
+      <c r="I94" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" spans="1:9">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -3249,13 +3433,15 @@
       <c r="E95" s="1">
         <v>20032</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="3">
         <v>700</v>
       </c>
-      <c r="G95" s="1"/>
       <c r="H95" s="1"/>
-    </row>
-    <row r="96" ht="14.25" spans="1:8">
+      <c r="I95" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" spans="1:9">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -3271,13 +3457,15 @@
       <c r="E96" s="1">
         <v>20032</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="3">
+        <v>275</v>
+      </c>
+      <c r="H96" s="1"/>
+      <c r="I96" s="4">
         <v>289</v>
       </c>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="97" ht="14.25" spans="1:8">
+    </row>
+    <row r="97" ht="14.25" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -3293,13 +3481,15 @@
       <c r="E97" s="1">
         <v>20032</v>
       </c>
-      <c r="F97" s="4">
-        <v>10</v>
-      </c>
-      <c r="G97" s="1"/>
+      <c r="F97" s="3">
+        <v>20</v>
+      </c>
       <c r="H97" s="1"/>
-    </row>
-    <row r="98" ht="14.25" spans="1:8">
+      <c r="I97" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25" spans="1:9">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -3315,13 +3505,15 @@
       <c r="E98" s="1">
         <v>20032</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="3">
+        <v>5</v>
+      </c>
+      <c r="H98" s="1"/>
+      <c r="I98" s="4">
         <v>1</v>
       </c>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-    </row>
-    <row r="99" ht="14.25" spans="1:8">
+    </row>
+    <row r="99" ht="14.25" spans="1:9">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -3337,13 +3529,15 @@
       <c r="E99" s="1">
         <v>20042</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="3">
         <v>4000</v>
       </c>
-      <c r="G99" s="1"/>
       <c r="H99" s="1"/>
-    </row>
-    <row r="100" ht="14.25" spans="1:8">
+      <c r="I99" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="100" ht="14.25" spans="1:9">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -3359,13 +3553,15 @@
       <c r="E100" s="1">
         <v>20042</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="3">
         <v>4000</v>
       </c>
-      <c r="G100" s="1"/>
       <c r="H100" s="1"/>
-    </row>
-    <row r="101" ht="14.25" spans="1:8">
+      <c r="I100" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25" spans="1:9">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -3381,13 +3577,15 @@
       <c r="E101" s="1">
         <v>20042</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="3">
         <v>1500</v>
       </c>
-      <c r="G101" s="1"/>
       <c r="H101" s="1"/>
-    </row>
-    <row r="102" ht="14.25" spans="1:8">
+      <c r="I101" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="102" ht="14.25" spans="1:9">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -3403,13 +3601,15 @@
       <c r="E102" s="1">
         <v>20042</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="3">
+        <v>450</v>
+      </c>
+      <c r="H102" s="1"/>
+      <c r="I102" s="4">
         <v>467</v>
       </c>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-    </row>
-    <row r="103" ht="14.25" spans="1:8">
+    </row>
+    <row r="103" ht="14.25" spans="1:9">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -3425,13 +3625,15 @@
       <c r="E103" s="1">
         <v>20042</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="3">
+        <v>40</v>
+      </c>
+      <c r="H103" s="1"/>
+      <c r="I103" s="4">
         <v>30</v>
       </c>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-    </row>
-    <row r="104" ht="14.25" spans="1:8">
+    </row>
+    <row r="104" ht="14.25" spans="1:9">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -3447,13 +3649,15 @@
       <c r="E104" s="1">
         <v>20042</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="3">
+        <v>10</v>
+      </c>
+      <c r="H104" s="1"/>
+      <c r="I104" s="4">
         <v>3</v>
       </c>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-    </row>
-    <row r="105" ht="14.25" spans="1:8">
+    </row>
+    <row r="105" ht="14.25" spans="1:9">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -3469,13 +3673,15 @@
       <c r="E105" s="1">
         <v>20042</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="3">
         <v>6000</v>
       </c>
-      <c r="G105" s="1"/>
       <c r="H105" s="1"/>
-    </row>
-    <row r="106" ht="14.25" spans="1:8">
+      <c r="I105" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" spans="1:9">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -3491,13 +3697,15 @@
       <c r="E106" s="1">
         <v>20042</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="3">
         <v>3000</v>
       </c>
-      <c r="G106" s="1"/>
       <c r="H106" s="1"/>
-    </row>
-    <row r="107" ht="14.25" spans="1:8">
+      <c r="I106" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="107" ht="14.25" spans="1:9">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -3513,13 +3721,15 @@
       <c r="E107" s="1">
         <v>20042</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="3">
         <v>700</v>
       </c>
-      <c r="G107" s="1"/>
       <c r="H107" s="1"/>
-    </row>
-    <row r="108" ht="14.25" spans="1:8">
+      <c r="I107" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" spans="1:9">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -3535,13 +3745,15 @@
       <c r="E108" s="1">
         <v>20042</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="3">
+        <v>275</v>
+      </c>
+      <c r="H108" s="1"/>
+      <c r="I108" s="4">
         <v>289</v>
       </c>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-    </row>
-    <row r="109" ht="14.25" spans="1:8">
+    </row>
+    <row r="109" ht="14.25" spans="1:9">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -3557,13 +3769,15 @@
       <c r="E109" s="1">
         <v>20042</v>
       </c>
-      <c r="F109" s="4">
-        <v>10</v>
-      </c>
-      <c r="G109" s="1"/>
+      <c r="F109" s="3">
+        <v>20</v>
+      </c>
       <c r="H109" s="1"/>
-    </row>
-    <row r="110" ht="14.25" spans="1:8">
+      <c r="I109" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" ht="14.25" spans="1:9">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -3579,13 +3793,15 @@
       <c r="E110" s="1">
         <v>20042</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="3">
+        <v>5</v>
+      </c>
+      <c r="H110" s="1"/>
+      <c r="I110" s="4">
         <v>1</v>
       </c>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-    </row>
-    <row r="111" ht="14.25" spans="1:8">
+    </row>
+    <row r="111" ht="14.25" spans="1:9">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -3601,13 +3817,15 @@
       <c r="E111" s="1">
         <v>20052</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="3">
         <v>4000</v>
       </c>
-      <c r="G111" s="1"/>
       <c r="H111" s="1"/>
-    </row>
-    <row r="112" ht="14.25" spans="1:8">
+      <c r="I111" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="112" ht="14.25" spans="1:9">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -3623,13 +3841,15 @@
       <c r="E112" s="1">
         <v>20052</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="3">
         <v>4000</v>
       </c>
-      <c r="G112" s="1"/>
       <c r="H112" s="1"/>
-    </row>
-    <row r="113" ht="14.25" spans="1:8">
+      <c r="I112" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="113" ht="14.25" spans="1:9">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -3645,13 +3865,15 @@
       <c r="E113" s="1">
         <v>20052</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="3">
         <v>1500</v>
       </c>
-      <c r="G113" s="1"/>
       <c r="H113" s="1"/>
-    </row>
-    <row r="114" ht="14.25" spans="1:8">
+      <c r="I113" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25" spans="1:9">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -3667,13 +3889,15 @@
       <c r="E114" s="1">
         <v>20052</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="3">
+        <v>450</v>
+      </c>
+      <c r="H114" s="1"/>
+      <c r="I114" s="4">
         <v>467</v>
       </c>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1"/>
-    </row>
-    <row r="115" ht="14.25" spans="1:8">
+    </row>
+    <row r="115" ht="14.25" spans="1:9">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -3689,13 +3913,15 @@
       <c r="E115" s="1">
         <v>20052</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="3">
+        <v>40</v>
+      </c>
+      <c r="H115" s="1"/>
+      <c r="I115" s="4">
         <v>30</v>
       </c>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-    </row>
-    <row r="116" ht="14.25" spans="1:8">
+    </row>
+    <row r="116" ht="14.25" spans="1:9">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -3711,13 +3937,15 @@
       <c r="E116" s="1">
         <v>20052</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="3">
+        <v>10</v>
+      </c>
+      <c r="H116" s="1"/>
+      <c r="I116" s="4">
         <v>3</v>
       </c>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-    </row>
-    <row r="117" ht="14.25" spans="1:8">
+    </row>
+    <row r="117" ht="14.25" spans="1:9">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -3733,13 +3961,15 @@
       <c r="E117" s="1">
         <v>20052</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="3">
         <v>6000</v>
       </c>
-      <c r="G117" s="1"/>
       <c r="H117" s="1"/>
-    </row>
-    <row r="118" ht="14.25" spans="1:8">
+      <c r="I117" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="118" ht="14.25" spans="1:9">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -3755,13 +3985,15 @@
       <c r="E118" s="1">
         <v>20052</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="3">
         <v>3000</v>
       </c>
-      <c r="G118" s="1"/>
       <c r="H118" s="1"/>
-    </row>
-    <row r="119" ht="14.25" spans="1:8">
+      <c r="I118" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="119" ht="14.25" spans="1:9">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -3777,13 +4009,15 @@
       <c r="E119" s="1">
         <v>20052</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="3">
         <v>700</v>
       </c>
-      <c r="G119" s="1"/>
       <c r="H119" s="1"/>
-    </row>
-    <row r="120" ht="14.25" spans="1:8">
+      <c r="I119" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="120" ht="14.25" spans="1:9">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -3799,13 +4033,15 @@
       <c r="E120" s="1">
         <v>20052</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="3">
+        <v>275</v>
+      </c>
+      <c r="H120" s="1"/>
+      <c r="I120" s="4">
         <v>289</v>
       </c>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
-    </row>
-    <row r="121" ht="14.25" spans="1:8">
+    </row>
+    <row r="121" ht="14.25" spans="1:9">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -3821,13 +4057,15 @@
       <c r="E121" s="1">
         <v>20052</v>
       </c>
-      <c r="F121" s="4">
-        <v>10</v>
-      </c>
-      <c r="G121" s="1"/>
+      <c r="F121" s="3">
+        <v>20</v>
+      </c>
       <c r="H121" s="1"/>
-    </row>
-    <row r="122" ht="14.25" spans="1:8">
+      <c r="I121" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" ht="14.25" spans="1:9">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -3843,13 +4081,15 @@
       <c r="E122" s="1">
         <v>20052</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="3">
+        <v>5</v>
+      </c>
+      <c r="H122" s="1"/>
+      <c r="I122" s="4">
         <v>1</v>
       </c>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-    </row>
-    <row r="123" ht="14.25" spans="1:8">
+    </row>
+    <row r="123" ht="14.25" spans="1:9">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -3865,13 +4105,15 @@
       <c r="E123" s="1">
         <v>20062</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="3">
         <v>4000</v>
       </c>
-      <c r="G123" s="1"/>
       <c r="H123" s="1"/>
-    </row>
-    <row r="124" ht="14.25" spans="1:8">
+      <c r="I123" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="124" ht="14.25" spans="1:9">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -3887,13 +4129,15 @@
       <c r="E124" s="1">
         <v>20062</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="3">
         <v>4000</v>
       </c>
-      <c r="G124" s="1"/>
       <c r="H124" s="1"/>
-    </row>
-    <row r="125" ht="14.25" spans="1:8">
+      <c r="I124" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="125" ht="14.25" spans="1:9">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -3909,13 +4153,15 @@
       <c r="E125" s="1">
         <v>20062</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="3">
         <v>1500</v>
       </c>
-      <c r="G125" s="1"/>
       <c r="H125" s="1"/>
-    </row>
-    <row r="126" ht="14.25" spans="1:8">
+      <c r="I125" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="126" ht="14.25" spans="1:9">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -3931,13 +4177,15 @@
       <c r="E126" s="1">
         <v>20062</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="3">
+        <v>450</v>
+      </c>
+      <c r="H126" s="1"/>
+      <c r="I126" s="4">
         <v>467</v>
       </c>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-    </row>
-    <row r="127" ht="14.25" spans="1:8">
+    </row>
+    <row r="127" ht="14.25" spans="1:9">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -3953,13 +4201,15 @@
       <c r="E127" s="1">
         <v>20062</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="3">
+        <v>40</v>
+      </c>
+      <c r="H127" s="1"/>
+      <c r="I127" s="4">
         <v>30</v>
       </c>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-    </row>
-    <row r="128" ht="14.25" spans="1:8">
+    </row>
+    <row r="128" ht="14.25" spans="1:9">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -3975,13 +4225,15 @@
       <c r="E128" s="1">
         <v>20062</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="3">
+        <v>10</v>
+      </c>
+      <c r="H128" s="1"/>
+      <c r="I128" s="4">
         <v>3</v>
       </c>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-    </row>
-    <row r="129" ht="14.25" spans="1:8">
+    </row>
+    <row r="129" ht="14.25" spans="1:9">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -3997,13 +4249,15 @@
       <c r="E129" s="1">
         <v>20062</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="3">
         <v>6000</v>
       </c>
-      <c r="G129" s="1"/>
       <c r="H129" s="1"/>
-    </row>
-    <row r="130" ht="14.25" spans="1:8">
+      <c r="I129" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="130" ht="14.25" spans="1:9">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -4019,13 +4273,15 @@
       <c r="E130" s="1">
         <v>20062</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="3">
         <v>3000</v>
       </c>
-      <c r="G130" s="1"/>
       <c r="H130" s="1"/>
-    </row>
-    <row r="131" ht="14.25" spans="1:8">
+      <c r="I130" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="131" ht="14.25" spans="1:9">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -4041,13 +4297,15 @@
       <c r="E131" s="1">
         <v>20062</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="3">
         <v>700</v>
       </c>
-      <c r="G131" s="1"/>
       <c r="H131" s="1"/>
-    </row>
-    <row r="132" ht="14.25" spans="1:8">
+      <c r="I131" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="132" ht="14.25" spans="1:9">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -4063,13 +4321,15 @@
       <c r="E132" s="1">
         <v>20062</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="3">
+        <v>275</v>
+      </c>
+      <c r="H132" s="1"/>
+      <c r="I132" s="4">
         <v>289</v>
       </c>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-    </row>
-    <row r="133" ht="14.25" spans="1:8">
+    </row>
+    <row r="133" ht="14.25" spans="1:9">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -4085,13 +4345,15 @@
       <c r="E133" s="1">
         <v>20062</v>
       </c>
-      <c r="F133" s="4">
-        <v>10</v>
-      </c>
-      <c r="G133" s="1"/>
+      <c r="F133" s="3">
+        <v>20</v>
+      </c>
       <c r="H133" s="1"/>
-    </row>
-    <row r="134" ht="14.25" spans="1:8">
+      <c r="I133" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" ht="14.25" spans="1:9">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -4107,13 +4369,15 @@
       <c r="E134" s="1">
         <v>20062</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="3">
+        <v>5</v>
+      </c>
+      <c r="H134" s="1"/>
+      <c r="I134" s="4">
         <v>1</v>
       </c>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-    </row>
-    <row r="135" ht="14.25" spans="1:8">
+    </row>
+    <row r="135" ht="14.25" spans="1:9">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -4129,13 +4393,15 @@
       <c r="E135" s="1">
         <v>20072</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="3">
         <v>4000</v>
       </c>
-      <c r="G135" s="1"/>
       <c r="H135" s="1"/>
-    </row>
-    <row r="136" ht="14.25" spans="1:8">
+      <c r="I135" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="136" ht="14.25" spans="1:9">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -4151,13 +4417,15 @@
       <c r="E136" s="1">
         <v>20072</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="3">
         <v>4000</v>
       </c>
-      <c r="G136" s="1"/>
       <c r="H136" s="1"/>
-    </row>
-    <row r="137" ht="14.25" spans="1:8">
+      <c r="I136" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="137" ht="14.25" spans="1:9">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -4173,13 +4441,15 @@
       <c r="E137" s="1">
         <v>20072</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="3">
         <v>1500</v>
       </c>
-      <c r="G137" s="1"/>
       <c r="H137" s="1"/>
-    </row>
-    <row r="138" ht="14.25" spans="1:8">
+      <c r="I137" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="138" ht="14.25" spans="1:9">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -4195,13 +4465,15 @@
       <c r="E138" s="1">
         <v>20072</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="3">
+        <v>450</v>
+      </c>
+      <c r="H138" s="1"/>
+      <c r="I138" s="4">
         <v>467</v>
       </c>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
-    </row>
-    <row r="139" ht="14.25" spans="1:8">
+    </row>
+    <row r="139" ht="14.25" spans="1:9">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -4217,13 +4489,15 @@
       <c r="E139" s="1">
         <v>20072</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="3">
+        <v>40</v>
+      </c>
+      <c r="H139" s="1"/>
+      <c r="I139" s="4">
         <v>30</v>
       </c>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-    </row>
-    <row r="140" ht="14.25" spans="1:8">
+    </row>
+    <row r="140" ht="14.25" spans="1:9">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -4239,13 +4513,15 @@
       <c r="E140" s="1">
         <v>20072</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="3">
+        <v>10</v>
+      </c>
+      <c r="H140" s="1"/>
+      <c r="I140" s="4">
         <v>3</v>
       </c>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-    </row>
-    <row r="141" ht="14.25" spans="1:8">
+    </row>
+    <row r="141" ht="14.25" spans="1:9">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -4261,13 +4537,15 @@
       <c r="E141" s="1">
         <v>20072</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="3">
         <v>6000</v>
       </c>
-      <c r="G141" s="1"/>
       <c r="H141" s="1"/>
-    </row>
-    <row r="142" ht="14.25" spans="1:8">
+      <c r="I141" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="142" ht="14.25" spans="1:9">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -4283,13 +4561,15 @@
       <c r="E142" s="1">
         <v>20072</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="3">
         <v>3000</v>
       </c>
-      <c r="G142" s="1"/>
       <c r="H142" s="1"/>
-    </row>
-    <row r="143" ht="14.25" spans="1:8">
+      <c r="I142" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="143" ht="14.25" spans="1:9">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -4305,13 +4585,15 @@
       <c r="E143" s="1">
         <v>20072</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="3">
         <v>700</v>
       </c>
-      <c r="G143" s="1"/>
       <c r="H143" s="1"/>
-    </row>
-    <row r="144" ht="14.25" spans="1:8">
+      <c r="I143" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="144" ht="14.25" spans="1:9">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -4327,13 +4609,15 @@
       <c r="E144" s="1">
         <v>20072</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="3">
+        <v>275</v>
+      </c>
+      <c r="H144" s="1"/>
+      <c r="I144" s="4">
         <v>289</v>
       </c>
-      <c r="G144" s="1"/>
-      <c r="H144" s="1"/>
-    </row>
-    <row r="145" ht="14.25" spans="1:8">
+    </row>
+    <row r="145" ht="14.25" spans="1:9">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -4349,13 +4633,15 @@
       <c r="E145" s="1">
         <v>20072</v>
       </c>
-      <c r="F145" s="4">
-        <v>10</v>
-      </c>
-      <c r="G145" s="1"/>
+      <c r="F145" s="3">
+        <v>20</v>
+      </c>
       <c r="H145" s="1"/>
-    </row>
-    <row r="146" ht="14.25" spans="1:8">
+      <c r="I145" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" ht="14.25" spans="1:9">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -4371,13 +4657,15 @@
       <c r="E146" s="1">
         <v>20072</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="3">
+        <v>5</v>
+      </c>
+      <c r="H146" s="1"/>
+      <c r="I146" s="4">
         <v>1</v>
       </c>
-      <c r="G146" s="1"/>
-      <c r="H146" s="1"/>
-    </row>
-    <row r="147" ht="14.25" spans="1:8">
+    </row>
+    <row r="147" ht="14.25" spans="1:9">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -4393,13 +4681,15 @@
       <c r="E147" s="1">
         <v>20082</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="3">
         <v>4000</v>
       </c>
-      <c r="G147" s="1"/>
       <c r="H147" s="1"/>
-    </row>
-    <row r="148" ht="14.25" spans="1:8">
+      <c r="I147" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="148" ht="14.25" spans="1:9">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -4415,13 +4705,15 @@
       <c r="E148" s="1">
         <v>20082</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="3">
         <v>4000</v>
       </c>
-      <c r="G148" s="1"/>
       <c r="H148" s="1"/>
-    </row>
-    <row r="149" ht="14.25" spans="1:8">
+      <c r="I148" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="149" ht="14.25" spans="1:9">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -4437,13 +4729,15 @@
       <c r="E149" s="1">
         <v>20082</v>
       </c>
-      <c r="F149" s="4">
+      <c r="F149" s="3">
         <v>1500</v>
       </c>
-      <c r="G149" s="1"/>
       <c r="H149" s="1"/>
-    </row>
-    <row r="150" ht="14.25" spans="1:8">
+      <c r="I149" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="150" ht="14.25" spans="1:9">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -4459,13 +4753,15 @@
       <c r="E150" s="1">
         <v>20082</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="3">
+        <v>450</v>
+      </c>
+      <c r="H150" s="1"/>
+      <c r="I150" s="4">
         <v>467</v>
       </c>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-    </row>
-    <row r="151" ht="14.25" spans="1:8">
+    </row>
+    <row r="151" ht="14.25" spans="1:9">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -4481,13 +4777,15 @@
       <c r="E151" s="1">
         <v>20082</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="3">
+        <v>40</v>
+      </c>
+      <c r="H151" s="1"/>
+      <c r="I151" s="4">
         <v>30</v>
       </c>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1"/>
-    </row>
-    <row r="152" ht="14.25" spans="1:8">
+    </row>
+    <row r="152" ht="14.25" spans="1:9">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -4503,13 +4801,15 @@
       <c r="E152" s="1">
         <v>20082</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="3">
+        <v>10</v>
+      </c>
+      <c r="H152" s="1"/>
+      <c r="I152" s="4">
         <v>3</v>
       </c>
-      <c r="G152" s="1"/>
-      <c r="H152" s="1"/>
-    </row>
-    <row r="153" ht="14.25" spans="1:8">
+    </row>
+    <row r="153" ht="14.25" spans="1:9">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -4525,13 +4825,15 @@
       <c r="E153" s="1">
         <v>20082</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="3">
         <v>6000</v>
       </c>
-      <c r="G153" s="1"/>
       <c r="H153" s="1"/>
-    </row>
-    <row r="154" ht="14.25" spans="1:8">
+      <c r="I153" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="154" ht="14.25" spans="1:9">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -4547,13 +4849,15 @@
       <c r="E154" s="1">
         <v>20082</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="3">
         <v>3000</v>
       </c>
-      <c r="G154" s="1"/>
       <c r="H154" s="1"/>
-    </row>
-    <row r="155" ht="14.25" spans="1:8">
+      <c r="I154" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="155" ht="14.25" spans="1:9">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -4569,13 +4873,15 @@
       <c r="E155" s="1">
         <v>20082</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="3">
         <v>700</v>
       </c>
-      <c r="G155" s="1"/>
       <c r="H155" s="1"/>
-    </row>
-    <row r="156" ht="14.25" spans="1:8">
+      <c r="I155" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="156" ht="14.25" spans="1:9">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -4591,13 +4897,15 @@
       <c r="E156" s="1">
         <v>20082</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="3">
+        <v>275</v>
+      </c>
+      <c r="H156" s="1"/>
+      <c r="I156" s="4">
         <v>289</v>
       </c>
-      <c r="G156" s="1"/>
-      <c r="H156" s="1"/>
-    </row>
-    <row r="157" ht="14.25" spans="1:8">
+    </row>
+    <row r="157" ht="14.25" spans="1:9">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -4613,13 +4921,15 @@
       <c r="E157" s="1">
         <v>20082</v>
       </c>
-      <c r="F157" s="4">
-        <v>10</v>
-      </c>
-      <c r="G157" s="1"/>
+      <c r="F157" s="3">
+        <v>20</v>
+      </c>
       <c r="H157" s="1"/>
-    </row>
-    <row r="158" ht="14.25" spans="1:8">
+      <c r="I157" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" ht="14.25" spans="1:9">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -4635,13 +4945,15 @@
       <c r="E158" s="1">
         <v>20082</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="3">
+        <v>5</v>
+      </c>
+      <c r="H158" s="1"/>
+      <c r="I158" s="4">
         <v>1</v>
       </c>
-      <c r="G158" s="1"/>
-      <c r="H158" s="1"/>
-    </row>
-    <row r="159" ht="14.25" spans="1:8">
+    </row>
+    <row r="159" ht="14.25" spans="1:9">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -4657,13 +4969,15 @@
       <c r="E159" s="1">
         <v>30013</v>
       </c>
-      <c r="F159" s="4">
+      <c r="F159" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H159" s="1"/>
+      <c r="I159" s="4">
         <v>1600</v>
       </c>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-    </row>
-    <row r="160" ht="14.25" spans="1:8">
+    </row>
+    <row r="160" ht="14.25" spans="1:9">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -4679,13 +4993,15 @@
       <c r="E160" s="1">
         <v>30013</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H160" s="1"/>
+      <c r="I160" s="4">
         <v>4400</v>
       </c>
-      <c r="G160" s="1"/>
-      <c r="H160" s="1"/>
-    </row>
-    <row r="161" ht="14.25" spans="1:8">
+    </row>
+    <row r="161" ht="14.25" spans="1:9">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -4701,13 +5017,15 @@
       <c r="E161" s="1">
         <v>30013</v>
       </c>
-      <c r="F161" s="4">
+      <c r="F161" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H161" s="1"/>
+      <c r="I161" s="4">
         <v>3000</v>
       </c>
-      <c r="G161" s="1"/>
-      <c r="H161" s="1"/>
-    </row>
-    <row r="162" ht="14.25" spans="1:8">
+    </row>
+    <row r="162" ht="14.25" spans="1:9">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -4723,13 +5041,15 @@
       <c r="E162" s="1">
         <v>30013</v>
       </c>
-      <c r="F162" s="4">
+      <c r="F162" s="3">
+        <v>850</v>
+      </c>
+      <c r="H162" s="1"/>
+      <c r="I162" s="4">
         <v>900</v>
       </c>
-      <c r="G162" s="1"/>
-      <c r="H162" s="1"/>
-    </row>
-    <row r="163" ht="14.25" spans="1:8">
+    </row>
+    <row r="163" ht="14.25" spans="1:9">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -4745,13 +5065,15 @@
       <c r="E163" s="1">
         <v>30013</v>
       </c>
-      <c r="F163" s="4">
+      <c r="F163" s="3">
+        <v>120</v>
+      </c>
+      <c r="H163" s="1"/>
+      <c r="I163" s="4">
         <v>90</v>
       </c>
-      <c r="G163" s="1"/>
-      <c r="H163" s="1"/>
-    </row>
-    <row r="164" ht="14.25" spans="1:8">
+    </row>
+    <row r="164" ht="14.25" spans="1:9">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -4767,13 +5089,15 @@
       <c r="E164" s="1">
         <v>30013</v>
       </c>
-      <c r="F164" s="4">
-        <v>10</v>
-      </c>
-      <c r="G164" s="1"/>
+      <c r="F164" s="3">
+        <v>30</v>
+      </c>
       <c r="H164" s="1"/>
-    </row>
-    <row r="165" ht="14.25" spans="1:8">
+      <c r="I164" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" ht="14.25" spans="1:9">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -4789,13 +5113,15 @@
       <c r="E165" s="1">
         <v>30013</v>
       </c>
-      <c r="F165" s="4">
+      <c r="F165" s="3">
         <v>4000</v>
       </c>
-      <c r="G165" s="1"/>
       <c r="H165" s="1"/>
-    </row>
-    <row r="166" ht="14.25" spans="1:8">
+      <c r="I165" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="166" ht="14.25" spans="1:9">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -4811,13 +5137,15 @@
       <c r="E166" s="1">
         <v>30013</v>
       </c>
-      <c r="F166" s="4">
+      <c r="F166" s="3">
         <v>4000</v>
       </c>
-      <c r="G166" s="1"/>
       <c r="H166" s="1"/>
-    </row>
-    <row r="167" ht="14.25" spans="1:8">
+      <c r="I166" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="167" ht="14.25" spans="1:9">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -4833,13 +5161,15 @@
       <c r="E167" s="1">
         <v>30013</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="3">
         <v>1500</v>
       </c>
-      <c r="G167" s="1"/>
       <c r="H167" s="1"/>
-    </row>
-    <row r="168" ht="14.25" spans="1:8">
+      <c r="I167" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="168" ht="14.25" spans="1:9">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -4855,13 +5185,15 @@
       <c r="E168" s="1">
         <v>30013</v>
       </c>
-      <c r="F168" s="4">
+      <c r="F168" s="3">
+        <v>450</v>
+      </c>
+      <c r="H168" s="1"/>
+      <c r="I168" s="4">
         <v>467</v>
       </c>
-      <c r="G168" s="1"/>
-      <c r="H168" s="1"/>
-    </row>
-    <row r="169" ht="14.25" spans="1:8">
+    </row>
+    <row r="169" ht="14.25" spans="1:9">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -4877,13 +5209,15 @@
       <c r="E169" s="1">
         <v>30013</v>
       </c>
-      <c r="F169" s="4">
+      <c r="F169" s="3">
+        <v>40</v>
+      </c>
+      <c r="H169" s="1"/>
+      <c r="I169" s="4">
         <v>30</v>
       </c>
-      <c r="G169" s="1"/>
-      <c r="H169" s="1"/>
-    </row>
-    <row r="170" ht="14.25" spans="1:8">
+    </row>
+    <row r="170" ht="14.25" spans="1:9">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -4899,13 +5233,15 @@
       <c r="E170" s="1">
         <v>30013</v>
       </c>
-      <c r="F170" s="4">
+      <c r="F170" s="3">
+        <v>10</v>
+      </c>
+      <c r="H170" s="1"/>
+      <c r="I170" s="4">
         <v>3</v>
       </c>
-      <c r="G170" s="1"/>
-      <c r="H170" s="1"/>
-    </row>
-    <row r="171" ht="14.25" spans="1:8">
+    </row>
+    <row r="171" ht="14.25" spans="1:9">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -4921,13 +5257,15 @@
       <c r="E171" s="1">
         <v>30013</v>
       </c>
-      <c r="F171" s="4">
+      <c r="F171" s="3">
         <v>6000</v>
       </c>
-      <c r="G171" s="1"/>
       <c r="H171" s="1"/>
-    </row>
-    <row r="172" ht="14.25" spans="1:8">
+      <c r="I171" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="172" ht="14.25" spans="1:9">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -4943,13 +5281,15 @@
       <c r="E172" s="1">
         <v>30013</v>
       </c>
-      <c r="F172" s="4">
+      <c r="F172" s="3">
         <v>3000</v>
       </c>
-      <c r="G172" s="1"/>
       <c r="H172" s="1"/>
-    </row>
-    <row r="173" ht="14.25" spans="1:8">
+      <c r="I172" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="173" ht="14.25" spans="1:9">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -4965,13 +5305,15 @@
       <c r="E173" s="1">
         <v>30013</v>
       </c>
-      <c r="F173" s="4">
+      <c r="F173" s="3">
         <v>700</v>
       </c>
-      <c r="G173" s="1"/>
       <c r="H173" s="1"/>
-    </row>
-    <row r="174" ht="14.25" spans="1:8">
+      <c r="I173" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="174" ht="14.25" spans="1:9">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -4987,13 +5329,15 @@
       <c r="E174" s="1">
         <v>30013</v>
       </c>
-      <c r="F174" s="4">
+      <c r="F174" s="3">
+        <v>275</v>
+      </c>
+      <c r="H174" s="1"/>
+      <c r="I174" s="4">
         <v>289</v>
       </c>
-      <c r="G174" s="1"/>
-      <c r="H174" s="1"/>
-    </row>
-    <row r="175" ht="14.25" spans="1:8">
+    </row>
+    <row r="175" ht="14.25" spans="1:9">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -5009,13 +5353,15 @@
       <c r="E175" s="1">
         <v>30013</v>
       </c>
-      <c r="F175" s="4">
-        <v>10</v>
-      </c>
-      <c r="G175" s="1"/>
+      <c r="F175" s="3">
+        <v>20</v>
+      </c>
       <c r="H175" s="1"/>
-    </row>
-    <row r="176" ht="14.25" spans="1:8">
+      <c r="I175" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" ht="14.25" spans="1:9">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -5031,13 +5377,15 @@
       <c r="E176" s="1">
         <v>30013</v>
       </c>
-      <c r="F176" s="4">
+      <c r="F176" s="3">
+        <v>5</v>
+      </c>
+      <c r="H176" s="1"/>
+      <c r="I176" s="4">
         <v>1</v>
       </c>
-      <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
-    </row>
-    <row r="177" ht="14.25" spans="1:8">
+    </row>
+    <row r="177" ht="14.25" spans="1:9">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -5053,13 +5401,15 @@
       <c r="E177" s="1">
         <v>30023</v>
       </c>
-      <c r="F177" s="4">
+      <c r="F177" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H177" s="1"/>
+      <c r="I177" s="4">
         <v>1600</v>
       </c>
-      <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
-    </row>
-    <row r="178" ht="14.25" spans="1:8">
+    </row>
+    <row r="178" ht="14.25" spans="1:9">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -5075,13 +5425,15 @@
       <c r="E178" s="1">
         <v>30023</v>
       </c>
-      <c r="F178" s="4">
+      <c r="F178" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H178" s="1"/>
+      <c r="I178" s="4">
         <v>4400</v>
       </c>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-    </row>
-    <row r="179" ht="14.25" spans="1:8">
+    </row>
+    <row r="179" ht="14.25" spans="1:9">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -5097,13 +5449,15 @@
       <c r="E179" s="1">
         <v>30023</v>
       </c>
-      <c r="F179" s="4">
+      <c r="F179" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H179" s="1"/>
+      <c r="I179" s="4">
         <v>3000</v>
       </c>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
-    </row>
-    <row r="180" ht="14.25" spans="1:8">
+    </row>
+    <row r="180" ht="14.25" spans="1:9">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -5119,13 +5473,15 @@
       <c r="E180" s="1">
         <v>30023</v>
       </c>
-      <c r="F180" s="4">
+      <c r="F180" s="3">
+        <v>850</v>
+      </c>
+      <c r="H180" s="1"/>
+      <c r="I180" s="4">
         <v>900</v>
       </c>
-      <c r="G180" s="1"/>
-      <c r="H180" s="1"/>
-    </row>
-    <row r="181" ht="14.25" spans="1:8">
+    </row>
+    <row r="181" ht="14.25" spans="1:9">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -5141,13 +5497,15 @@
       <c r="E181" s="1">
         <v>30023</v>
       </c>
-      <c r="F181" s="4">
+      <c r="F181" s="3">
+        <v>120</v>
+      </c>
+      <c r="H181" s="1"/>
+      <c r="I181" s="4">
         <v>90</v>
       </c>
-      <c r="G181" s="1"/>
-      <c r="H181" s="1"/>
-    </row>
-    <row r="182" ht="14.25" spans="1:8">
+    </row>
+    <row r="182" ht="14.25" spans="1:9">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -5163,13 +5521,15 @@
       <c r="E182" s="1">
         <v>30023</v>
       </c>
-      <c r="F182" s="4">
-        <v>10</v>
-      </c>
-      <c r="G182" s="1"/>
+      <c r="F182" s="3">
+        <v>30</v>
+      </c>
       <c r="H182" s="1"/>
-    </row>
-    <row r="183" ht="14.25" spans="1:8">
+      <c r="I182" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" ht="14.25" spans="1:9">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -5185,13 +5545,15 @@
       <c r="E183" s="1">
         <v>30023</v>
       </c>
-      <c r="F183" s="4">
+      <c r="F183" s="3">
         <v>4000</v>
       </c>
-      <c r="G183" s="1"/>
       <c r="H183" s="1"/>
-    </row>
-    <row r="184" ht="14.25" spans="1:8">
+      <c r="I183" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="184" ht="14.25" spans="1:9">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -5207,13 +5569,15 @@
       <c r="E184" s="1">
         <v>30023</v>
       </c>
-      <c r="F184" s="4">
+      <c r="F184" s="3">
         <v>4000</v>
       </c>
-      <c r="G184" s="1"/>
       <c r="H184" s="1"/>
-    </row>
-    <row r="185" ht="14.25" spans="1:8">
+      <c r="I184" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="185" ht="14.25" spans="1:9">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -5229,13 +5593,15 @@
       <c r="E185" s="1">
         <v>30023</v>
       </c>
-      <c r="F185" s="4">
+      <c r="F185" s="3">
         <v>1500</v>
       </c>
-      <c r="G185" s="1"/>
       <c r="H185" s="1"/>
-    </row>
-    <row r="186" ht="14.25" spans="1:8">
+      <c r="I185" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="186" ht="14.25" spans="1:9">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -5251,13 +5617,15 @@
       <c r="E186" s="1">
         <v>30023</v>
       </c>
-      <c r="F186" s="4">
+      <c r="F186" s="3">
+        <v>450</v>
+      </c>
+      <c r="H186" s="1"/>
+      <c r="I186" s="4">
         <v>467</v>
       </c>
-      <c r="G186" s="1"/>
-      <c r="H186" s="1"/>
-    </row>
-    <row r="187" ht="14.25" spans="1:8">
+    </row>
+    <row r="187" ht="14.25" spans="1:9">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -5273,13 +5641,15 @@
       <c r="E187" s="1">
         <v>30023</v>
       </c>
-      <c r="F187" s="4">
+      <c r="F187" s="3">
+        <v>40</v>
+      </c>
+      <c r="H187" s="1"/>
+      <c r="I187" s="4">
         <v>30</v>
       </c>
-      <c r="G187" s="1"/>
-      <c r="H187" s="1"/>
-    </row>
-    <row r="188" ht="14.25" spans="1:8">
+    </row>
+    <row r="188" ht="14.25" spans="1:9">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -5295,13 +5665,15 @@
       <c r="E188" s="1">
         <v>30023</v>
       </c>
-      <c r="F188" s="4">
+      <c r="F188" s="3">
+        <v>10</v>
+      </c>
+      <c r="H188" s="1"/>
+      <c r="I188" s="4">
         <v>3</v>
       </c>
-      <c r="G188" s="1"/>
-      <c r="H188" s="1"/>
-    </row>
-    <row r="189" ht="14.25" spans="1:8">
+    </row>
+    <row r="189" ht="14.25" spans="1:9">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -5317,13 +5689,15 @@
       <c r="E189" s="1">
         <v>30023</v>
       </c>
-      <c r="F189" s="4">
+      <c r="F189" s="3">
         <v>6000</v>
       </c>
-      <c r="G189" s="1"/>
       <c r="H189" s="1"/>
-    </row>
-    <row r="190" ht="14.25" spans="1:8">
+      <c r="I189" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="190" ht="14.25" spans="1:9">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -5339,13 +5713,15 @@
       <c r="E190" s="1">
         <v>30023</v>
       </c>
-      <c r="F190" s="4">
+      <c r="F190" s="3">
         <v>3000</v>
       </c>
-      <c r="G190" s="1"/>
       <c r="H190" s="1"/>
-    </row>
-    <row r="191" ht="14.25" spans="1:8">
+      <c r="I190" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="191" ht="14.25" spans="1:9">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -5361,13 +5737,15 @@
       <c r="E191" s="1">
         <v>30023</v>
       </c>
-      <c r="F191" s="4">
+      <c r="F191" s="3">
         <v>700</v>
       </c>
-      <c r="G191" s="1"/>
       <c r="H191" s="1"/>
-    </row>
-    <row r="192" ht="14.25" spans="1:8">
+      <c r="I191" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="192" ht="14.25" spans="1:9">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -5383,13 +5761,15 @@
       <c r="E192" s="1">
         <v>30023</v>
       </c>
-      <c r="F192" s="4">
+      <c r="F192" s="3">
+        <v>275</v>
+      </c>
+      <c r="H192" s="1"/>
+      <c r="I192" s="4">
         <v>289</v>
       </c>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
-    </row>
-    <row r="193" ht="14.25" spans="1:8">
+    </row>
+    <row r="193" ht="14.25" spans="1:9">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -5405,13 +5785,15 @@
       <c r="E193" s="1">
         <v>30023</v>
       </c>
-      <c r="F193" s="4">
-        <v>10</v>
-      </c>
-      <c r="G193" s="1"/>
+      <c r="F193" s="3">
+        <v>20</v>
+      </c>
       <c r="H193" s="1"/>
-    </row>
-    <row r="194" ht="14.25" spans="1:8">
+      <c r="I193" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25" spans="1:9">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -5427,13 +5809,15 @@
       <c r="E194" s="1">
         <v>30023</v>
       </c>
-      <c r="F194" s="4">
+      <c r="F194" s="3">
+        <v>5</v>
+      </c>
+      <c r="H194" s="1"/>
+      <c r="I194" s="4">
         <v>1</v>
       </c>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1"/>
-    </row>
-    <row r="195" ht="14.25" spans="1:8">
+    </row>
+    <row r="195" ht="14.25" spans="1:9">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -5449,13 +5833,15 @@
       <c r="E195" s="1">
         <v>30033</v>
       </c>
-      <c r="F195" s="4">
+      <c r="F195" s="3">
         <v>0</v>
       </c>
-      <c r="G195" s="1"/>
       <c r="H195" s="1"/>
-    </row>
-    <row r="196" ht="14.25" spans="1:8">
+      <c r="I195" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25" spans="1:9">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -5471,13 +5857,15 @@
       <c r="E196" s="1">
         <v>30033</v>
       </c>
-      <c r="F196" s="4">
+      <c r="F196" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H196" s="1"/>
+      <c r="I196" s="4">
         <v>5238</v>
       </c>
-      <c r="G196" s="1"/>
-      <c r="H196" s="1"/>
-    </row>
-    <row r="197" ht="14.25" spans="1:8">
+    </row>
+    <row r="197" ht="14.25" spans="1:9">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -5493,13 +5881,15 @@
       <c r="E197" s="1">
         <v>30033</v>
       </c>
-      <c r="F197" s="4">
+      <c r="F197" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H197" s="1"/>
+      <c r="I197" s="4">
         <v>3571</v>
       </c>
-      <c r="G197" s="1"/>
-      <c r="H197" s="1"/>
-    </row>
-    <row r="198" ht="14.25" spans="1:8">
+    </row>
+    <row r="198" ht="14.25" spans="1:9">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -5515,13 +5905,15 @@
       <c r="E198" s="1">
         <v>30033</v>
       </c>
-      <c r="F198" s="4">
+      <c r="F198" s="3">
+        <v>850</v>
+      </c>
+      <c r="H198" s="1"/>
+      <c r="I198" s="4">
         <v>1071</v>
       </c>
-      <c r="G198" s="1"/>
-      <c r="H198" s="1"/>
-    </row>
-    <row r="199" ht="14.25" spans="1:8">
+    </row>
+    <row r="199" ht="14.25" spans="1:9">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -5537,13 +5929,15 @@
       <c r="E199" s="1">
         <v>30033</v>
       </c>
-      <c r="F199" s="4">
+      <c r="F199" s="3">
+        <v>120</v>
+      </c>
+      <c r="H199" s="1"/>
+      <c r="I199" s="4">
         <v>107</v>
       </c>
-      <c r="G199" s="1"/>
-      <c r="H199" s="1"/>
-    </row>
-    <row r="200" ht="14.25" spans="1:8">
+    </row>
+    <row r="200" ht="14.25" spans="1:9">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -5559,13 +5953,15 @@
       <c r="E200" s="1">
         <v>30033</v>
       </c>
-      <c r="F200" s="4">
+      <c r="F200" s="3">
+        <v>30</v>
+      </c>
+      <c r="H200" s="1"/>
+      <c r="I200" s="4">
         <v>12</v>
       </c>
-      <c r="G200" s="1"/>
-      <c r="H200" s="1"/>
-    </row>
-    <row r="201" ht="14.25" spans="1:8">
+    </row>
+    <row r="201" ht="14.25" spans="1:9">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -5581,13 +5977,15 @@
       <c r="E201" s="1">
         <v>30033</v>
       </c>
-      <c r="F201" s="4">
+      <c r="F201" s="3">
         <v>0</v>
       </c>
-      <c r="G201" s="1"/>
       <c r="H201" s="1"/>
-    </row>
-    <row r="202" ht="14.25" spans="1:8">
+      <c r="I201" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25" spans="1:9">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -5603,13 +6001,15 @@
       <c r="E202" s="1">
         <v>30033</v>
       </c>
-      <c r="F202" s="4">
+      <c r="F202" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H202" s="1"/>
+      <c r="I202" s="4">
         <v>6667</v>
       </c>
-      <c r="G202" s="1"/>
-      <c r="H202" s="1"/>
-    </row>
-    <row r="203" ht="14.25" spans="1:8">
+    </row>
+    <row r="203" ht="14.25" spans="1:9">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -5625,13 +6025,15 @@
       <c r="E203" s="1">
         <v>30033</v>
       </c>
-      <c r="F203" s="4">
+      <c r="F203" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H203" s="1"/>
+      <c r="I203" s="4">
         <v>2500</v>
       </c>
-      <c r="G203" s="1"/>
-      <c r="H203" s="1"/>
-    </row>
-    <row r="204" ht="14.25" spans="1:8">
+    </row>
+    <row r="204" ht="14.25" spans="1:9">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -5647,13 +6049,15 @@
       <c r="E204" s="1">
         <v>30033</v>
       </c>
-      <c r="F204" s="4">
+      <c r="F204" s="3">
+        <v>450</v>
+      </c>
+      <c r="H204" s="1"/>
+      <c r="I204" s="4">
         <v>778</v>
       </c>
-      <c r="G204" s="1"/>
-      <c r="H204" s="1"/>
-    </row>
-    <row r="205" ht="14.25" spans="1:8">
+    </row>
+    <row r="205" ht="14.25" spans="1:9">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -5669,13 +6073,15 @@
       <c r="E205" s="1">
         <v>30033</v>
       </c>
-      <c r="F205" s="4">
+      <c r="F205" s="3">
+        <v>40</v>
+      </c>
+      <c r="H205" s="1"/>
+      <c r="I205" s="4">
         <v>50</v>
       </c>
-      <c r="G205" s="1"/>
-      <c r="H205" s="1"/>
-    </row>
-    <row r="206" ht="14.25" spans="1:8">
+    </row>
+    <row r="206" ht="14.25" spans="1:9">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -5691,13 +6097,15 @@
       <c r="E206" s="1">
         <v>30033</v>
       </c>
-      <c r="F206" s="4">
+      <c r="F206" s="3">
+        <v>10</v>
+      </c>
+      <c r="H206" s="1"/>
+      <c r="I206" s="4">
         <v>5</v>
       </c>
-      <c r="G206" s="1"/>
-      <c r="H206" s="1"/>
-    </row>
-    <row r="207" ht="14.25" spans="1:8">
+    </row>
+    <row r="207" ht="14.25" spans="1:9">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -5713,13 +6121,15 @@
       <c r="E207" s="1">
         <v>30033</v>
       </c>
-      <c r="F207" s="4">
+      <c r="F207" s="3">
         <v>0</v>
       </c>
-      <c r="G207" s="1"/>
       <c r="H207" s="1"/>
-    </row>
-    <row r="208" ht="14.25" spans="1:8">
+      <c r="I207" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" ht="14.25" spans="1:9">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -5735,13 +6145,15 @@
       <c r="E208" s="1">
         <v>30033</v>
       </c>
-      <c r="F208" s="4">
+      <c r="F208" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H208" s="1"/>
+      <c r="I208" s="4">
         <v>7500</v>
       </c>
-      <c r="G208" s="1"/>
-      <c r="H208" s="1"/>
-    </row>
-    <row r="209" ht="14.25" spans="1:8">
+    </row>
+    <row r="209" ht="14.25" spans="1:9">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -5757,13 +6169,15 @@
       <c r="E209" s="1">
         <v>30033</v>
       </c>
-      <c r="F209" s="4">
+      <c r="F209" s="3">
+        <v>700</v>
+      </c>
+      <c r="H209" s="1"/>
+      <c r="I209" s="4">
         <v>1750</v>
       </c>
-      <c r="G209" s="1"/>
-      <c r="H209" s="1"/>
-    </row>
-    <row r="210" ht="14.25" spans="1:8">
+    </row>
+    <row r="210" ht="14.25" spans="1:9">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -5779,13 +6193,15 @@
       <c r="E210" s="1">
         <v>30033</v>
       </c>
-      <c r="F210" s="4">
+      <c r="F210" s="3">
+        <v>275</v>
+      </c>
+      <c r="H210" s="1"/>
+      <c r="I210" s="4">
         <v>723</v>
       </c>
-      <c r="G210" s="1"/>
-      <c r="H210" s="1"/>
-    </row>
-    <row r="211" ht="14.25" spans="1:8">
+    </row>
+    <row r="211" ht="14.25" spans="1:9">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -5801,13 +6217,15 @@
       <c r="E211" s="1">
         <v>30033</v>
       </c>
-      <c r="F211" s="4">
+      <c r="F211" s="3">
+        <v>20</v>
+      </c>
+      <c r="H211" s="1"/>
+      <c r="I211" s="4">
         <v>25</v>
       </c>
-      <c r="G211" s="1"/>
-      <c r="H211" s="1"/>
-    </row>
-    <row r="212" ht="14.25" spans="1:8">
+    </row>
+    <row r="212" ht="14.25" spans="1:9">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -5823,13 +6241,15 @@
       <c r="E212" s="1">
         <v>30033</v>
       </c>
-      <c r="F212" s="4">
+      <c r="F212" s="3">
+        <v>5</v>
+      </c>
+      <c r="H212" s="1"/>
+      <c r="I212" s="4">
         <v>3</v>
       </c>
-      <c r="G212" s="1"/>
-      <c r="H212" s="1"/>
-    </row>
-    <row r="213" ht="14.25" spans="1:8">
+    </row>
+    <row r="213" ht="14.25" spans="1:9">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -5845,13 +6265,15 @@
       <c r="E213" s="1">
         <v>30043</v>
       </c>
-      <c r="F213" s="4">
+      <c r="F213" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H213" s="1"/>
+      <c r="I213" s="4">
         <v>1600</v>
       </c>
-      <c r="G213" s="1"/>
-      <c r="H213" s="1"/>
-    </row>
-    <row r="214" ht="14.25" spans="1:8">
+    </row>
+    <row r="214" ht="14.25" spans="1:9">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -5867,13 +6289,15 @@
       <c r="E214" s="1">
         <v>30043</v>
       </c>
-      <c r="F214" s="4">
+      <c r="F214" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H214" s="1"/>
+      <c r="I214" s="4">
         <v>4400</v>
       </c>
-      <c r="G214" s="1"/>
-      <c r="H214" s="1"/>
-    </row>
-    <row r="215" ht="14.25" spans="1:8">
+    </row>
+    <row r="215" ht="14.25" spans="1:9">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -5889,13 +6313,15 @@
       <c r="E215" s="1">
         <v>30043</v>
       </c>
-      <c r="F215" s="4">
+      <c r="F215" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H215" s="1"/>
+      <c r="I215" s="4">
         <v>3000</v>
       </c>
-      <c r="G215" s="1"/>
-      <c r="H215" s="1"/>
-    </row>
-    <row r="216" ht="14.25" spans="1:8">
+    </row>
+    <row r="216" ht="14.25" spans="1:9">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -5911,13 +6337,15 @@
       <c r="E216" s="1">
         <v>30043</v>
       </c>
-      <c r="F216" s="4">
+      <c r="F216" s="3">
+        <v>850</v>
+      </c>
+      <c r="H216" s="1"/>
+      <c r="I216" s="4">
         <v>900</v>
       </c>
-      <c r="G216" s="1"/>
-      <c r="H216" s="1"/>
-    </row>
-    <row r="217" ht="14.25" spans="1:8">
+    </row>
+    <row r="217" ht="14.25" spans="1:9">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -5933,13 +6361,15 @@
       <c r="E217" s="1">
         <v>30043</v>
       </c>
-      <c r="F217" s="4">
+      <c r="F217" s="3">
+        <v>120</v>
+      </c>
+      <c r="H217" s="1"/>
+      <c r="I217" s="4">
         <v>90</v>
       </c>
-      <c r="G217" s="1"/>
-      <c r="H217" s="1"/>
-    </row>
-    <row r="218" ht="14.25" spans="1:8">
+    </row>
+    <row r="218" ht="14.25" spans="1:9">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -5955,13 +6385,15 @@
       <c r="E218" s="1">
         <v>30043</v>
       </c>
-      <c r="F218" s="4">
-        <v>10</v>
-      </c>
-      <c r="G218" s="1"/>
+      <c r="F218" s="3">
+        <v>30</v>
+      </c>
       <c r="H218" s="1"/>
-    </row>
-    <row r="219" ht="14.25" spans="1:8">
+      <c r="I218" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="219" ht="14.25" spans="1:9">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -5977,13 +6409,15 @@
       <c r="E219" s="1">
         <v>30043</v>
       </c>
-      <c r="F219" s="4">
+      <c r="F219" s="3">
         <v>4000</v>
       </c>
-      <c r="G219" s="1"/>
       <c r="H219" s="1"/>
-    </row>
-    <row r="220" ht="14.25" spans="1:8">
+      <c r="I219" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="220" ht="14.25" spans="1:9">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -5999,13 +6433,15 @@
       <c r="E220" s="1">
         <v>30043</v>
       </c>
-      <c r="F220" s="4">
+      <c r="F220" s="3">
         <v>4000</v>
       </c>
-      <c r="G220" s="1"/>
       <c r="H220" s="1"/>
-    </row>
-    <row r="221" ht="14.25" spans="1:8">
+      <c r="I220" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="221" ht="14.25" spans="1:9">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -6021,13 +6457,15 @@
       <c r="E221" s="1">
         <v>30043</v>
       </c>
-      <c r="F221" s="4">
+      <c r="F221" s="3">
         <v>1500</v>
       </c>
-      <c r="G221" s="1"/>
       <c r="H221" s="1"/>
-    </row>
-    <row r="222" ht="14.25" spans="1:8">
+      <c r="I221" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="222" ht="14.25" spans="1:9">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -6043,13 +6481,15 @@
       <c r="E222" s="1">
         <v>30043</v>
       </c>
-      <c r="F222" s="4">
+      <c r="F222" s="3">
+        <v>450</v>
+      </c>
+      <c r="H222" s="1"/>
+      <c r="I222" s="4">
         <v>467</v>
       </c>
-      <c r="G222" s="1"/>
-      <c r="H222" s="1"/>
-    </row>
-    <row r="223" ht="14.25" spans="1:8">
+    </row>
+    <row r="223" ht="14.25" spans="1:9">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -6065,13 +6505,15 @@
       <c r="E223" s="1">
         <v>30043</v>
       </c>
-      <c r="F223" s="4">
+      <c r="F223" s="3">
+        <v>40</v>
+      </c>
+      <c r="H223" s="1"/>
+      <c r="I223" s="4">
         <v>30</v>
       </c>
-      <c r="G223" s="1"/>
-      <c r="H223" s="1"/>
-    </row>
-    <row r="224" ht="14.25" spans="1:8">
+    </row>
+    <row r="224" ht="14.25" spans="1:9">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -6087,13 +6529,15 @@
       <c r="E224" s="1">
         <v>30043</v>
       </c>
-      <c r="F224" s="4">
+      <c r="F224" s="3">
+        <v>10</v>
+      </c>
+      <c r="H224" s="1"/>
+      <c r="I224" s="4">
         <v>3</v>
       </c>
-      <c r="G224" s="1"/>
-      <c r="H224" s="1"/>
-    </row>
-    <row r="225" ht="14.25" spans="1:8">
+    </row>
+    <row r="225" ht="14.25" spans="1:9">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -6109,13 +6553,15 @@
       <c r="E225" s="1">
         <v>30043</v>
       </c>
-      <c r="F225" s="4">
+      <c r="F225" s="3">
         <v>6000</v>
       </c>
-      <c r="G225" s="1"/>
       <c r="H225" s="1"/>
-    </row>
-    <row r="226" ht="14.25" spans="1:8">
+      <c r="I225" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="226" ht="14.25" spans="1:9">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -6131,13 +6577,15 @@
       <c r="E226" s="1">
         <v>30043</v>
       </c>
-      <c r="F226" s="4">
+      <c r="F226" s="3">
         <v>3000</v>
       </c>
-      <c r="G226" s="1"/>
       <c r="H226" s="1"/>
-    </row>
-    <row r="227" ht="14.25" spans="1:8">
+      <c r="I226" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="227" ht="14.25" spans="1:9">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -6153,13 +6601,15 @@
       <c r="E227" s="1">
         <v>30043</v>
       </c>
-      <c r="F227" s="4">
+      <c r="F227" s="3">
         <v>700</v>
       </c>
-      <c r="G227" s="1"/>
       <c r="H227" s="1"/>
-    </row>
-    <row r="228" ht="14.25" spans="1:8">
+      <c r="I227" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="228" ht="14.25" spans="1:9">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -6175,13 +6625,15 @@
       <c r="E228" s="1">
         <v>30043</v>
       </c>
-      <c r="F228" s="4">
+      <c r="F228" s="3">
+        <v>275</v>
+      </c>
+      <c r="H228" s="1"/>
+      <c r="I228" s="4">
         <v>289</v>
       </c>
-      <c r="G228" s="1"/>
-      <c r="H228" s="1"/>
-    </row>
-    <row r="229" ht="14.25" spans="1:8">
+    </row>
+    <row r="229" ht="14.25" spans="1:9">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -6197,13 +6649,15 @@
       <c r="E229" s="1">
         <v>30043</v>
       </c>
-      <c r="F229" s="4">
-        <v>10</v>
-      </c>
-      <c r="G229" s="1"/>
+      <c r="F229" s="3">
+        <v>20</v>
+      </c>
       <c r="H229" s="1"/>
-    </row>
-    <row r="230" ht="14.25" spans="1:8">
+      <c r="I229" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230" ht="14.25" spans="1:9">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -6219,13 +6673,15 @@
       <c r="E230" s="1">
         <v>30043</v>
       </c>
-      <c r="F230" s="4">
+      <c r="F230" s="3">
+        <v>5</v>
+      </c>
+      <c r="H230" s="1"/>
+      <c r="I230" s="4">
         <v>1</v>
       </c>
-      <c r="G230" s="1"/>
-      <c r="H230" s="1"/>
-    </row>
-    <row r="231" ht="14.25" spans="1:8">
+    </row>
+    <row r="231" ht="14.25" spans="1:9">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -6241,13 +6697,15 @@
       <c r="E231" s="1">
         <v>30053</v>
       </c>
-      <c r="F231" s="4">
+      <c r="F231" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H231" s="1"/>
+      <c r="I231" s="4">
         <v>1600</v>
       </c>
-      <c r="G231" s="1"/>
-      <c r="H231" s="1"/>
-    </row>
-    <row r="232" ht="14.25" spans="1:8">
+    </row>
+    <row r="232" ht="14.25" spans="1:9">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -6263,13 +6721,15 @@
       <c r="E232" s="1">
         <v>30053</v>
       </c>
-      <c r="F232" s="4">
+      <c r="F232" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H232" s="1"/>
+      <c r="I232" s="4">
         <v>4400</v>
       </c>
-      <c r="G232" s="1"/>
-      <c r="H232" s="1"/>
-    </row>
-    <row r="233" ht="14.25" spans="1:8">
+    </row>
+    <row r="233" ht="14.25" spans="1:9">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -6285,13 +6745,15 @@
       <c r="E233" s="1">
         <v>30053</v>
       </c>
-      <c r="F233" s="4">
+      <c r="F233" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H233" s="1"/>
+      <c r="I233" s="4">
         <v>3000</v>
       </c>
-      <c r="G233" s="1"/>
-      <c r="H233" s="1"/>
-    </row>
-    <row r="234" ht="14.25" spans="1:8">
+    </row>
+    <row r="234" ht="14.25" spans="1:9">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -6307,13 +6769,15 @@
       <c r="E234" s="1">
         <v>30053</v>
       </c>
-      <c r="F234" s="4">
+      <c r="F234" s="3">
+        <v>850</v>
+      </c>
+      <c r="H234" s="1"/>
+      <c r="I234" s="4">
         <v>900</v>
       </c>
-      <c r="G234" s="1"/>
-      <c r="H234" s="1"/>
-    </row>
-    <row r="235" ht="14.25" spans="1:8">
+    </row>
+    <row r="235" ht="14.25" spans="1:9">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -6329,13 +6793,15 @@
       <c r="E235" s="1">
         <v>30053</v>
       </c>
-      <c r="F235" s="4">
+      <c r="F235" s="3">
+        <v>120</v>
+      </c>
+      <c r="H235" s="1"/>
+      <c r="I235" s="4">
         <v>90</v>
       </c>
-      <c r="G235" s="1"/>
-      <c r="H235" s="1"/>
-    </row>
-    <row r="236" ht="14.25" spans="1:8">
+    </row>
+    <row r="236" ht="14.25" spans="1:9">
       <c r="A236" s="1">
         <v>234</v>
       </c>
@@ -6351,13 +6817,15 @@
       <c r="E236" s="1">
         <v>30053</v>
       </c>
-      <c r="F236" s="4">
-        <v>10</v>
-      </c>
-      <c r="G236" s="1"/>
+      <c r="F236" s="3">
+        <v>30</v>
+      </c>
       <c r="H236" s="1"/>
-    </row>
-    <row r="237" ht="14.25" spans="1:8">
+      <c r="I236" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="237" ht="14.25" spans="1:9">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -6373,13 +6841,15 @@
       <c r="E237" s="1">
         <v>30053</v>
       </c>
-      <c r="F237" s="4">
+      <c r="F237" s="3">
         <v>4000</v>
       </c>
-      <c r="G237" s="1"/>
       <c r="H237" s="1"/>
-    </row>
-    <row r="238" ht="14.25" spans="1:8">
+      <c r="I237" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="238" ht="14.25" spans="1:9">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -6395,13 +6865,15 @@
       <c r="E238" s="1">
         <v>30053</v>
       </c>
-      <c r="F238" s="4">
+      <c r="F238" s="3">
         <v>4000</v>
       </c>
-      <c r="G238" s="1"/>
       <c r="H238" s="1"/>
-    </row>
-    <row r="239" ht="14.25" spans="1:8">
+      <c r="I238" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="239" ht="14.25" spans="1:9">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -6417,13 +6889,15 @@
       <c r="E239" s="1">
         <v>30053</v>
       </c>
-      <c r="F239" s="4">
+      <c r="F239" s="3">
         <v>1500</v>
       </c>
-      <c r="G239" s="1"/>
       <c r="H239" s="1"/>
-    </row>
-    <row r="240" ht="14.25" spans="1:8">
+      <c r="I239" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="240" ht="14.25" spans="1:9">
       <c r="A240" s="1">
         <v>238</v>
       </c>
@@ -6439,13 +6913,15 @@
       <c r="E240" s="1">
         <v>30053</v>
       </c>
-      <c r="F240" s="4">
+      <c r="F240" s="3">
+        <v>450</v>
+      </c>
+      <c r="H240" s="1"/>
+      <c r="I240" s="4">
         <v>467</v>
       </c>
-      <c r="G240" s="1"/>
-      <c r="H240" s="1"/>
-    </row>
-    <row r="241" ht="14.25" spans="1:8">
+    </row>
+    <row r="241" ht="14.25" spans="1:9">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -6461,13 +6937,15 @@
       <c r="E241" s="1">
         <v>30053</v>
       </c>
-      <c r="F241" s="4">
+      <c r="F241" s="3">
+        <v>40</v>
+      </c>
+      <c r="H241" s="1"/>
+      <c r="I241" s="4">
         <v>30</v>
       </c>
-      <c r="G241" s="1"/>
-      <c r="H241" s="1"/>
-    </row>
-    <row r="242" ht="14.25" spans="1:8">
+    </row>
+    <row r="242" ht="14.25" spans="1:9">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -6483,13 +6961,15 @@
       <c r="E242" s="1">
         <v>30053</v>
       </c>
-      <c r="F242" s="4">
+      <c r="F242" s="3">
+        <v>10</v>
+      </c>
+      <c r="H242" s="1"/>
+      <c r="I242" s="4">
         <v>3</v>
       </c>
-      <c r="G242" s="1"/>
-      <c r="H242" s="1"/>
-    </row>
-    <row r="243" ht="14.25" spans="1:8">
+    </row>
+    <row r="243" ht="14.25" spans="1:9">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -6505,13 +6985,15 @@
       <c r="E243" s="1">
         <v>30053</v>
       </c>
-      <c r="F243" s="4">
+      <c r="F243" s="3">
         <v>6000</v>
       </c>
-      <c r="G243" s="1"/>
       <c r="H243" s="1"/>
-    </row>
-    <row r="244" ht="14.25" spans="1:8">
+      <c r="I243" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="244" ht="14.25" spans="1:9">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -6527,13 +7009,15 @@
       <c r="E244" s="1">
         <v>30053</v>
       </c>
-      <c r="F244" s="4">
+      <c r="F244" s="3">
         <v>3000</v>
       </c>
-      <c r="G244" s="1"/>
       <c r="H244" s="1"/>
-    </row>
-    <row r="245" ht="14.25" spans="1:8">
+      <c r="I244" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="245" ht="14.25" spans="1:9">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -6549,13 +7033,15 @@
       <c r="E245" s="1">
         <v>30053</v>
       </c>
-      <c r="F245" s="4">
+      <c r="F245" s="3">
         <v>700</v>
       </c>
-      <c r="G245" s="1"/>
       <c r="H245" s="1"/>
-    </row>
-    <row r="246" ht="14.25" spans="1:8">
+      <c r="I245" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="246" ht="14.25" spans="1:9">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -6571,13 +7057,15 @@
       <c r="E246" s="1">
         <v>30053</v>
       </c>
-      <c r="F246" s="4">
+      <c r="F246" s="3">
+        <v>275</v>
+      </c>
+      <c r="H246" s="1"/>
+      <c r="I246" s="4">
         <v>289</v>
       </c>
-      <c r="G246" s="1"/>
-      <c r="H246" s="1"/>
-    </row>
-    <row r="247" ht="14.25" spans="1:8">
+    </row>
+    <row r="247" ht="14.25" spans="1:9">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -6593,13 +7081,15 @@
       <c r="E247" s="1">
         <v>30053</v>
       </c>
-      <c r="F247" s="4">
-        <v>10</v>
-      </c>
-      <c r="G247" s="1"/>
+      <c r="F247" s="3">
+        <v>20</v>
+      </c>
       <c r="H247" s="1"/>
-    </row>
-    <row r="248" ht="14.25" spans="1:8">
+      <c r="I247" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" ht="14.25" spans="1:9">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -6615,13 +7105,15 @@
       <c r="E248" s="1">
         <v>30053</v>
       </c>
-      <c r="F248" s="4">
+      <c r="F248" s="3">
+        <v>5</v>
+      </c>
+      <c r="H248" s="1"/>
+      <c r="I248" s="4">
         <v>1</v>
       </c>
-      <c r="G248" s="1"/>
-      <c r="H248" s="1"/>
-    </row>
-    <row r="249" ht="14.25" spans="1:8">
+    </row>
+    <row r="249" ht="14.25" spans="1:9">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -6637,13 +7129,15 @@
       <c r="E249" s="1">
         <v>30063</v>
       </c>
-      <c r="F249" s="4">
+      <c r="F249" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H249" s="1"/>
+      <c r="I249" s="4">
         <v>1600</v>
       </c>
-      <c r="G249" s="1"/>
-      <c r="H249" s="1"/>
-    </row>
-    <row r="250" ht="14.25" spans="1:8">
+    </row>
+    <row r="250" ht="14.25" spans="1:9">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -6659,13 +7153,15 @@
       <c r="E250" s="1">
         <v>30063</v>
       </c>
-      <c r="F250" s="4">
+      <c r="F250" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H250" s="1"/>
+      <c r="I250" s="4">
         <v>4400</v>
       </c>
-      <c r="G250" s="1"/>
-      <c r="H250" s="1"/>
-    </row>
-    <row r="251" ht="14.25" spans="1:8">
+    </row>
+    <row r="251" ht="14.25" spans="1:9">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -6681,13 +7177,15 @@
       <c r="E251" s="1">
         <v>30063</v>
       </c>
-      <c r="F251" s="4">
+      <c r="F251" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H251" s="1"/>
+      <c r="I251" s="4">
         <v>3000</v>
       </c>
-      <c r="G251" s="1"/>
-      <c r="H251" s="1"/>
-    </row>
-    <row r="252" ht="14.25" spans="1:8">
+    </row>
+    <row r="252" ht="14.25" spans="1:9">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -6703,13 +7201,15 @@
       <c r="E252" s="1">
         <v>30063</v>
       </c>
-      <c r="F252" s="4">
+      <c r="F252" s="3">
+        <v>850</v>
+      </c>
+      <c r="H252" s="1"/>
+      <c r="I252" s="4">
         <v>900</v>
       </c>
-      <c r="G252" s="1"/>
-      <c r="H252" s="1"/>
-    </row>
-    <row r="253" ht="14.25" spans="1:8">
+    </row>
+    <row r="253" ht="14.25" spans="1:9">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -6725,13 +7225,15 @@
       <c r="E253" s="1">
         <v>30063</v>
       </c>
-      <c r="F253" s="4">
+      <c r="F253" s="3">
+        <v>120</v>
+      </c>
+      <c r="H253" s="1"/>
+      <c r="I253" s="4">
         <v>90</v>
       </c>
-      <c r="G253" s="1"/>
-      <c r="H253" s="1"/>
-    </row>
-    <row r="254" ht="14.25" spans="1:8">
+    </row>
+    <row r="254" ht="14.25" spans="1:9">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -6747,13 +7249,15 @@
       <c r="E254" s="1">
         <v>30063</v>
       </c>
-      <c r="F254" s="4">
-        <v>10</v>
-      </c>
-      <c r="G254" s="1"/>
+      <c r="F254" s="3">
+        <v>30</v>
+      </c>
       <c r="H254" s="1"/>
-    </row>
-    <row r="255" ht="14.25" spans="1:8">
+      <c r="I254" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="255" ht="14.25" spans="1:9">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -6769,13 +7273,15 @@
       <c r="E255" s="1">
         <v>30063</v>
       </c>
-      <c r="F255" s="4">
+      <c r="F255" s="3">
         <v>4000</v>
       </c>
-      <c r="G255" s="1"/>
       <c r="H255" s="1"/>
-    </row>
-    <row r="256" ht="14.25" spans="1:8">
+      <c r="I255" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="256" ht="14.25" spans="1:9">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -6791,13 +7297,15 @@
       <c r="E256" s="1">
         <v>30063</v>
       </c>
-      <c r="F256" s="4">
+      <c r="F256" s="3">
         <v>4000</v>
       </c>
-      <c r="G256" s="1"/>
       <c r="H256" s="1"/>
-    </row>
-    <row r="257" ht="14.25" spans="1:8">
+      <c r="I256" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="257" ht="14.25" spans="1:9">
       <c r="A257" s="1">
         <v>255</v>
       </c>
@@ -6813,13 +7321,15 @@
       <c r="E257" s="1">
         <v>30063</v>
       </c>
-      <c r="F257" s="4">
+      <c r="F257" s="3">
         <v>1500</v>
       </c>
-      <c r="G257" s="1"/>
       <c r="H257" s="1"/>
-    </row>
-    <row r="258" ht="14.25" spans="1:8">
+      <c r="I257" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="258" ht="14.25" spans="1:9">
       <c r="A258" s="1">
         <v>256</v>
       </c>
@@ -6835,13 +7345,15 @@
       <c r="E258" s="1">
         <v>30063</v>
       </c>
-      <c r="F258" s="4">
+      <c r="F258" s="3">
+        <v>450</v>
+      </c>
+      <c r="H258" s="1"/>
+      <c r="I258" s="4">
         <v>467</v>
       </c>
-      <c r="G258" s="1"/>
-      <c r="H258" s="1"/>
-    </row>
-    <row r="259" ht="14.25" spans="1:8">
+    </row>
+    <row r="259" ht="14.25" spans="1:9">
       <c r="A259" s="1">
         <v>257</v>
       </c>
@@ -6857,13 +7369,15 @@
       <c r="E259" s="1">
         <v>30063</v>
       </c>
-      <c r="F259" s="4">
+      <c r="F259" s="3">
+        <v>40</v>
+      </c>
+      <c r="H259" s="1"/>
+      <c r="I259" s="4">
         <v>30</v>
       </c>
-      <c r="G259" s="1"/>
-      <c r="H259" s="1"/>
-    </row>
-    <row r="260" ht="14.25" spans="1:8">
+    </row>
+    <row r="260" ht="14.25" spans="1:9">
       <c r="A260" s="1">
         <v>258</v>
       </c>
@@ -6879,13 +7393,15 @@
       <c r="E260" s="1">
         <v>30063</v>
       </c>
-      <c r="F260" s="4">
+      <c r="F260" s="3">
+        <v>10</v>
+      </c>
+      <c r="H260" s="1"/>
+      <c r="I260" s="4">
         <v>3</v>
       </c>
-      <c r="G260" s="1"/>
-      <c r="H260" s="1"/>
-    </row>
-    <row r="261" ht="14.25" spans="1:8">
+    </row>
+    <row r="261" ht="14.25" spans="1:9">
       <c r="A261" s="1">
         <v>259</v>
       </c>
@@ -6901,13 +7417,15 @@
       <c r="E261" s="1">
         <v>30063</v>
       </c>
-      <c r="F261" s="4">
+      <c r="F261" s="3">
         <v>6000</v>
       </c>
-      <c r="G261" s="1"/>
       <c r="H261" s="1"/>
-    </row>
-    <row r="262" ht="14.25" spans="1:8">
+      <c r="I261" s="4">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="262" ht="14.25" spans="1:9">
       <c r="A262" s="1">
         <v>260</v>
       </c>
@@ -6923,13 +7441,15 @@
       <c r="E262" s="1">
         <v>30063</v>
       </c>
-      <c r="F262" s="4">
+      <c r="F262" s="3">
         <v>3000</v>
       </c>
-      <c r="G262" s="1"/>
       <c r="H262" s="1"/>
-    </row>
-    <row r="263" ht="14.25" spans="1:8">
+      <c r="I262" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="263" ht="14.25" spans="1:9">
       <c r="A263" s="1">
         <v>261</v>
       </c>
@@ -6945,13 +7465,15 @@
       <c r="E263" s="1">
         <v>30063</v>
       </c>
-      <c r="F263" s="4">
+      <c r="F263" s="3">
         <v>700</v>
       </c>
-      <c r="G263" s="1"/>
       <c r="H263" s="1"/>
-    </row>
-    <row r="264" ht="14.25" spans="1:8">
+      <c r="I263" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="264" ht="14.25" spans="1:9">
       <c r="A264" s="1">
         <v>262</v>
       </c>
@@ -6967,13 +7489,15 @@
       <c r="E264" s="1">
         <v>30063</v>
       </c>
-      <c r="F264" s="4">
+      <c r="F264" s="3">
+        <v>275</v>
+      </c>
+      <c r="H264" s="1"/>
+      <c r="I264" s="4">
         <v>289</v>
       </c>
-      <c r="G264" s="1"/>
-      <c r="H264" s="1"/>
-    </row>
-    <row r="265" ht="14.25" spans="1:8">
+    </row>
+    <row r="265" ht="14.25" spans="1:9">
       <c r="A265" s="1">
         <v>263</v>
       </c>
@@ -6989,13 +7513,15 @@
       <c r="E265" s="1">
         <v>30063</v>
       </c>
-      <c r="F265" s="4">
-        <v>10</v>
-      </c>
-      <c r="G265" s="1"/>
+      <c r="F265" s="3">
+        <v>20</v>
+      </c>
       <c r="H265" s="1"/>
-    </row>
-    <row r="266" ht="14.25" spans="1:8">
+      <c r="I265" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" ht="14.25" spans="1:9">
       <c r="A266" s="1">
         <v>264</v>
       </c>
@@ -7011,13 +7537,15 @@
       <c r="E266" s="1">
         <v>30063</v>
       </c>
-      <c r="F266" s="4">
+      <c r="F266" s="3">
+        <v>5</v>
+      </c>
+      <c r="H266" s="1"/>
+      <c r="I266" s="4">
         <v>1</v>
       </c>
-      <c r="G266" s="1"/>
-      <c r="H266" s="1"/>
-    </row>
-    <row r="267" ht="14.25" spans="1:8">
+    </row>
+    <row r="267" ht="14.25" spans="1:9">
       <c r="A267" s="1">
         <v>265</v>
       </c>
@@ -7033,13 +7561,15 @@
       <c r="E267" s="1">
         <v>40014</v>
       </c>
-      <c r="F267" s="4">
+      <c r="F267" s="3">
+        <v>900</v>
+      </c>
+      <c r="H267" s="1"/>
+      <c r="I267" s="4">
         <v>0</v>
       </c>
-      <c r="G267" s="1"/>
-      <c r="H267" s="1"/>
-    </row>
-    <row r="268" ht="14.25" spans="1:8">
+    </row>
+    <row r="268" ht="14.25" spans="1:9">
       <c r="A268" s="1">
         <v>266</v>
       </c>
@@ -7055,13 +7585,15 @@
       <c r="E268" s="1">
         <v>40014</v>
       </c>
-      <c r="F268" s="4">
+      <c r="F268" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H268" s="1"/>
+      <c r="I268" s="4">
         <v>4000</v>
       </c>
-      <c r="G268" s="1"/>
-      <c r="H268" s="1"/>
-    </row>
-    <row r="269" ht="14.25" spans="1:8">
+    </row>
+    <row r="269" ht="14.25" spans="1:9">
       <c r="A269" s="1">
         <v>267</v>
       </c>
@@ -7077,13 +7609,15 @@
       <c r="E269" s="1">
         <v>40014</v>
       </c>
-      <c r="F269" s="4">
+      <c r="F269" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H269" s="1"/>
+      <c r="I269" s="4">
         <v>4000</v>
       </c>
-      <c r="G269" s="1"/>
-      <c r="H269" s="1"/>
-    </row>
-    <row r="270" ht="14.25" spans="1:8">
+    </row>
+    <row r="270" ht="14.25" spans="1:9">
       <c r="A270" s="1">
         <v>268</v>
       </c>
@@ -7099,13 +7633,15 @@
       <c r="E270" s="1">
         <v>40014</v>
       </c>
-      <c r="F270" s="4">
+      <c r="F270" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H270" s="1"/>
+      <c r="I270" s="4">
         <v>1470</v>
       </c>
-      <c r="G270" s="1"/>
-      <c r="H270" s="1"/>
-    </row>
-    <row r="271" ht="14.25" spans="1:8">
+    </row>
+    <row r="271" ht="14.25" spans="1:9">
       <c r="A271" s="1">
         <v>269</v>
       </c>
@@ -7121,13 +7657,15 @@
       <c r="E271" s="1">
         <v>40014</v>
       </c>
-      <c r="F271" s="4">
+      <c r="F271" s="3">
+        <v>450</v>
+      </c>
+      <c r="H271" s="1"/>
+      <c r="I271" s="4">
         <v>500</v>
       </c>
-      <c r="G271" s="1"/>
-      <c r="H271" s="1"/>
-    </row>
-    <row r="272" ht="14.25" spans="1:8">
+    </row>
+    <row r="272" ht="14.25" spans="1:9">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -7143,13 +7681,15 @@
       <c r="E272" s="1">
         <v>40014</v>
       </c>
-      <c r="F272" s="4">
+      <c r="F272" s="3">
+        <v>120</v>
+      </c>
+      <c r="H272" s="1"/>
+      <c r="I272" s="4">
         <v>30</v>
       </c>
-      <c r="G272" s="1"/>
-      <c r="H272" s="1"/>
-    </row>
-    <row r="273" ht="14.25" spans="1:8">
+    </row>
+    <row r="273" ht="14.25" spans="1:9">
       <c r="A273" s="1">
         <v>271</v>
       </c>
@@ -7165,13 +7705,15 @@
       <c r="E273" s="1">
         <v>40014</v>
       </c>
-      <c r="F273" s="4">
+      <c r="F273" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H273" s="1"/>
+      <c r="I273" s="4">
         <v>1600</v>
       </c>
-      <c r="G273" s="1"/>
-      <c r="H273" s="1"/>
-    </row>
-    <row r="274" ht="14.25" spans="1:8">
+    </row>
+    <row r="274" ht="14.25" spans="1:9">
       <c r="A274" s="1">
         <v>272</v>
       </c>
@@ -7187,13 +7729,15 @@
       <c r="E274" s="1">
         <v>40014</v>
       </c>
-      <c r="F274" s="4">
+      <c r="F274" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H274" s="1"/>
+      <c r="I274" s="4">
         <v>4400</v>
       </c>
-      <c r="G274" s="1"/>
-      <c r="H274" s="1"/>
-    </row>
-    <row r="275" ht="14.25" spans="1:8">
+    </row>
+    <row r="275" ht="14.25" spans="1:9">
       <c r="A275" s="1">
         <v>273</v>
       </c>
@@ -7209,13 +7753,15 @@
       <c r="E275" s="1">
         <v>40014</v>
       </c>
-      <c r="F275" s="4">
+      <c r="F275" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H275" s="1"/>
+      <c r="I275" s="4">
         <v>3000</v>
       </c>
-      <c r="G275" s="1"/>
-      <c r="H275" s="1"/>
-    </row>
-    <row r="276" ht="14.25" spans="1:8">
+    </row>
+    <row r="276" ht="14.25" spans="1:9">
       <c r="A276" s="1">
         <v>274</v>
       </c>
@@ -7231,13 +7777,15 @@
       <c r="E276" s="1">
         <v>40014</v>
       </c>
-      <c r="F276" s="4">
+      <c r="F276" s="3">
+        <v>850</v>
+      </c>
+      <c r="H276" s="1"/>
+      <c r="I276" s="4">
         <v>900</v>
       </c>
-      <c r="G276" s="1"/>
-      <c r="H276" s="1"/>
-    </row>
-    <row r="277" ht="14.25" spans="1:8">
+    </row>
+    <row r="277" ht="14.25" spans="1:9">
       <c r="A277" s="1">
         <v>275</v>
       </c>
@@ -7253,13 +7801,15 @@
       <c r="E277" s="1">
         <v>40014</v>
       </c>
-      <c r="F277" s="4">
+      <c r="F277" s="3">
+        <v>120</v>
+      </c>
+      <c r="H277" s="1"/>
+      <c r="I277" s="4">
         <v>90</v>
       </c>
-      <c r="G277" s="1"/>
-      <c r="H277" s="1"/>
-    </row>
-    <row r="278" ht="14.25" spans="1:8">
+    </row>
+    <row r="278" ht="14.25" spans="1:9">
       <c r="A278" s="1">
         <v>276</v>
       </c>
@@ -7275,13 +7825,15 @@
       <c r="E278" s="1">
         <v>40014</v>
       </c>
-      <c r="F278" s="4">
-        <v>10</v>
-      </c>
-      <c r="G278" s="1"/>
+      <c r="F278" s="3">
+        <v>30</v>
+      </c>
       <c r="H278" s="1"/>
-    </row>
-    <row r="279" ht="14.25" spans="1:8">
+      <c r="I278" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" ht="14.25" spans="1:9">
       <c r="A279" s="1">
         <v>277</v>
       </c>
@@ -7297,13 +7849,15 @@
       <c r="E279" s="1">
         <v>40014</v>
       </c>
-      <c r="F279" s="4">
+      <c r="F279" s="3">
         <v>4000</v>
       </c>
-      <c r="G279" s="1"/>
       <c r="H279" s="1"/>
-    </row>
-    <row r="280" ht="14.25" spans="1:8">
+      <c r="I279" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="280" ht="14.25" spans="1:9">
       <c r="A280" s="1">
         <v>278</v>
       </c>
@@ -7319,13 +7873,15 @@
       <c r="E280" s="1">
         <v>40014</v>
       </c>
-      <c r="F280" s="4">
+      <c r="F280" s="3">
         <v>4000</v>
       </c>
-      <c r="G280" s="1"/>
       <c r="H280" s="1"/>
-    </row>
-    <row r="281" ht="14.25" spans="1:8">
+      <c r="I280" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="281" ht="14.25" spans="1:9">
       <c r="A281" s="1">
         <v>279</v>
       </c>
@@ -7341,13 +7897,15 @@
       <c r="E281" s="1">
         <v>40014</v>
       </c>
-      <c r="F281" s="4">
+      <c r="F281" s="3">
         <v>1500</v>
       </c>
-      <c r="G281" s="1"/>
       <c r="H281" s="1"/>
-    </row>
-    <row r="282" ht="14.25" spans="1:8">
+      <c r="I281" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="282" ht="14.25" spans="1:9">
       <c r="A282" s="1">
         <v>280</v>
       </c>
@@ -7363,13 +7921,15 @@
       <c r="E282" s="1">
         <v>40014</v>
       </c>
-      <c r="F282" s="4">
+      <c r="F282" s="3">
+        <v>450</v>
+      </c>
+      <c r="H282" s="1"/>
+      <c r="I282" s="4">
         <v>467</v>
       </c>
-      <c r="G282" s="1"/>
-      <c r="H282" s="1"/>
-    </row>
-    <row r="283" ht="14.25" spans="1:8">
+    </row>
+    <row r="283" ht="14.25" spans="1:9">
       <c r="A283" s="1">
         <v>281</v>
       </c>
@@ -7385,13 +7945,15 @@
       <c r="E283" s="1">
         <v>40014</v>
       </c>
-      <c r="F283" s="4">
+      <c r="F283" s="3">
+        <v>40</v>
+      </c>
+      <c r="H283" s="1"/>
+      <c r="I283" s="4">
         <v>30</v>
       </c>
-      <c r="G283" s="1"/>
-      <c r="H283" s="1"/>
-    </row>
-    <row r="284" ht="14.25" spans="1:8">
+    </row>
+    <row r="284" ht="14.25" spans="1:9">
       <c r="A284" s="1">
         <v>282</v>
       </c>
@@ -7407,13 +7969,15 @@
       <c r="E284" s="1">
         <v>40014</v>
       </c>
-      <c r="F284" s="4">
+      <c r="F284" s="3">
+        <v>10</v>
+      </c>
+      <c r="H284" s="1"/>
+      <c r="I284" s="4">
         <v>3</v>
       </c>
-      <c r="G284" s="1"/>
-      <c r="H284" s="1"/>
-    </row>
-    <row r="285" ht="14.25" spans="1:8">
+    </row>
+    <row r="285" ht="14.25" spans="1:9">
       <c r="A285" s="1">
         <v>283</v>
       </c>
@@ -7429,13 +7993,15 @@
       <c r="E285" s="1">
         <v>40024</v>
       </c>
-      <c r="F285" s="4">
+      <c r="F285" s="3">
+        <v>900</v>
+      </c>
+      <c r="H285" s="1"/>
+      <c r="I285" s="4">
         <v>0</v>
       </c>
-      <c r="G285" s="1"/>
-      <c r="H285" s="1"/>
-    </row>
-    <row r="286" ht="14.25" spans="1:8">
+    </row>
+    <row r="286" ht="14.25" spans="1:9">
       <c r="A286" s="1">
         <v>284</v>
       </c>
@@ -7451,13 +8017,15 @@
       <c r="E286" s="1">
         <v>40024</v>
       </c>
-      <c r="F286" s="4">
+      <c r="F286" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H286" s="1"/>
+      <c r="I286" s="4">
         <v>4000</v>
       </c>
-      <c r="G286" s="1"/>
-      <c r="H286" s="1"/>
-    </row>
-    <row r="287" ht="14.25" spans="1:8">
+    </row>
+    <row r="287" ht="14.25" spans="1:9">
       <c r="A287" s="1">
         <v>285</v>
       </c>
@@ -7473,13 +8041,15 @@
       <c r="E287" s="1">
         <v>40024</v>
       </c>
-      <c r="F287" s="4">
+      <c r="F287" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H287" s="1"/>
+      <c r="I287" s="4">
         <v>4000</v>
       </c>
-      <c r="G287" s="1"/>
-      <c r="H287" s="1"/>
-    </row>
-    <row r="288" ht="14.25" spans="1:8">
+    </row>
+    <row r="288" ht="14.25" spans="1:9">
       <c r="A288" s="1">
         <v>286</v>
       </c>
@@ -7495,13 +8065,15 @@
       <c r="E288" s="1">
         <v>40024</v>
       </c>
-      <c r="F288" s="4">
+      <c r="F288" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H288" s="1"/>
+      <c r="I288" s="4">
         <v>1470</v>
       </c>
-      <c r="G288" s="1"/>
-      <c r="H288" s="1"/>
-    </row>
-    <row r="289" ht="14.25" spans="1:8">
+    </row>
+    <row r="289" ht="14.25" spans="1:9">
       <c r="A289" s="1">
         <v>287</v>
       </c>
@@ -7517,13 +8089,15 @@
       <c r="E289" s="1">
         <v>40024</v>
       </c>
-      <c r="F289" s="4">
+      <c r="F289" s="3">
+        <v>450</v>
+      </c>
+      <c r="H289" s="1"/>
+      <c r="I289" s="4">
         <v>500</v>
       </c>
-      <c r="G289" s="1"/>
-      <c r="H289" s="1"/>
-    </row>
-    <row r="290" ht="14.25" spans="1:8">
+    </row>
+    <row r="290" ht="14.25" spans="1:9">
       <c r="A290" s="1">
         <v>288</v>
       </c>
@@ -7539,13 +8113,15 @@
       <c r="E290" s="1">
         <v>40024</v>
       </c>
-      <c r="F290" s="4">
+      <c r="F290" s="3">
+        <v>120</v>
+      </c>
+      <c r="H290" s="1"/>
+      <c r="I290" s="4">
         <v>30</v>
       </c>
-      <c r="G290" s="1"/>
-      <c r="H290" s="1"/>
-    </row>
-    <row r="291" ht="14.25" spans="1:8">
+    </row>
+    <row r="291" ht="14.25" spans="1:9">
       <c r="A291" s="1">
         <v>289</v>
       </c>
@@ -7561,13 +8137,15 @@
       <c r="E291" s="1">
         <v>40024</v>
       </c>
-      <c r="F291" s="4">
+      <c r="F291" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H291" s="1"/>
+      <c r="I291" s="4">
         <v>1600</v>
       </c>
-      <c r="G291" s="1"/>
-      <c r="H291" s="1"/>
-    </row>
-    <row r="292" ht="14.25" spans="1:8">
+    </row>
+    <row r="292" ht="14.25" spans="1:9">
       <c r="A292" s="1">
         <v>290</v>
       </c>
@@ -7583,13 +8161,15 @@
       <c r="E292" s="1">
         <v>40024</v>
       </c>
-      <c r="F292" s="4">
+      <c r="F292" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H292" s="1"/>
+      <c r="I292" s="4">
         <v>4400</v>
       </c>
-      <c r="G292" s="1"/>
-      <c r="H292" s="1"/>
-    </row>
-    <row r="293" ht="14.25" spans="1:8">
+    </row>
+    <row r="293" ht="14.25" spans="1:9">
       <c r="A293" s="1">
         <v>291</v>
       </c>
@@ -7605,13 +8185,15 @@
       <c r="E293" s="1">
         <v>40024</v>
       </c>
-      <c r="F293" s="4">
+      <c r="F293" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H293" s="1"/>
+      <c r="I293" s="4">
         <v>3000</v>
       </c>
-      <c r="G293" s="1"/>
-      <c r="H293" s="1"/>
-    </row>
-    <row r="294" ht="14.25" spans="1:8">
+    </row>
+    <row r="294" ht="14.25" spans="1:9">
       <c r="A294" s="1">
         <v>292</v>
       </c>
@@ -7627,13 +8209,15 @@
       <c r="E294" s="1">
         <v>40024</v>
       </c>
-      <c r="F294" s="4">
+      <c r="F294" s="3">
+        <v>850</v>
+      </c>
+      <c r="H294" s="1"/>
+      <c r="I294" s="4">
         <v>900</v>
       </c>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-    </row>
-    <row r="295" ht="14.25" spans="1:8">
+    </row>
+    <row r="295" ht="14.25" spans="1:9">
       <c r="A295" s="1">
         <v>293</v>
       </c>
@@ -7649,13 +8233,15 @@
       <c r="E295" s="1">
         <v>40024</v>
       </c>
-      <c r="F295" s="4">
+      <c r="F295" s="3">
+        <v>120</v>
+      </c>
+      <c r="H295" s="1"/>
+      <c r="I295" s="4">
         <v>90</v>
       </c>
-      <c r="G295" s="1"/>
-      <c r="H295" s="1"/>
-    </row>
-    <row r="296" ht="14.25" spans="1:8">
+    </row>
+    <row r="296" ht="14.25" spans="1:9">
       <c r="A296" s="1">
         <v>294</v>
       </c>
@@ -7671,13 +8257,15 @@
       <c r="E296" s="1">
         <v>40024</v>
       </c>
-      <c r="F296" s="4">
-        <v>10</v>
-      </c>
-      <c r="G296" s="1"/>
+      <c r="F296" s="3">
+        <v>30</v>
+      </c>
       <c r="H296" s="1"/>
-    </row>
-    <row r="297" ht="14.25" spans="1:8">
+      <c r="I296" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" ht="14.25" spans="1:9">
       <c r="A297" s="1">
         <v>295</v>
       </c>
@@ -7693,13 +8281,15 @@
       <c r="E297" s="1">
         <v>40024</v>
       </c>
-      <c r="F297" s="4">
+      <c r="F297" s="3">
         <v>4000</v>
       </c>
-      <c r="G297" s="1"/>
       <c r="H297" s="1"/>
-    </row>
-    <row r="298" ht="14.25" spans="1:8">
+      <c r="I297" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="298" ht="14.25" spans="1:9">
       <c r="A298" s="1">
         <v>296</v>
       </c>
@@ -7715,13 +8305,15 @@
       <c r="E298" s="1">
         <v>40024</v>
       </c>
-      <c r="F298" s="4">
+      <c r="F298" s="3">
         <v>4000</v>
       </c>
-      <c r="G298" s="1"/>
       <c r="H298" s="1"/>
-    </row>
-    <row r="299" ht="14.25" spans="1:8">
+      <c r="I298" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="299" ht="14.25" spans="1:9">
       <c r="A299" s="1">
         <v>297</v>
       </c>
@@ -7737,13 +8329,15 @@
       <c r="E299" s="1">
         <v>40024</v>
       </c>
-      <c r="F299" s="4">
+      <c r="F299" s="3">
         <v>1500</v>
       </c>
-      <c r="G299" s="1"/>
       <c r="H299" s="1"/>
-    </row>
-    <row r="300" ht="14.25" spans="1:8">
+      <c r="I299" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="300" ht="14.25" spans="1:9">
       <c r="A300" s="1">
         <v>298</v>
       </c>
@@ -7759,13 +8353,15 @@
       <c r="E300" s="1">
         <v>40024</v>
       </c>
-      <c r="F300" s="4">
+      <c r="F300" s="3">
+        <v>450</v>
+      </c>
+      <c r="H300" s="1"/>
+      <c r="I300" s="4">
         <v>467</v>
       </c>
-      <c r="G300" s="1"/>
-      <c r="H300" s="1"/>
-    </row>
-    <row r="301" ht="14.25" spans="1:8">
+    </row>
+    <row r="301" ht="14.25" spans="1:9">
       <c r="A301" s="1">
         <v>299</v>
       </c>
@@ -7781,13 +8377,15 @@
       <c r="E301" s="1">
         <v>40024</v>
       </c>
-      <c r="F301" s="4">
+      <c r="F301" s="3">
+        <v>40</v>
+      </c>
+      <c r="H301" s="1"/>
+      <c r="I301" s="4">
         <v>30</v>
       </c>
-      <c r="G301" s="1"/>
-      <c r="H301" s="1"/>
-    </row>
-    <row r="302" ht="14.25" spans="1:8">
+    </row>
+    <row r="302" ht="14.25" spans="1:9">
       <c r="A302" s="1">
         <v>300</v>
       </c>
@@ -7803,13 +8401,15 @@
       <c r="E302" s="1">
         <v>40024</v>
       </c>
-      <c r="F302" s="4">
+      <c r="F302" s="3">
+        <v>10</v>
+      </c>
+      <c r="H302" s="1"/>
+      <c r="I302" s="4">
         <v>3</v>
       </c>
-      <c r="G302" s="1"/>
-      <c r="H302" s="1"/>
-    </row>
-    <row r="303" ht="14.25" spans="1:8">
+    </row>
+    <row r="303" ht="14.25" spans="1:9">
       <c r="A303" s="1">
         <v>301</v>
       </c>
@@ -7825,13 +8425,15 @@
       <c r="E303" s="1">
         <v>40034</v>
       </c>
-      <c r="F303" s="4">
+      <c r="F303" s="3">
+        <v>900</v>
+      </c>
+      <c r="H303" s="1"/>
+      <c r="I303" s="4">
         <v>0</v>
       </c>
-      <c r="G303" s="1"/>
-      <c r="H303" s="1"/>
-    </row>
-    <row r="304" ht="14.25" spans="1:8">
+    </row>
+    <row r="304" ht="14.25" spans="1:9">
       <c r="A304" s="1">
         <v>302</v>
       </c>
@@ -7847,13 +8449,15 @@
       <c r="E304" s="1">
         <v>40034</v>
       </c>
-      <c r="F304" s="4">
+      <c r="F304" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H304" s="1"/>
+      <c r="I304" s="4">
         <v>4000</v>
       </c>
-      <c r="G304" s="1"/>
-      <c r="H304" s="1"/>
-    </row>
-    <row r="305" ht="14.25" spans="1:8">
+    </row>
+    <row r="305" ht="14.25" spans="1:9">
       <c r="A305" s="1">
         <v>303</v>
       </c>
@@ -7869,13 +8473,15 @@
       <c r="E305" s="1">
         <v>40034</v>
       </c>
-      <c r="F305" s="4">
+      <c r="F305" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H305" s="1"/>
+      <c r="I305" s="4">
         <v>4000</v>
       </c>
-      <c r="G305" s="1"/>
-      <c r="H305" s="1"/>
-    </row>
-    <row r="306" ht="14.25" spans="1:8">
+    </row>
+    <row r="306" ht="14.25" spans="1:9">
       <c r="A306" s="1">
         <v>304</v>
       </c>
@@ -7891,13 +8497,15 @@
       <c r="E306" s="1">
         <v>40034</v>
       </c>
-      <c r="F306" s="4">
+      <c r="F306" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H306" s="1"/>
+      <c r="I306" s="4">
         <v>1470</v>
       </c>
-      <c r="G306" s="1"/>
-      <c r="H306" s="1"/>
-    </row>
-    <row r="307" ht="14.25" spans="1:8">
+    </row>
+    <row r="307" ht="14.25" spans="1:9">
       <c r="A307" s="1">
         <v>305</v>
       </c>
@@ -7913,13 +8521,15 @@
       <c r="E307" s="1">
         <v>40034</v>
       </c>
-      <c r="F307" s="4">
+      <c r="F307" s="3">
+        <v>450</v>
+      </c>
+      <c r="H307" s="1"/>
+      <c r="I307" s="4">
         <v>500</v>
       </c>
-      <c r="G307" s="1"/>
-      <c r="H307" s="1"/>
-    </row>
-    <row r="308" ht="14.25" spans="1:8">
+    </row>
+    <row r="308" ht="14.25" spans="1:9">
       <c r="A308" s="1">
         <v>306</v>
       </c>
@@ -7935,13 +8545,15 @@
       <c r="E308" s="1">
         <v>40034</v>
       </c>
-      <c r="F308" s="4">
+      <c r="F308" s="3">
+        <v>120</v>
+      </c>
+      <c r="H308" s="1"/>
+      <c r="I308" s="4">
         <v>30</v>
       </c>
-      <c r="G308" s="1"/>
-      <c r="H308" s="1"/>
-    </row>
-    <row r="309" ht="14.25" spans="1:8">
+    </row>
+    <row r="309" ht="14.25" spans="1:9">
       <c r="A309" s="1">
         <v>307</v>
       </c>
@@ -7957,13 +8569,15 @@
       <c r="E309" s="1">
         <v>40034</v>
       </c>
-      <c r="F309" s="4">
+      <c r="F309" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H309" s="1"/>
+      <c r="I309" s="4">
         <v>1600</v>
       </c>
-      <c r="G309" s="1"/>
-      <c r="H309" s="1"/>
-    </row>
-    <row r="310" ht="14.25" spans="1:8">
+    </row>
+    <row r="310" ht="14.25" spans="1:9">
       <c r="A310" s="1">
         <v>308</v>
       </c>
@@ -7979,13 +8593,15 @@
       <c r="E310" s="1">
         <v>40034</v>
       </c>
-      <c r="F310" s="4">
+      <c r="F310" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H310" s="1"/>
+      <c r="I310" s="4">
         <v>4400</v>
       </c>
-      <c r="G310" s="1"/>
-      <c r="H310" s="1"/>
-    </row>
-    <row r="311" ht="14.25" spans="1:8">
+    </row>
+    <row r="311" ht="14.25" spans="1:9">
       <c r="A311" s="1">
         <v>309</v>
       </c>
@@ -8001,13 +8617,15 @@
       <c r="E311" s="1">
         <v>40034</v>
       </c>
-      <c r="F311" s="4">
+      <c r="F311" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H311" s="1"/>
+      <c r="I311" s="4">
         <v>3000</v>
       </c>
-      <c r="G311" s="1"/>
-      <c r="H311" s="1"/>
-    </row>
-    <row r="312" ht="14.25" spans="1:8">
+    </row>
+    <row r="312" ht="14.25" spans="1:9">
       <c r="A312" s="1">
         <v>310</v>
       </c>
@@ -8023,13 +8641,15 @@
       <c r="E312" s="1">
         <v>40034</v>
       </c>
-      <c r="F312" s="4">
+      <c r="F312" s="3">
+        <v>850</v>
+      </c>
+      <c r="H312" s="1"/>
+      <c r="I312" s="4">
         <v>900</v>
       </c>
-      <c r="G312" s="1"/>
-      <c r="H312" s="1"/>
-    </row>
-    <row r="313" ht="14.25" spans="1:8">
+    </row>
+    <row r="313" ht="14.25" spans="1:9">
       <c r="A313" s="1">
         <v>311</v>
       </c>
@@ -8045,13 +8665,15 @@
       <c r="E313" s="1">
         <v>40034</v>
       </c>
-      <c r="F313" s="4">
+      <c r="F313" s="3">
+        <v>120</v>
+      </c>
+      <c r="H313" s="1"/>
+      <c r="I313" s="4">
         <v>90</v>
       </c>
-      <c r="G313" s="1"/>
-      <c r="H313" s="1"/>
-    </row>
-    <row r="314" ht="14.25" spans="1:8">
+    </row>
+    <row r="314" ht="14.25" spans="1:9">
       <c r="A314" s="1">
         <v>312</v>
       </c>
@@ -8067,13 +8689,15 @@
       <c r="E314" s="1">
         <v>40034</v>
       </c>
-      <c r="F314" s="4">
-        <v>10</v>
-      </c>
-      <c r="G314" s="1"/>
+      <c r="F314" s="3">
+        <v>30</v>
+      </c>
       <c r="H314" s="1"/>
-    </row>
-    <row r="315" ht="14.25" spans="1:8">
+      <c r="I314" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315" ht="14.25" spans="1:9">
       <c r="A315" s="1">
         <v>313</v>
       </c>
@@ -8089,13 +8713,15 @@
       <c r="E315" s="1">
         <v>40034</v>
       </c>
-      <c r="F315" s="4">
+      <c r="F315" s="3">
         <v>4000</v>
       </c>
-      <c r="G315" s="1"/>
       <c r="H315" s="1"/>
-    </row>
-    <row r="316" ht="14.25" spans="1:8">
+      <c r="I315" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="316" ht="14.25" spans="1:9">
       <c r="A316" s="1">
         <v>314</v>
       </c>
@@ -8111,13 +8737,15 @@
       <c r="E316" s="1">
         <v>40034</v>
       </c>
-      <c r="F316" s="4">
+      <c r="F316" s="3">
         <v>4000</v>
       </c>
-      <c r="G316" s="1"/>
       <c r="H316" s="1"/>
-    </row>
-    <row r="317" ht="14.25" spans="1:8">
+      <c r="I316" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="317" ht="14.25" spans="1:9">
       <c r="A317" s="1">
         <v>315</v>
       </c>
@@ -8133,13 +8761,15 @@
       <c r="E317" s="1">
         <v>40034</v>
       </c>
-      <c r="F317" s="4">
+      <c r="F317" s="3">
         <v>1500</v>
       </c>
-      <c r="G317" s="1"/>
       <c r="H317" s="1"/>
-    </row>
-    <row r="318" ht="14.25" spans="1:8">
+      <c r="I317" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="318" ht="14.25" spans="1:9">
       <c r="A318" s="1">
         <v>316</v>
       </c>
@@ -8155,13 +8785,15 @@
       <c r="E318" s="1">
         <v>40034</v>
       </c>
-      <c r="F318" s="4">
+      <c r="F318" s="3">
+        <v>450</v>
+      </c>
+      <c r="H318" s="1"/>
+      <c r="I318" s="4">
         <v>467</v>
       </c>
-      <c r="G318" s="1"/>
-      <c r="H318" s="1"/>
-    </row>
-    <row r="319" ht="14.25" spans="1:8">
+    </row>
+    <row r="319" ht="14.25" spans="1:9">
       <c r="A319" s="1">
         <v>317</v>
       </c>
@@ -8177,13 +8809,15 @@
       <c r="E319" s="1">
         <v>40034</v>
       </c>
-      <c r="F319" s="4">
+      <c r="F319" s="3">
+        <v>40</v>
+      </c>
+      <c r="H319" s="1"/>
+      <c r="I319" s="4">
         <v>30</v>
       </c>
-      <c r="G319" s="1"/>
-      <c r="H319" s="1"/>
-    </row>
-    <row r="320" ht="14.25" spans="1:8">
+    </row>
+    <row r="320" ht="14.25" spans="1:9">
       <c r="A320" s="1">
         <v>318</v>
       </c>
@@ -8199,13 +8833,15 @@
       <c r="E320" s="1">
         <v>40034</v>
       </c>
-      <c r="F320" s="4">
+      <c r="F320" s="3">
+        <v>10</v>
+      </c>
+      <c r="H320" s="1"/>
+      <c r="I320" s="4">
         <v>3</v>
       </c>
-      <c r="G320" s="1"/>
-      <c r="H320" s="1"/>
-    </row>
-    <row r="321" ht="14.25" spans="1:8">
+    </row>
+    <row r="321" ht="14.25" spans="1:9">
       <c r="A321" s="1">
         <v>319</v>
       </c>
@@ -8221,13 +8857,15 @@
       <c r="E321" s="1">
         <v>40044</v>
       </c>
-      <c r="F321" s="4">
+      <c r="F321" s="3">
+        <v>900</v>
+      </c>
+      <c r="H321" s="1"/>
+      <c r="I321" s="4">
         <v>0</v>
       </c>
-      <c r="G321" s="1"/>
-      <c r="H321" s="1"/>
-    </row>
-    <row r="322" ht="14.25" spans="1:8">
+    </row>
+    <row r="322" ht="14.25" spans="1:9">
       <c r="A322" s="1">
         <v>320</v>
       </c>
@@ -8243,13 +8881,15 @@
       <c r="E322" s="1">
         <v>40044</v>
       </c>
-      <c r="F322" s="4">
+      <c r="F322" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H322" s="1"/>
+      <c r="I322" s="4">
         <v>4000</v>
       </c>
-      <c r="G322" s="1"/>
-      <c r="H322" s="1"/>
-    </row>
-    <row r="323" ht="14.25" spans="1:8">
+    </row>
+    <row r="323" ht="14.25" spans="1:9">
       <c r="A323" s="1">
         <v>321</v>
       </c>
@@ -8265,13 +8905,15 @@
       <c r="E323" s="1">
         <v>40044</v>
       </c>
-      <c r="F323" s="4">
+      <c r="F323" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H323" s="1"/>
+      <c r="I323" s="4">
         <v>4000</v>
       </c>
-      <c r="G323" s="1"/>
-      <c r="H323" s="1"/>
-    </row>
-    <row r="324" ht="14.25" spans="1:8">
+    </row>
+    <row r="324" ht="14.25" spans="1:9">
       <c r="A324" s="1">
         <v>322</v>
       </c>
@@ -8287,13 +8929,15 @@
       <c r="E324" s="1">
         <v>40044</v>
       </c>
-      <c r="F324" s="4">
+      <c r="F324" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H324" s="1"/>
+      <c r="I324" s="4">
         <v>1470</v>
       </c>
-      <c r="G324" s="1"/>
-      <c r="H324" s="1"/>
-    </row>
-    <row r="325" ht="14.25" spans="1:8">
+    </row>
+    <row r="325" ht="14.25" spans="1:9">
       <c r="A325" s="1">
         <v>323</v>
       </c>
@@ -8309,13 +8953,15 @@
       <c r="E325" s="1">
         <v>40044</v>
       </c>
-      <c r="F325" s="4">
+      <c r="F325" s="3">
+        <v>450</v>
+      </c>
+      <c r="H325" s="1"/>
+      <c r="I325" s="4">
         <v>500</v>
       </c>
-      <c r="G325" s="1"/>
-      <c r="H325" s="1"/>
-    </row>
-    <row r="326" ht="14.25" spans="1:8">
+    </row>
+    <row r="326" ht="14.25" spans="1:9">
       <c r="A326" s="1">
         <v>324</v>
       </c>
@@ -8331,13 +8977,15 @@
       <c r="E326" s="1">
         <v>40044</v>
       </c>
-      <c r="F326" s="4">
+      <c r="F326" s="3">
+        <v>120</v>
+      </c>
+      <c r="H326" s="1"/>
+      <c r="I326" s="4">
         <v>30</v>
       </c>
-      <c r="G326" s="1"/>
-      <c r="H326" s="1"/>
-    </row>
-    <row r="327" ht="14.25" spans="1:8">
+    </row>
+    <row r="327" ht="14.25" spans="1:9">
       <c r="A327" s="1">
         <v>325</v>
       </c>
@@ -8353,13 +9001,15 @@
       <c r="E327" s="1">
         <v>40044</v>
       </c>
-      <c r="F327" s="4">
+      <c r="F327" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H327" s="1"/>
+      <c r="I327" s="4">
         <v>1600</v>
       </c>
-      <c r="G327" s="1"/>
-      <c r="H327" s="1"/>
-    </row>
-    <row r="328" ht="14.25" spans="1:8">
+    </row>
+    <row r="328" ht="14.25" spans="1:9">
       <c r="A328" s="1">
         <v>326</v>
       </c>
@@ -8375,13 +9025,15 @@
       <c r="E328" s="1">
         <v>40044</v>
       </c>
-      <c r="F328" s="4">
+      <c r="F328" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H328" s="1"/>
+      <c r="I328" s="4">
         <v>4400</v>
       </c>
-      <c r="G328" s="1"/>
-      <c r="H328" s="1"/>
-    </row>
-    <row r="329" ht="14.25" spans="1:8">
+    </row>
+    <row r="329" ht="14.25" spans="1:9">
       <c r="A329" s="1">
         <v>327</v>
       </c>
@@ -8397,13 +9049,15 @@
       <c r="E329" s="1">
         <v>40044</v>
       </c>
-      <c r="F329" s="4">
+      <c r="F329" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H329" s="1"/>
+      <c r="I329" s="4">
         <v>3000</v>
       </c>
-      <c r="G329" s="1"/>
-      <c r="H329" s="1"/>
-    </row>
-    <row r="330" ht="14.25" spans="1:8">
+    </row>
+    <row r="330" ht="14.25" spans="1:9">
       <c r="A330" s="1">
         <v>328</v>
       </c>
@@ -8419,13 +9073,15 @@
       <c r="E330" s="1">
         <v>40044</v>
       </c>
-      <c r="F330" s="4">
+      <c r="F330" s="3">
+        <v>850</v>
+      </c>
+      <c r="H330" s="1"/>
+      <c r="I330" s="4">
         <v>900</v>
       </c>
-      <c r="G330" s="1"/>
-      <c r="H330" s="1"/>
-    </row>
-    <row r="331" ht="14.25" spans="1:8">
+    </row>
+    <row r="331" ht="14.25" spans="1:9">
       <c r="A331" s="1">
         <v>329</v>
       </c>
@@ -8441,13 +9097,15 @@
       <c r="E331" s="1">
         <v>40044</v>
       </c>
-      <c r="F331" s="4">
+      <c r="F331" s="3">
+        <v>120</v>
+      </c>
+      <c r="H331" s="1"/>
+      <c r="I331" s="4">
         <v>90</v>
       </c>
-      <c r="G331" s="1"/>
-      <c r="H331" s="1"/>
-    </row>
-    <row r="332" ht="14.25" spans="1:8">
+    </row>
+    <row r="332" ht="14.25" spans="1:9">
       <c r="A332" s="1">
         <v>330</v>
       </c>
@@ -8463,13 +9121,15 @@
       <c r="E332" s="1">
         <v>40044</v>
       </c>
-      <c r="F332" s="4">
-        <v>10</v>
-      </c>
-      <c r="G332" s="1"/>
+      <c r="F332" s="3">
+        <v>30</v>
+      </c>
       <c r="H332" s="1"/>
-    </row>
-    <row r="333" ht="14.25" spans="1:8">
+      <c r="I332" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" ht="14.25" spans="1:9">
       <c r="A333" s="1">
         <v>331</v>
       </c>
@@ -8485,13 +9145,15 @@
       <c r="E333" s="1">
         <v>40044</v>
       </c>
-      <c r="F333" s="4">
+      <c r="F333" s="3">
         <v>4000</v>
       </c>
-      <c r="G333" s="1"/>
       <c r="H333" s="1"/>
-    </row>
-    <row r="334" ht="14.25" spans="1:8">
+      <c r="I333" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="334" ht="14.25" spans="1:9">
       <c r="A334" s="1">
         <v>332</v>
       </c>
@@ -8507,13 +9169,15 @@
       <c r="E334" s="1">
         <v>40044</v>
       </c>
-      <c r="F334" s="4">
+      <c r="F334" s="3">
         <v>4000</v>
       </c>
-      <c r="G334" s="1"/>
       <c r="H334" s="1"/>
-    </row>
-    <row r="335" ht="14.25" spans="1:8">
+      <c r="I334" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="335" ht="14.25" spans="1:9">
       <c r="A335" s="1">
         <v>333</v>
       </c>
@@ -8529,13 +9193,15 @@
       <c r="E335" s="1">
         <v>40044</v>
       </c>
-      <c r="F335" s="4">
+      <c r="F335" s="3">
         <v>1500</v>
       </c>
-      <c r="G335" s="1"/>
       <c r="H335" s="1"/>
-    </row>
-    <row r="336" ht="14.25" spans="1:8">
+      <c r="I335" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="336" ht="14.25" spans="1:9">
       <c r="A336" s="1">
         <v>334</v>
       </c>
@@ -8551,13 +9217,15 @@
       <c r="E336" s="1">
         <v>40044</v>
       </c>
-      <c r="F336" s="4">
+      <c r="F336" s="3">
+        <v>450</v>
+      </c>
+      <c r="H336" s="1"/>
+      <c r="I336" s="4">
         <v>467</v>
       </c>
-      <c r="G336" s="1"/>
-      <c r="H336" s="1"/>
-    </row>
-    <row r="337" ht="14.25" spans="1:8">
+    </row>
+    <row r="337" ht="14.25" spans="1:9">
       <c r="A337" s="1">
         <v>335</v>
       </c>
@@ -8573,13 +9241,15 @@
       <c r="E337" s="1">
         <v>40044</v>
       </c>
-      <c r="F337" s="4">
+      <c r="F337" s="3">
+        <v>40</v>
+      </c>
+      <c r="H337" s="1"/>
+      <c r="I337" s="4">
         <v>30</v>
       </c>
-      <c r="G337" s="1"/>
-      <c r="H337" s="1"/>
-    </row>
-    <row r="338" ht="14.25" spans="1:8">
+    </row>
+    <row r="338" ht="14.25" spans="1:9">
       <c r="A338" s="1">
         <v>336</v>
       </c>
@@ -8595,13 +9265,15 @@
       <c r="E338" s="1">
         <v>40044</v>
       </c>
-      <c r="F338" s="4">
+      <c r="F338" s="3">
+        <v>10</v>
+      </c>
+      <c r="H338" s="1"/>
+      <c r="I338" s="4">
         <v>3</v>
       </c>
-      <c r="G338" s="1"/>
-      <c r="H338" s="1"/>
-    </row>
-    <row r="339" ht="14.25" spans="1:8">
+    </row>
+    <row r="339" ht="14.25" spans="1:9">
       <c r="A339" s="1">
         <v>337</v>
       </c>
@@ -8617,13 +9289,15 @@
       <c r="E339" s="1">
         <v>40054</v>
       </c>
-      <c r="F339" s="4">
+      <c r="F339" s="3">
+        <v>900</v>
+      </c>
+      <c r="H339" s="1"/>
+      <c r="I339" s="4">
         <v>0</v>
       </c>
-      <c r="G339" s="1"/>
-      <c r="H339" s="1"/>
-    </row>
-    <row r="340" ht="14.25" spans="1:8">
+    </row>
+    <row r="340" ht="14.25" spans="1:9">
       <c r="A340" s="1">
         <v>338</v>
       </c>
@@ -8639,13 +9313,15 @@
       <c r="E340" s="1">
         <v>40054</v>
       </c>
-      <c r="F340" s="4">
+      <c r="F340" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H340" s="1"/>
+      <c r="I340" s="4">
         <v>4000</v>
       </c>
-      <c r="G340" s="1"/>
-      <c r="H340" s="1"/>
-    </row>
-    <row r="341" ht="14.25" spans="1:8">
+    </row>
+    <row r="341" ht="14.25" spans="1:9">
       <c r="A341" s="1">
         <v>339</v>
       </c>
@@ -8661,13 +9337,15 @@
       <c r="E341" s="1">
         <v>40054</v>
       </c>
-      <c r="F341" s="4">
+      <c r="F341" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H341" s="1"/>
+      <c r="I341" s="4">
         <v>4000</v>
       </c>
-      <c r="G341" s="1"/>
-      <c r="H341" s="1"/>
-    </row>
-    <row r="342" ht="14.25" spans="1:8">
+    </row>
+    <row r="342" ht="14.25" spans="1:9">
       <c r="A342" s="1">
         <v>340</v>
       </c>
@@ -8683,13 +9361,15 @@
       <c r="E342" s="1">
         <v>40054</v>
       </c>
-      <c r="F342" s="4">
+      <c r="F342" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H342" s="1"/>
+      <c r="I342" s="4">
         <v>1470</v>
       </c>
-      <c r="G342" s="1"/>
-      <c r="H342" s="1"/>
-    </row>
-    <row r="343" ht="14.25" spans="1:8">
+    </row>
+    <row r="343" ht="14.25" spans="1:9">
       <c r="A343" s="1">
         <v>341</v>
       </c>
@@ -8705,13 +9385,15 @@
       <c r="E343" s="1">
         <v>40054</v>
       </c>
-      <c r="F343" s="4">
+      <c r="F343" s="3">
+        <v>450</v>
+      </c>
+      <c r="H343" s="1"/>
+      <c r="I343" s="4">
         <v>500</v>
       </c>
-      <c r="G343" s="1"/>
-      <c r="H343" s="1"/>
-    </row>
-    <row r="344" ht="14.25" spans="1:8">
+    </row>
+    <row r="344" ht="14.25" spans="1:9">
       <c r="A344" s="1">
         <v>342</v>
       </c>
@@ -8727,13 +9409,15 @@
       <c r="E344" s="1">
         <v>40054</v>
       </c>
-      <c r="F344" s="4">
+      <c r="F344" s="3">
+        <v>120</v>
+      </c>
+      <c r="H344" s="1"/>
+      <c r="I344" s="4">
         <v>30</v>
       </c>
-      <c r="G344" s="1"/>
-      <c r="H344" s="1"/>
-    </row>
-    <row r="345" ht="14.25" spans="1:8">
+    </row>
+    <row r="345" ht="14.25" spans="1:9">
       <c r="A345" s="1">
         <v>343</v>
       </c>
@@ -8749,13 +9433,15 @@
       <c r="E345" s="1">
         <v>40054</v>
       </c>
-      <c r="F345" s="4">
+      <c r="F345" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H345" s="1"/>
+      <c r="I345" s="4">
         <v>1600</v>
       </c>
-      <c r="G345" s="1"/>
-      <c r="H345" s="1"/>
-    </row>
-    <row r="346" ht="14.25" spans="1:8">
+    </row>
+    <row r="346" ht="14.25" spans="1:9">
       <c r="A346" s="1">
         <v>344</v>
       </c>
@@ -8771,13 +9457,15 @@
       <c r="E346" s="1">
         <v>40054</v>
       </c>
-      <c r="F346" s="4">
+      <c r="F346" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H346" s="1"/>
+      <c r="I346" s="4">
         <v>4400</v>
       </c>
-      <c r="G346" s="1"/>
-      <c r="H346" s="1"/>
-    </row>
-    <row r="347" ht="14.25" spans="1:8">
+    </row>
+    <row r="347" ht="14.25" spans="1:9">
       <c r="A347" s="1">
         <v>345</v>
       </c>
@@ -8793,13 +9481,15 @@
       <c r="E347" s="1">
         <v>40054</v>
       </c>
-      <c r="F347" s="4">
+      <c r="F347" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H347" s="1"/>
+      <c r="I347" s="4">
         <v>3000</v>
       </c>
-      <c r="G347" s="1"/>
-      <c r="H347" s="1"/>
-    </row>
-    <row r="348" ht="14.25" spans="1:8">
+    </row>
+    <row r="348" ht="14.25" spans="1:9">
       <c r="A348" s="1">
         <v>346</v>
       </c>
@@ -8815,13 +9505,15 @@
       <c r="E348" s="1">
         <v>40054</v>
       </c>
-      <c r="F348" s="4">
+      <c r="F348" s="3">
+        <v>850</v>
+      </c>
+      <c r="H348" s="1"/>
+      <c r="I348" s="4">
         <v>900</v>
       </c>
-      <c r="G348" s="1"/>
-      <c r="H348" s="1"/>
-    </row>
-    <row r="349" ht="14.25" spans="1:8">
+    </row>
+    <row r="349" ht="14.25" spans="1:9">
       <c r="A349" s="1">
         <v>347</v>
       </c>
@@ -8837,13 +9529,15 @@
       <c r="E349" s="1">
         <v>40054</v>
       </c>
-      <c r="F349" s="4">
+      <c r="F349" s="3">
+        <v>120</v>
+      </c>
+      <c r="H349" s="1"/>
+      <c r="I349" s="4">
         <v>90</v>
       </c>
-      <c r="G349" s="1"/>
-      <c r="H349" s="1"/>
-    </row>
-    <row r="350" ht="14.25" spans="1:8">
+    </row>
+    <row r="350" ht="14.25" spans="1:9">
       <c r="A350" s="1">
         <v>348</v>
       </c>
@@ -8859,13 +9553,15 @@
       <c r="E350" s="1">
         <v>40054</v>
       </c>
-      <c r="F350" s="4">
-        <v>10</v>
-      </c>
-      <c r="G350" s="1"/>
+      <c r="F350" s="3">
+        <v>30</v>
+      </c>
       <c r="H350" s="1"/>
-    </row>
-    <row r="351" ht="14.25" spans="1:8">
+      <c r="I350" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351" ht="14.25" spans="1:9">
       <c r="A351" s="1">
         <v>349</v>
       </c>
@@ -8881,13 +9577,15 @@
       <c r="E351" s="1">
         <v>40054</v>
       </c>
-      <c r="F351" s="4">
+      <c r="F351" s="3">
         <v>4000</v>
       </c>
-      <c r="G351" s="1"/>
       <c r="H351" s="1"/>
-    </row>
-    <row r="352" ht="14.25" spans="1:8">
+      <c r="I351" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="352" ht="14.25" spans="1:9">
       <c r="A352" s="1">
         <v>350</v>
       </c>
@@ -8903,13 +9601,15 @@
       <c r="E352" s="1">
         <v>40054</v>
       </c>
-      <c r="F352" s="4">
+      <c r="F352" s="3">
         <v>4000</v>
       </c>
-      <c r="G352" s="1"/>
       <c r="H352" s="1"/>
-    </row>
-    <row r="353" ht="14.25" spans="1:8">
+      <c r="I352" s="4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="353" ht="14.25" spans="1:9">
       <c r="A353" s="1">
         <v>351</v>
       </c>
@@ -8925,13 +9625,15 @@
       <c r="E353" s="1">
         <v>40054</v>
       </c>
-      <c r="F353" s="4">
+      <c r="F353" s="3">
         <v>1500</v>
       </c>
-      <c r="G353" s="1"/>
       <c r="H353" s="1"/>
-    </row>
-    <row r="354" ht="14.25" spans="1:8">
+      <c r="I353" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="354" ht="14.25" spans="1:9">
       <c r="A354" s="1">
         <v>352</v>
       </c>
@@ -8947,13 +9649,15 @@
       <c r="E354" s="1">
         <v>40054</v>
       </c>
-      <c r="F354" s="4">
+      <c r="F354" s="3">
+        <v>450</v>
+      </c>
+      <c r="H354" s="1"/>
+      <c r="I354" s="4">
         <v>467</v>
       </c>
-      <c r="G354" s="1"/>
-      <c r="H354" s="1"/>
-    </row>
-    <row r="355" ht="14.25" spans="1:8">
+    </row>
+    <row r="355" ht="14.25" spans="1:9">
       <c r="A355" s="1">
         <v>353</v>
       </c>
@@ -8969,13 +9673,15 @@
       <c r="E355" s="1">
         <v>40054</v>
       </c>
-      <c r="F355" s="4">
+      <c r="F355" s="3">
+        <v>40</v>
+      </c>
+      <c r="H355" s="1"/>
+      <c r="I355" s="4">
         <v>30</v>
       </c>
-      <c r="G355" s="1"/>
-      <c r="H355" s="1"/>
-    </row>
-    <row r="356" ht="14.25" spans="1:8">
+    </row>
+    <row r="356" ht="14.25" spans="1:9">
       <c r="A356" s="1">
         <v>354</v>
       </c>
@@ -8991,13 +9697,15 @@
       <c r="E356" s="1">
         <v>40054</v>
       </c>
-      <c r="F356" s="4">
+      <c r="F356" s="3">
+        <v>10</v>
+      </c>
+      <c r="H356" s="1"/>
+      <c r="I356" s="4">
         <v>3</v>
       </c>
-      <c r="G356" s="1"/>
-      <c r="H356" s="1"/>
-    </row>
-    <row r="357" ht="14.25" spans="1:8">
+    </row>
+    <row r="357" ht="14.25" spans="1:9">
       <c r="A357" s="1">
         <v>355</v>
       </c>
@@ -9013,13 +9721,15 @@
       <c r="E357" s="1">
         <v>50015</v>
       </c>
-      <c r="F357" s="4">
+      <c r="F357" s="3">
         <v>0</v>
       </c>
-      <c r="G357" s="1"/>
       <c r="H357" s="1"/>
-    </row>
-    <row r="358" ht="14.25" spans="1:8">
+      <c r="I357" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" ht="14.25" spans="1:9">
       <c r="A358" s="1">
         <v>356</v>
       </c>
@@ -9035,13 +9745,15 @@
       <c r="E358" s="1">
         <v>50015</v>
       </c>
-      <c r="F358" s="4">
+      <c r="F358" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H358" s="1"/>
+      <c r="I358" s="4">
         <v>0</v>
       </c>
-      <c r="G358" s="1"/>
-      <c r="H358" s="1"/>
-    </row>
-    <row r="359" ht="14.25" spans="1:8">
+    </row>
+    <row r="359" ht="14.25" spans="1:9">
       <c r="A359" s="1">
         <v>357</v>
       </c>
@@ -9057,13 +9769,15 @@
       <c r="E359" s="1">
         <v>50015</v>
       </c>
-      <c r="F359" s="4">
+      <c r="F359" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H359" s="1"/>
+      <c r="I359" s="4">
         <v>4400</v>
       </c>
-      <c r="G359" s="1"/>
-      <c r="H359" s="1"/>
-    </row>
-    <row r="360" ht="14.25" spans="1:8">
+    </row>
+    <row r="360" ht="14.25" spans="1:9">
       <c r="A360" s="1">
         <v>358</v>
       </c>
@@ -9079,13 +9793,15 @@
       <c r="E360" s="1">
         <v>50015</v>
       </c>
-      <c r="F360" s="4">
+      <c r="F360" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H360" s="1"/>
+      <c r="I360" s="4">
         <v>4400</v>
       </c>
-      <c r="G360" s="1"/>
-      <c r="H360" s="1"/>
-    </row>
-    <row r="361" ht="14.25" spans="1:8">
+    </row>
+    <row r="361" ht="14.25" spans="1:9">
       <c r="A361" s="1">
         <v>359</v>
       </c>
@@ -9101,13 +9817,15 @@
       <c r="E361" s="1">
         <v>50015</v>
       </c>
-      <c r="F361" s="4">
+      <c r="F361" s="3">
+        <v>900</v>
+      </c>
+      <c r="H361" s="1"/>
+      <c r="I361" s="4">
         <v>1100</v>
       </c>
-      <c r="G361" s="1"/>
-      <c r="H361" s="1"/>
-    </row>
-    <row r="362" ht="14.25" spans="1:8">
+    </row>
+    <row r="362" ht="14.25" spans="1:9">
       <c r="A362" s="1">
         <v>360</v>
       </c>
@@ -9123,13 +9841,15 @@
       <c r="E362" s="1">
         <v>50015</v>
       </c>
-      <c r="F362" s="4">
+      <c r="F362" s="3">
+        <v>300</v>
+      </c>
+      <c r="H362" s="1"/>
+      <c r="I362" s="4">
         <v>100</v>
       </c>
-      <c r="G362" s="1"/>
-      <c r="H362" s="1"/>
-    </row>
-    <row r="363" ht="14.25" spans="1:8">
+    </row>
+    <row r="363" ht="14.25" spans="1:9">
       <c r="A363" s="1">
         <v>361</v>
       </c>
@@ -9145,13 +9865,15 @@
       <c r="E363" s="1">
         <v>50015</v>
       </c>
-      <c r="F363" s="4">
+      <c r="F363" s="3">
+        <v>900</v>
+      </c>
+      <c r="H363" s="1"/>
+      <c r="I363" s="4">
         <v>0</v>
       </c>
-      <c r="G363" s="1"/>
-      <c r="H363" s="1"/>
-    </row>
-    <row r="364" ht="14.25" spans="1:8">
+    </row>
+    <row r="364" ht="14.25" spans="1:9">
       <c r="A364" s="1">
         <v>362</v>
       </c>
@@ -9167,13 +9889,15 @@
       <c r="E364" s="1">
         <v>50015</v>
       </c>
-      <c r="F364" s="4">
+      <c r="F364" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H364" s="1"/>
+      <c r="I364" s="4">
         <v>4000</v>
       </c>
-      <c r="G364" s="1"/>
-      <c r="H364" s="1"/>
-    </row>
-    <row r="365" ht="14.25" spans="1:8">
+    </row>
+    <row r="365" ht="14.25" spans="1:9">
       <c r="A365" s="1">
         <v>363</v>
       </c>
@@ -9189,13 +9913,15 @@
       <c r="E365" s="1">
         <v>50015</v>
       </c>
-      <c r="F365" s="4">
+      <c r="F365" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H365" s="1"/>
+      <c r="I365" s="4">
         <v>4000</v>
       </c>
-      <c r="G365" s="1"/>
-      <c r="H365" s="1"/>
-    </row>
-    <row r="366" ht="14.25" spans="1:8">
+    </row>
+    <row r="366" ht="14.25" spans="1:9">
       <c r="A366" s="1">
         <v>364</v>
       </c>
@@ -9211,13 +9937,15 @@
       <c r="E366" s="1">
         <v>50015</v>
       </c>
-      <c r="F366" s="4">
+      <c r="F366" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H366" s="1"/>
+      <c r="I366" s="4">
         <v>1470</v>
       </c>
-      <c r="G366" s="1"/>
-      <c r="H366" s="1"/>
-    </row>
-    <row r="367" ht="14.25" spans="1:8">
+    </row>
+    <row r="367" ht="14.25" spans="1:9">
       <c r="A367" s="1">
         <v>365</v>
       </c>
@@ -9233,13 +9961,15 @@
       <c r="E367" s="1">
         <v>50015</v>
       </c>
-      <c r="F367" s="4">
+      <c r="F367" s="3">
+        <v>450</v>
+      </c>
+      <c r="H367" s="1"/>
+      <c r="I367" s="4">
         <v>500</v>
       </c>
-      <c r="G367" s="1"/>
-      <c r="H367" s="1"/>
-    </row>
-    <row r="368" ht="14.25" spans="1:8">
+    </row>
+    <row r="368" ht="14.25" spans="1:9">
       <c r="A368" s="1">
         <v>366</v>
       </c>
@@ -9255,13 +9985,15 @@
       <c r="E368" s="1">
         <v>50015</v>
       </c>
-      <c r="F368" s="4">
+      <c r="F368" s="3">
+        <v>120</v>
+      </c>
+      <c r="H368" s="1"/>
+      <c r="I368" s="4">
         <v>30</v>
       </c>
-      <c r="G368" s="1"/>
-      <c r="H368" s="1"/>
-    </row>
-    <row r="369" ht="14.25" spans="1:8">
+    </row>
+    <row r="369" ht="14.25" spans="1:9">
       <c r="A369" s="1">
         <v>367</v>
       </c>
@@ -9277,13 +10009,15 @@
       <c r="E369" s="1">
         <v>50015</v>
       </c>
-      <c r="F369" s="4">
+      <c r="F369" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H369" s="1"/>
+      <c r="I369" s="4">
         <v>1600</v>
       </c>
-      <c r="G369" s="1"/>
-      <c r="H369" s="1"/>
-    </row>
-    <row r="370" ht="14.25" spans="1:8">
+    </row>
+    <row r="370" ht="14.25" spans="1:9">
       <c r="A370" s="1">
         <v>368</v>
       </c>
@@ -9299,13 +10033,15 @@
       <c r="E370" s="1">
         <v>50015</v>
       </c>
-      <c r="F370" s="4">
+      <c r="F370" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H370" s="1"/>
+      <c r="I370" s="4">
         <v>4400</v>
       </c>
-      <c r="G370" s="1"/>
-      <c r="H370" s="1"/>
-    </row>
-    <row r="371" ht="14.25" spans="1:8">
+    </row>
+    <row r="371" ht="14.25" spans="1:9">
       <c r="A371" s="1">
         <v>369</v>
       </c>
@@ -9321,13 +10057,15 @@
       <c r="E371" s="1">
         <v>50015</v>
       </c>
-      <c r="F371" s="4">
+      <c r="F371" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H371" s="1"/>
+      <c r="I371" s="4">
         <v>3000</v>
       </c>
-      <c r="G371" s="1"/>
-      <c r="H371" s="1"/>
-    </row>
-    <row r="372" ht="14.25" spans="1:8">
+    </row>
+    <row r="372" ht="14.25" spans="1:9">
       <c r="A372" s="1">
         <v>370</v>
       </c>
@@ -9343,13 +10081,15 @@
       <c r="E372" s="1">
         <v>50015</v>
       </c>
-      <c r="F372" s="4">
+      <c r="F372" s="3">
+        <v>850</v>
+      </c>
+      <c r="H372" s="1"/>
+      <c r="I372" s="4">
         <v>900</v>
       </c>
-      <c r="G372" s="1"/>
-      <c r="H372" s="1"/>
-    </row>
-    <row r="373" ht="14.25" spans="1:8">
+    </row>
+    <row r="373" ht="14.25" spans="1:9">
       <c r="A373" s="1">
         <v>371</v>
       </c>
@@ -9365,13 +10105,15 @@
       <c r="E373" s="1">
         <v>50015</v>
       </c>
-      <c r="F373" s="4">
+      <c r="F373" s="3">
+        <v>120</v>
+      </c>
+      <c r="H373" s="1"/>
+      <c r="I373" s="4">
         <v>90</v>
       </c>
-      <c r="G373" s="1"/>
-      <c r="H373" s="1"/>
-    </row>
-    <row r="374" ht="14.25" spans="1:8">
+    </row>
+    <row r="374" ht="14.25" spans="1:9">
       <c r="A374" s="1">
         <v>372</v>
       </c>
@@ -9387,13 +10129,15 @@
       <c r="E374" s="1">
         <v>50015</v>
       </c>
-      <c r="F374" s="4">
-        <v>10</v>
-      </c>
-      <c r="G374" s="1"/>
+      <c r="F374" s="3">
+        <v>30</v>
+      </c>
       <c r="H374" s="1"/>
-    </row>
-    <row r="375" ht="14.25" spans="1:8">
+      <c r="I374" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375" ht="14.25" spans="1:9">
       <c r="A375" s="6">
         <v>373</v>
       </c>
@@ -9409,13 +10153,15 @@
       <c r="E375" s="6">
         <v>60016</v>
       </c>
-      <c r="F375" s="7">
+      <c r="F375" s="3">
         <v>0</v>
       </c>
-      <c r="G375" s="1"/>
       <c r="H375" s="1"/>
-    </row>
-    <row r="376" ht="14.25" spans="1:8">
+      <c r="I375" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" ht="14.25" spans="1:9">
       <c r="A376" s="6">
         <v>374</v>
       </c>
@@ -9431,13 +10177,15 @@
       <c r="E376" s="6">
         <v>60016</v>
       </c>
-      <c r="F376" s="7">
+      <c r="F376" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H376" s="1"/>
+      <c r="I376" s="7">
         <v>0</v>
       </c>
-      <c r="G376" s="1"/>
-      <c r="H376" s="1"/>
-    </row>
-    <row r="377" ht="14.25" spans="1:8">
+    </row>
+    <row r="377" ht="14.25" spans="1:9">
       <c r="A377" s="6">
         <v>375</v>
       </c>
@@ -9453,13 +10201,15 @@
       <c r="E377" s="6">
         <v>60016</v>
       </c>
-      <c r="F377" s="7">
+      <c r="F377" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H377" s="1"/>
+      <c r="I377" s="7">
         <v>0</v>
       </c>
-      <c r="G377" s="1"/>
-      <c r="H377" s="1"/>
-    </row>
-    <row r="378" ht="14.25" spans="1:8">
+    </row>
+    <row r="378" ht="14.25" spans="1:9">
       <c r="A378" s="6">
         <v>376</v>
       </c>
@@ -9475,13 +10225,15 @@
       <c r="E378" s="6">
         <v>60016</v>
       </c>
-      <c r="F378" s="7">
+      <c r="F378" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H378" s="1"/>
+      <c r="I378" s="7">
         <v>7000</v>
       </c>
-      <c r="G378" s="1"/>
-      <c r="H378" s="1"/>
-    </row>
-    <row r="379" ht="14.25" spans="1:8">
+    </row>
+    <row r="379" ht="14.25" spans="1:9">
       <c r="A379" s="6">
         <v>377</v>
       </c>
@@ -9497,13 +10249,15 @@
       <c r="E379" s="6">
         <v>60016</v>
       </c>
-      <c r="F379" s="7">
+      <c r="F379" s="3">
+        <v>900</v>
+      </c>
+      <c r="H379" s="1"/>
+      <c r="I379" s="7">
         <v>2700</v>
       </c>
-      <c r="G379" s="1"/>
-      <c r="H379" s="1"/>
-    </row>
-    <row r="380" ht="14.25" spans="1:8">
+    </row>
+    <row r="380" ht="14.25" spans="1:9">
       <c r="A380" s="6">
         <v>378</v>
       </c>
@@ -9519,13 +10273,15 @@
       <c r="E380" s="6">
         <v>60016</v>
       </c>
-      <c r="F380" s="7">
+      <c r="F380" s="3">
         <v>300</v>
       </c>
-      <c r="G380" s="1"/>
       <c r="H380" s="1"/>
-    </row>
-    <row r="381" ht="14.25" spans="1:8">
+      <c r="I380" s="7">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="381" ht="14.25" spans="1:9">
       <c r="A381" s="1">
         <v>379</v>
       </c>
@@ -9541,13 +10297,15 @@
       <c r="E381" s="1">
         <v>50025</v>
       </c>
-      <c r="F381" s="4">
+      <c r="F381" s="3">
+        <v>900</v>
+      </c>
+      <c r="H381" s="1"/>
+      <c r="I381" s="4">
         <v>0</v>
       </c>
-      <c r="G381" s="1"/>
-      <c r="H381" s="1"/>
-    </row>
-    <row r="382" ht="14.25" spans="1:8">
+    </row>
+    <row r="382" ht="14.25" spans="1:9">
       <c r="A382" s="1">
         <v>380</v>
       </c>
@@ -9563,13 +10321,15 @@
       <c r="E382" s="1">
         <v>50025</v>
       </c>
-      <c r="F382" s="4">
+      <c r="F382" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H382" s="1"/>
+      <c r="I382" s="4">
         <v>4000</v>
       </c>
-      <c r="G382" s="1"/>
-      <c r="H382" s="1"/>
-    </row>
-    <row r="383" ht="14.25" spans="1:8">
+    </row>
+    <row r="383" ht="14.25" spans="1:9">
       <c r="A383" s="1">
         <v>381</v>
       </c>
@@ -9585,13 +10345,15 @@
       <c r="E383" s="1">
         <v>50025</v>
       </c>
-      <c r="F383" s="4">
+      <c r="F383" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H383" s="1"/>
+      <c r="I383" s="4">
         <v>4000</v>
       </c>
-      <c r="G383" s="1"/>
-      <c r="H383" s="1"/>
-    </row>
-    <row r="384" ht="14.25" spans="1:8">
+    </row>
+    <row r="384" ht="14.25" spans="1:9">
       <c r="A384" s="1">
         <v>382</v>
       </c>
@@ -9607,13 +10369,15 @@
       <c r="E384" s="1">
         <v>50025</v>
       </c>
-      <c r="F384" s="4">
+      <c r="F384" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H384" s="1"/>
+      <c r="I384" s="4">
         <v>1470</v>
       </c>
-      <c r="G384" s="1"/>
-      <c r="H384" s="1"/>
-    </row>
-    <row r="385" ht="14.25" spans="1:8">
+    </row>
+    <row r="385" ht="14.25" spans="1:9">
       <c r="A385" s="1">
         <v>383</v>
       </c>
@@ -9629,13 +10393,15 @@
       <c r="E385" s="1">
         <v>50025</v>
       </c>
-      <c r="F385" s="4">
+      <c r="F385" s="3">
+        <v>450</v>
+      </c>
+      <c r="H385" s="1"/>
+      <c r="I385" s="4">
         <v>500</v>
       </c>
-      <c r="G385" s="1"/>
-      <c r="H385" s="1"/>
-    </row>
-    <row r="386" ht="14.25" spans="1:8">
+    </row>
+    <row r="386" ht="14.25" spans="1:9">
       <c r="A386" s="1">
         <v>384</v>
       </c>
@@ -9651,13 +10417,15 @@
       <c r="E386" s="1">
         <v>50025</v>
       </c>
-      <c r="F386" s="4">
+      <c r="F386" s="3">
+        <v>120</v>
+      </c>
+      <c r="H386" s="1"/>
+      <c r="I386" s="4">
         <v>30</v>
       </c>
-      <c r="G386" s="1"/>
-      <c r="H386" s="1"/>
-    </row>
-    <row r="387" ht="14.25" spans="1:8">
+    </row>
+    <row r="387" ht="14.25" spans="1:9">
       <c r="A387" s="1">
         <v>385</v>
       </c>
@@ -9673,13 +10441,15 @@
       <c r="E387" s="1">
         <v>50025</v>
       </c>
-      <c r="F387" s="4">
+      <c r="F387" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H387" s="1"/>
+      <c r="I387" s="4">
         <v>1600</v>
       </c>
-      <c r="G387" s="1"/>
-      <c r="H387" s="1"/>
-    </row>
-    <row r="388" ht="14.25" spans="1:8">
+    </row>
+    <row r="388" ht="14.25" spans="1:9">
       <c r="A388" s="1">
         <v>386</v>
       </c>
@@ -9695,13 +10465,15 @@
       <c r="E388" s="1">
         <v>50025</v>
       </c>
-      <c r="F388" s="4">
+      <c r="F388" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H388" s="1"/>
+      <c r="I388" s="4">
         <v>4400</v>
       </c>
-      <c r="G388" s="1"/>
-      <c r="H388" s="1"/>
-    </row>
-    <row r="389" ht="14.25" spans="1:8">
+    </row>
+    <row r="389" ht="14.25" spans="1:9">
       <c r="A389" s="1">
         <v>387</v>
       </c>
@@ -9717,13 +10489,15 @@
       <c r="E389" s="1">
         <v>50025</v>
       </c>
-      <c r="F389" s="4">
+      <c r="F389" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H389" s="1"/>
+      <c r="I389" s="4">
         <v>3000</v>
       </c>
-      <c r="G389" s="1"/>
-      <c r="H389" s="1"/>
-    </row>
-    <row r="390" ht="14.25" spans="1:8">
+    </row>
+    <row r="390" ht="14.25" spans="1:9">
       <c r="A390" s="1">
         <v>388</v>
       </c>
@@ -9739,13 +10513,15 @@
       <c r="E390" s="1">
         <v>50025</v>
       </c>
-      <c r="F390" s="4">
+      <c r="F390" s="3">
+        <v>850</v>
+      </c>
+      <c r="H390" s="1"/>
+      <c r="I390" s="4">
         <v>900</v>
       </c>
-      <c r="G390" s="1"/>
-      <c r="H390" s="1"/>
-    </row>
-    <row r="391" ht="14.25" spans="1:8">
+    </row>
+    <row r="391" ht="14.25" spans="1:9">
       <c r="A391" s="1">
         <v>389</v>
       </c>
@@ -9761,13 +10537,15 @@
       <c r="E391" s="1">
         <v>50025</v>
       </c>
-      <c r="F391" s="4">
+      <c r="F391" s="3">
+        <v>120</v>
+      </c>
+      <c r="H391" s="1"/>
+      <c r="I391" s="4">
         <v>90</v>
       </c>
-      <c r="G391" s="1"/>
-      <c r="H391" s="1"/>
-    </row>
-    <row r="392" ht="14.25" spans="1:8">
+    </row>
+    <row r="392" ht="14.25" spans="1:9">
       <c r="A392" s="1">
         <v>390</v>
       </c>
@@ -9783,13 +10561,15 @@
       <c r="E392" s="1">
         <v>50025</v>
       </c>
-      <c r="F392" s="4">
-        <v>10</v>
-      </c>
-      <c r="G392" s="1"/>
+      <c r="F392" s="3">
+        <v>30</v>
+      </c>
       <c r="H392" s="1"/>
-    </row>
-    <row r="393" ht="14.25" spans="1:8">
+      <c r="I392" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="393" ht="14.25" spans="1:9">
       <c r="A393" s="1">
         <v>391</v>
       </c>
@@ -9805,13 +10585,15 @@
       <c r="E393" s="1">
         <v>60016</v>
       </c>
-      <c r="F393" s="4">
+      <c r="F393" s="3">
         <v>0</v>
       </c>
-      <c r="G393" s="1"/>
       <c r="H393" s="1"/>
-    </row>
-    <row r="394" ht="14.25" spans="1:8">
+      <c r="I393" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" ht="14.25" spans="1:9">
       <c r="A394" s="1">
         <v>392</v>
       </c>
@@ -9827,13 +10609,15 @@
       <c r="E394" s="1">
         <v>60016</v>
       </c>
-      <c r="F394" s="4">
+      <c r="F394" s="3">
         <v>0</v>
       </c>
-      <c r="G394" s="1"/>
       <c r="H394" s="1"/>
-    </row>
-    <row r="395" ht="14.25" spans="1:8">
+      <c r="I394" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" ht="14.25" spans="1:9">
       <c r="A395" s="1">
         <v>393</v>
       </c>
@@ -9849,13 +10633,15 @@
       <c r="E395" s="1">
         <v>60016</v>
       </c>
-      <c r="F395" s="4">
+      <c r="F395" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H395" s="1"/>
+      <c r="I395" s="4">
         <v>0</v>
       </c>
-      <c r="G395" s="1"/>
-      <c r="H395" s="1"/>
-    </row>
-    <row r="396" ht="14.25" spans="1:8">
+    </row>
+    <row r="396" ht="14.25" spans="1:9">
       <c r="A396" s="1">
         <v>394</v>
       </c>
@@ -9871,13 +10657,15 @@
       <c r="E396" s="1">
         <v>60016</v>
       </c>
-      <c r="F396" s="4">
+      <c r="F396" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H396" s="1"/>
+      <c r="I396" s="4">
         <v>7000</v>
       </c>
-      <c r="G396" s="1"/>
-      <c r="H396" s="1"/>
-    </row>
-    <row r="397" ht="14.25" spans="1:8">
+    </row>
+    <row r="397" ht="14.25" spans="1:9">
       <c r="A397" s="1">
         <v>395</v>
       </c>
@@ -9893,13 +10681,15 @@
       <c r="E397" s="1">
         <v>60016</v>
       </c>
-      <c r="F397" s="4">
+      <c r="F397" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H397" s="1"/>
+      <c r="I397" s="4">
         <v>2700</v>
       </c>
-      <c r="G397" s="1"/>
-      <c r="H397" s="1"/>
-    </row>
-    <row r="398" ht="14.25" spans="1:8">
+    </row>
+    <row r="398" ht="14.25" spans="1:9">
       <c r="A398" s="1">
         <v>396</v>
       </c>
@@ -9915,13 +10705,15 @@
       <c r="E398" s="1">
         <v>60016</v>
       </c>
-      <c r="F398" s="4">
+      <c r="F398" s="3">
+        <v>500</v>
+      </c>
+      <c r="H398" s="1"/>
+      <c r="I398" s="4">
         <v>300</v>
       </c>
-      <c r="G398" s="1"/>
-      <c r="H398" s="1"/>
-    </row>
-    <row r="399" ht="14.25" spans="1:8">
+    </row>
+    <row r="399" ht="14.25" spans="1:9">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -9937,13 +10729,15 @@
       <c r="E399" s="1">
         <v>60016</v>
       </c>
-      <c r="F399" s="4">
+      <c r="F399" s="3">
         <v>0</v>
       </c>
-      <c r="G399" s="1"/>
       <c r="H399" s="1"/>
-    </row>
-    <row r="400" ht="14.25" spans="1:8">
+      <c r="I399" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" ht="14.25" spans="1:9">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -9959,13 +10753,15 @@
       <c r="E400" s="1">
         <v>60016</v>
       </c>
-      <c r="F400" s="4">
+      <c r="F400" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H400" s="1"/>
+      <c r="I400" s="4">
         <v>0</v>
       </c>
-      <c r="G400" s="1"/>
-      <c r="H400" s="1"/>
-    </row>
-    <row r="401" ht="14.25" spans="1:8">
+    </row>
+    <row r="401" ht="14.25" spans="1:9">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -9981,13 +10777,15 @@
       <c r="E401" s="1">
         <v>60016</v>
       </c>
-      <c r="F401" s="4">
+      <c r="F401" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H401" s="1"/>
+      <c r="I401" s="4">
         <v>4400</v>
       </c>
-      <c r="G401" s="1"/>
-      <c r="H401" s="1"/>
-    </row>
-    <row r="402" ht="14.25" spans="1:8">
+    </row>
+    <row r="402" ht="14.25" spans="1:9">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -10003,13 +10801,15 @@
       <c r="E402" s="1">
         <v>60016</v>
       </c>
-      <c r="F402" s="4">
+      <c r="F402" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H402" s="1"/>
+      <c r="I402" s="4">
         <v>4400</v>
       </c>
-      <c r="G402" s="1"/>
-      <c r="H402" s="1"/>
-    </row>
-    <row r="403" ht="14.25" spans="1:8">
+    </row>
+    <row r="403" ht="14.25" spans="1:9">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -10025,13 +10825,15 @@
       <c r="E403" s="1">
         <v>60016</v>
       </c>
-      <c r="F403" s="4">
+      <c r="F403" s="3">
+        <v>900</v>
+      </c>
+      <c r="H403" s="1"/>
+      <c r="I403" s="4">
         <v>1100</v>
       </c>
-      <c r="G403" s="1"/>
-      <c r="H403" s="1"/>
-    </row>
-    <row r="404" ht="14.25" spans="1:8">
+    </row>
+    <row r="404" ht="14.25" spans="1:9">
       <c r="A404" s="1">
         <v>402</v>
       </c>
@@ -10047,13 +10849,15 @@
       <c r="E404" s="1">
         <v>60016</v>
       </c>
-      <c r="F404" s="4">
+      <c r="F404" s="3">
+        <v>300</v>
+      </c>
+      <c r="H404" s="1"/>
+      <c r="I404" s="4">
         <v>100</v>
       </c>
-      <c r="G404" s="1"/>
-      <c r="H404" s="1"/>
-    </row>
-    <row r="405" ht="14.25" spans="1:8">
+    </row>
+    <row r="405" ht="14.25" spans="1:9">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -10069,13 +10873,15 @@
       <c r="E405" s="1">
         <v>60016</v>
       </c>
-      <c r="F405" s="4">
+      <c r="F405" s="3">
+        <v>900</v>
+      </c>
+      <c r="H405" s="1"/>
+      <c r="I405" s="4">
         <v>0</v>
       </c>
-      <c r="G405" s="1"/>
-      <c r="H405" s="1"/>
-    </row>
-    <row r="406" ht="14.25" spans="1:8">
+    </row>
+    <row r="406" ht="14.25" spans="1:9">
       <c r="A406" s="1">
         <v>404</v>
       </c>
@@ -10091,13 +10897,15 @@
       <c r="E406" s="1">
         <v>60016</v>
       </c>
-      <c r="F406" s="4">
+      <c r="F406" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H406" s="1"/>
+      <c r="I406" s="4">
         <v>4000</v>
       </c>
-      <c r="G406" s="1"/>
-      <c r="H406" s="1"/>
-    </row>
-    <row r="407" ht="14.25" spans="1:8">
+    </row>
+    <row r="407" ht="14.25" spans="1:9">
       <c r="A407" s="1">
         <v>405</v>
       </c>
@@ -10113,13 +10921,15 @@
       <c r="E407" s="1">
         <v>60016</v>
       </c>
-      <c r="F407" s="4">
+      <c r="F407" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H407" s="1"/>
+      <c r="I407" s="4">
         <v>4000</v>
       </c>
-      <c r="G407" s="1"/>
-      <c r="H407" s="1"/>
-    </row>
-    <row r="408" ht="14.25" spans="1:8">
+    </row>
+    <row r="408" ht="14.25" spans="1:9">
       <c r="A408" s="1">
         <v>406</v>
       </c>
@@ -10135,13 +10945,15 @@
       <c r="E408" s="1">
         <v>60016</v>
       </c>
-      <c r="F408" s="4">
+      <c r="F408" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H408" s="1"/>
+      <c r="I408" s="4">
         <v>1470</v>
       </c>
-      <c r="G408" s="1"/>
-      <c r="H408" s="1"/>
-    </row>
-    <row r="409" ht="14.25" spans="1:8">
+    </row>
+    <row r="409" ht="14.25" spans="1:9">
       <c r="A409" s="1">
         <v>407</v>
       </c>
@@ -10157,13 +10969,15 @@
       <c r="E409" s="1">
         <v>60016</v>
       </c>
-      <c r="F409" s="4">
+      <c r="F409" s="3">
+        <v>450</v>
+      </c>
+      <c r="H409" s="1"/>
+      <c r="I409" s="4">
         <v>500</v>
       </c>
-      <c r="G409" s="1"/>
-      <c r="H409" s="1"/>
-    </row>
-    <row r="410" ht="14.25" spans="1:8">
+    </row>
+    <row r="410" ht="14.25" spans="1:9">
       <c r="A410" s="1">
         <v>408</v>
       </c>
@@ -10179,32 +10993,34 @@
       <c r="E410" s="1">
         <v>60016</v>
       </c>
-      <c r="F410" s="4">
+      <c r="F410" s="3">
+        <v>120</v>
+      </c>
+      <c r="H410" s="1"/>
+      <c r="I410" s="4">
         <v>30</v>
       </c>
-      <c r="G410" s="1"/>
-      <c r="H410" s="1"/>
-    </row>
-    <row r="411" ht="14.25" spans="1:8">
+    </row>
+    <row r="411" ht="14.25" spans="1:9">
       <c r="F411" s="1"/>
     </row>
-    <row r="412" ht="14.25" spans="1:8">
+    <row r="412" ht="14.25" spans="1:9">
       <c r="F412" s="1"/>
     </row>
-    <row r="413" ht="14.25" spans="1:8">
+    <row r="413" ht="14.25" spans="1:9">
       <c r="F413" s="1"/>
     </row>
-    <row r="414" ht="14.25" spans="1:8">
+    <row r="414" ht="14.25" spans="1:9">
       <c r="F414" s="1"/>
     </row>
-    <row r="415" ht="14.25" spans="1:8">
+    <row r="415" ht="14.25" spans="1:9">
       <c r="F415" s="1"/>
     </row>
-    <row r="416" ht="14.25" spans="1:8">
+    <row r="416" ht="14.25" spans="1:9">
       <c r="F416" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F3:F410">
+  <conditionalFormatting sqref="I3:I410">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($D3,2)=1</formula>
     </cfRule>
